--- a/research/traditional_assets/database/data/colombia/colombia_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_oil_gas_integrated.xlsx
@@ -650,10 +650,10 @@
         <v>0.1896138330321124</v>
       </c>
       <c r="X2">
-        <v>0.1846575442342597</v>
+        <v>0.1846262052551799</v>
       </c>
       <c r="Y2">
-        <v>0.004956288797852704</v>
+        <v>0.004987627776932541</v>
       </c>
       <c r="Z2">
         <v>0.7563572550280969</v>
@@ -662,10 +662,10 @@
         <v>0.140379389155289</v>
       </c>
       <c r="AB2">
-        <v>0.09968654234642182</v>
+        <v>0.0996752923937613</v>
       </c>
       <c r="AC2">
-        <v>0.04069284680886714</v>
+        <v>0.04070409676152767</v>
       </c>
       <c r="AD2">
         <v>27916.9</v>
@@ -787,10 +787,10 @@
         <v>0.1896138330321124</v>
       </c>
       <c r="X3">
-        <v>0.1846575442342597</v>
+        <v>0.1846262052551799</v>
       </c>
       <c r="Y3">
-        <v>0.004956288797852704</v>
+        <v>0.004987627776932541</v>
       </c>
       <c r="Z3">
         <v>0.7563572550280969</v>
@@ -799,10 +799,10 @@
         <v>0.140379389155289</v>
       </c>
       <c r="AB3">
-        <v>0.09968654234642182</v>
+        <v>0.0996752923937613</v>
       </c>
       <c r="AC3">
-        <v>0.04069284680886714</v>
+        <v>0.04070409676152767</v>
       </c>
       <c r="AD3">
         <v>27916.9</v>
@@ -1139,7 +1139,7 @@
         <v>7.09143226261084</v>
       </c>
       <c r="F2">
-        <v>3.64900122904341</v>
+        <v>3.77693710474472</v>
       </c>
       <c r="G2">
         <v>2.21694659519555</v>
@@ -1157,13 +1157,13 @@
         <v>15633.6</v>
       </c>
       <c r="L2">
-        <v>4373.33516980649</v>
+        <v>5315.07634698105</v>
       </c>
       <c r="M2">
         <v>40168.8</v>
       </c>
       <c r="N2">
-        <v>44106.6301698065</v>
+        <v>45048.3713469811</v>
       </c>
       <c r="O2">
         <v>27916.9</v>
@@ -1172,16 +1172,16 @@
         <v>43114.995</v>
       </c>
       <c r="Q2">
-        <v>0.0996865423464218</v>
+        <v>0.0996752923937613</v>
       </c>
       <c r="R2">
-        <v>0.09184858777039211</v>
+        <v>0.0901660093684255</v>
       </c>
       <c r="S2">
         <v>0.0521023673444086</v>
       </c>
       <c r="T2">
-        <v>0.0498923673444086</v>
+        <v>0.0482023673444086</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.18465754423426</v>
+        <v>0.18462620525518</v>
       </c>
       <c r="X2">
-        <v>4.24551440994275</v>
+        <v>4.2445665697461</v>
       </c>
       <c r="Y2">
         <v>2.0200904410493</v>
@@ -1236,7 +1236,7 @@
         <v>15633.6</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524602</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1100649488897132</v>
+        <v>0.1100504448316159</v>
       </c>
       <c r="C2">
-        <v>39303.87716277559</v>
+        <v>39305.02910482491</v>
       </c>
       <c r="D2">
-        <v>35922.1771627756</v>
+        <v>35923.32910482491</v>
       </c>
       <c r="E2">
         <v>-27916.9</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1100649488897132</v>
+        <v>0.1100504448316159</v>
       </c>
       <c r="T2">
         <v>0.9349222590860212</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V2">
         <v>0.35</v>
       </c>
       <c r="W2">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1098406452420433</v>
+        <v>0.1098170919481493</v>
       </c>
       <c r="C3">
-        <v>38950.63744280067</v>
+        <v>38955.1225512445</v>
       </c>
       <c r="D3">
-        <v>36004.44244280067</v>
+        <v>36008.9275512445</v>
       </c>
       <c r="E3">
         <v>-27481.395</v>
@@ -1539,37 +1539,37 @@
         <v>12076</v>
       </c>
       <c r="M3">
-        <v>30.72813890819489</v>
+        <v>30.11843190819489</v>
       </c>
       <c r="N3">
-        <v>12045.27186109181</v>
+        <v>12045.88156809181</v>
       </c>
       <c r="O3">
-        <v>4215.845151382132</v>
+        <v>4216.058548832131</v>
       </c>
       <c r="P3">
-        <v>7829.426709709674</v>
+        <v>7829.823019259674</v>
       </c>
       <c r="Q3">
-        <v>8345.926709709674</v>
+        <v>8346.323019259675</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1104868904733325</v>
+        <v>0.110472291186571</v>
       </c>
       <c r="T3">
         <v>0.9410606375547679</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V3">
         <v>0.35</v>
       </c>
       <c r="W3">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>392.99483890251</v>
+        <v>400.9504889500656</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1096163415943734</v>
+        <v>0.1095837390646828</v>
       </c>
       <c r="C4">
-        <v>38597.77537868157</v>
+        <v>38605.62490157037</v>
       </c>
       <c r="D4">
-        <v>36087.08537868158</v>
+        <v>36094.93490157037</v>
       </c>
       <c r="E4">
         <v>-27045.89</v>
@@ -1621,37 +1621,37 @@
         <v>12076</v>
       </c>
       <c r="M4">
-        <v>61.45627781638978</v>
+        <v>60.23686381638979</v>
       </c>
       <c r="N4">
-        <v>12014.54372218361</v>
+        <v>12015.76313618361</v>
       </c>
       <c r="O4">
-        <v>4205.090302764263</v>
+        <v>4205.517097664263</v>
       </c>
       <c r="P4">
-        <v>7809.453419419347</v>
+        <v>7810.246038519347</v>
       </c>
       <c r="Q4">
-        <v>8325.953419419347</v>
+        <v>8326.746038519348</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1109174431096788</v>
+        <v>0.1109027466508108</v>
       </c>
       <c r="T4">
         <v>0.9473242890534889</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V4">
         <v>0.35</v>
       </c>
       <c r="W4">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>196.497419451255</v>
+        <v>200.4752444750328</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1093920379467035</v>
+        <v>0.1093503861812162</v>
       </c>
       <c r="C5">
-        <v>38245.29357696274</v>
+        <v>38256.53909281947</v>
       </c>
       <c r="D5">
-        <v>36170.10857696275</v>
+        <v>36181.35409281947</v>
       </c>
       <c r="E5">
         <v>-26610.385</v>
@@ -1703,37 +1703,37 @@
         <v>12076</v>
       </c>
       <c r="M5">
-        <v>92.18441672458466</v>
+        <v>90.35529572458466</v>
       </c>
       <c r="N5">
-        <v>11983.81558327541</v>
+        <v>11985.64470427542</v>
       </c>
       <c r="O5">
-        <v>4194.335454146395</v>
+        <v>4194.975646496395</v>
       </c>
       <c r="P5">
-        <v>7789.48012912902</v>
+        <v>7790.66905777902</v>
       </c>
       <c r="Q5">
-        <v>8305.98012912902</v>
+        <v>8307.169057779021</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1113568731199703</v>
+        <v>0.1113420774854474</v>
       </c>
       <c r="T5">
         <v>0.9537170880057917</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V5">
         <v>0.35</v>
       </c>
       <c r="W5">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>130.99827963417</v>
+        <v>133.6501629833552</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1091677342990336</v>
+        <v>0.1091170332977496</v>
       </c>
       <c r="C6">
-        <v>37893.19466823072</v>
+        <v>37907.86809020365</v>
       </c>
       <c r="D6">
-        <v>36253.51466823072</v>
+        <v>36268.18809020365</v>
       </c>
       <c r="E6">
         <v>-26174.88</v>
@@ -1785,37 +1785,37 @@
         <v>12076</v>
       </c>
       <c r="M6">
-        <v>122.9125556327796</v>
+        <v>120.4737276327796</v>
       </c>
       <c r="N6">
-        <v>11953.08744436722</v>
+        <v>11955.52627236722</v>
       </c>
       <c r="O6">
-        <v>4183.580605528527</v>
+        <v>4184.434195328527</v>
       </c>
       <c r="P6">
-        <v>7769.506838838694</v>
+        <v>7771.092077038694</v>
       </c>
       <c r="Q6">
-        <v>8286.006838838694</v>
+        <v>8287.592077038695</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1118054579221429</v>
+        <v>0.1117905610458055</v>
       </c>
       <c r="T6">
         <v>0.960243070269601</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V6">
         <v>0.35</v>
       </c>
       <c r="W6">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>98.24870972562749</v>
+        <v>100.2376222375164</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1089434306513637</v>
+        <v>0.108883680414283</v>
       </c>
       <c r="C7">
-        <v>37541.48130739204</v>
+        <v>37559.61488746892</v>
       </c>
       <c r="D7">
-        <v>36337.30630739204</v>
+        <v>36355.43988746892</v>
       </c>
       <c r="E7">
         <v>-25739.375</v>
@@ -1867,37 +1867,37 @@
         <v>12076</v>
       </c>
       <c r="M7">
-        <v>153.6406945409745</v>
+        <v>150.5921595409745</v>
       </c>
       <c r="N7">
-        <v>11922.35930545903</v>
+        <v>11925.40784045903</v>
       </c>
       <c r="O7">
-        <v>4172.825756910659</v>
+        <v>4173.892744160658</v>
       </c>
       <c r="P7">
-        <v>7749.533548548367</v>
+        <v>7751.515096298367</v>
       </c>
       <c r="Q7">
-        <v>8266.033548548367</v>
+        <v>8268.015096298368</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1122634866148876</v>
+        <v>0.1122484863653291</v>
       </c>
       <c r="T7">
         <v>0.9669064416337009</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V7">
         <v>0.35</v>
       </c>
       <c r="W7">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>78.59896778050199</v>
+        <v>80.19009779001311</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1087191270036937</v>
+        <v>0.1086503275308165</v>
       </c>
       <c r="C8">
-        <v>37190.15617395493</v>
+        <v>37211.7825072394</v>
       </c>
       <c r="D8">
-        <v>36421.48617395493</v>
+        <v>36443.1125072394</v>
       </c>
       <c r="E8">
         <v>-25303.87</v>
@@ -1949,37 +1949,37 @@
         <v>12076</v>
       </c>
       <c r="M8">
-        <v>184.3688334491693</v>
+        <v>180.7105914491693</v>
       </c>
       <c r="N8">
-        <v>11891.63116655083</v>
+        <v>11895.28940855083</v>
       </c>
       <c r="O8">
-        <v>4162.070908292791</v>
+        <v>4163.35129299279</v>
       </c>
       <c r="P8">
-        <v>7729.56025825804</v>
+        <v>7731.93811555804</v>
       </c>
       <c r="Q8">
-        <v>8246.06025825804</v>
+        <v>8248.438115558041</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1127312605989673</v>
+        <v>0.1127161547767574</v>
       </c>
       <c r="T8">
         <v>0.9737115868566115</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V8">
         <v>0.35</v>
       </c>
       <c r="W8">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>65.49913981708501</v>
+        <v>66.82508149167761</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1084948233560238</v>
+        <v>0.1084169746473499</v>
       </c>
       <c r="C9">
-        <v>36839.22197231489</v>
+        <v>36864.37400136645</v>
       </c>
       <c r="D9">
-        <v>36506.05697231489</v>
+        <v>36531.20900136646</v>
       </c>
       <c r="E9">
         <v>-24868.365</v>
@@ -2031,37 +2031,37 @@
         <v>12076</v>
       </c>
       <c r="M9">
-        <v>215.0969723573643</v>
+        <v>210.8290233573643</v>
       </c>
       <c r="N9">
-        <v>11860.90302764264</v>
+        <v>11865.17097664264</v>
       </c>
       <c r="O9">
-        <v>4151.316059674922</v>
+        <v>4152.809841824922</v>
       </c>
       <c r="P9">
-        <v>7709.586967967714</v>
+        <v>7712.361134817714</v>
       </c>
       <c r="Q9">
-        <v>8226.086967967714</v>
+        <v>8228.861134817715</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1132090942386185</v>
+        <v>0.1131938805733778</v>
       </c>
       <c r="T9">
         <v>0.9806630792886168</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>56.14211984321571</v>
+        <v>57.2786412785808</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1082705197083539</v>
+        <v>0.1081836217638834</v>
       </c>
       <c r="C10">
-        <v>36488.68143204435</v>
+        <v>36517.39245128275</v>
       </c>
       <c r="D10">
-        <v>36591.02143204436</v>
+        <v>36619.73245128275</v>
       </c>
       <c r="E10">
         <v>-24432.86</v>
@@ -2113,37 +2113,37 @@
         <v>12076</v>
       </c>
       <c r="M10">
-        <v>245.8251112655591</v>
+        <v>240.9474552655591</v>
       </c>
       <c r="N10">
-        <v>11830.17488873444</v>
+        <v>11835.05254473444</v>
       </c>
       <c r="O10">
-        <v>4140.561211057054</v>
+        <v>4142.268390657054</v>
       </c>
       <c r="P10">
-        <v>7689.613677677386</v>
+        <v>7692.784154077387</v>
       </c>
       <c r="Q10">
-        <v>8206.113677677386</v>
+        <v>8209.284154077388</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1136973155660883</v>
+        <v>0.1136819917134029</v>
       </c>
       <c r="T10">
         <v>0.987765691121318</v>
       </c>
       <c r="U10">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>49.12435486281375</v>
+        <v>50.1188111187582</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.108046216060684</v>
+        <v>0.1079502688804168</v>
       </c>
       <c r="C11">
-        <v>36138.53730818634</v>
+        <v>36170.84096836159</v>
       </c>
       <c r="D11">
-        <v>36676.38230818634</v>
+        <v>36708.68596836159</v>
       </c>
       <c r="E11">
         <v>-23997.355</v>
@@ -2195,37 +2195,37 @@
         <v>12076</v>
       </c>
       <c r="M11">
-        <v>276.553250173754</v>
+        <v>271.065887173754</v>
       </c>
       <c r="N11">
-        <v>11799.44674982625</v>
+        <v>11804.93411282625</v>
       </c>
       <c r="O11">
-        <v>4129.806362439186</v>
+        <v>4131.726939489185</v>
       </c>
       <c r="P11">
-        <v>7669.640387387059</v>
+        <v>7673.20717333706</v>
       </c>
       <c r="Q11">
-        <v>8186.140387387059</v>
+        <v>8189.70717333706</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1141962670326233</v>
+        <v>0.1141808305707912</v>
       </c>
       <c r="T11">
         <v>0.9950244043129797</v>
       </c>
       <c r="U11">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>43.66609321139</v>
+        <v>44.55005432778506</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1078219124130141</v>
+        <v>0.1077169159969502</v>
       </c>
       <c r="C12">
-        <v>35788.79238155227</v>
+        <v>35824.72269428138</v>
       </c>
       <c r="D12">
-        <v>36762.14238155228</v>
+        <v>36798.07269428139</v>
       </c>
       <c r="E12">
         <v>-23561.85</v>
@@ -2277,37 +2277,37 @@
         <v>12076</v>
       </c>
       <c r="M12">
-        <v>307.2813890819489</v>
+        <v>301.184319081949</v>
       </c>
       <c r="N12">
-        <v>11768.71861091805</v>
+        <v>11774.81568091805</v>
       </c>
       <c r="O12">
-        <v>4119.051513821318</v>
+        <v>4121.185488321317</v>
       </c>
       <c r="P12">
-        <v>7649.667097096733</v>
+        <v>7653.630192596734</v>
       </c>
       <c r="Q12">
-        <v>8166.167097096733</v>
+        <v>8170.130192596734</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1147063063095258</v>
+        <v>0.1146907547361215</v>
       </c>
       <c r="T12">
         <v>1.002444422242234</v>
       </c>
       <c r="U12">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>39.299483890251</v>
+        <v>40.09504889500656</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1075976087653442</v>
+        <v>0.1074835631134836</v>
       </c>
       <c r="C13">
-        <v>35439.44945902385</v>
+        <v>35479.04080139557</v>
       </c>
       <c r="D13">
-        <v>36848.30445902386</v>
+        <v>36887.89580139557</v>
       </c>
       <c r="E13">
         <v>-23126.345</v>
@@ -2359,37 +2359,37 @@
         <v>12076</v>
       </c>
       <c r="M13">
-        <v>338.0095279901439</v>
+        <v>331.3027509901438</v>
       </c>
       <c r="N13">
-        <v>11737.99047200986</v>
+        <v>11744.69724900986</v>
       </c>
       <c r="O13">
-        <v>4108.296665203449</v>
+        <v>4110.644037153449</v>
       </c>
       <c r="P13">
-        <v>7629.693806806407</v>
+        <v>7634.053211856407</v>
       </c>
       <c r="Q13">
-        <v>8146.193806806407</v>
+        <v>8150.553211856407</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1152278071432127</v>
+        <v>0.1152121378714592</v>
       </c>
       <c r="T13">
         <v>1.010031182147426</v>
       </c>
       <c r="U13">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>35.72680353659181</v>
+        <v>36.45004445000597</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1073733051176743</v>
+        <v>0.1072502102300171</v>
       </c>
       <c r="C14">
-        <v>35090.51137385946</v>
+        <v>35133.7984931079</v>
       </c>
       <c r="D14">
-        <v>36934.87137385946</v>
+        <v>36978.15849310791</v>
       </c>
       <c r="E14">
         <v>-22690.84</v>
@@ -2441,37 +2441,37 @@
         <v>12076</v>
       </c>
       <c r="M14">
-        <v>368.7376668983387</v>
+        <v>361.4211828983387</v>
       </c>
       <c r="N14">
-        <v>11707.26233310166</v>
+        <v>11714.57881710166</v>
       </c>
       <c r="O14">
-        <v>4097.541816585582</v>
+        <v>4100.102585985581</v>
       </c>
       <c r="P14">
-        <v>7609.72051651608</v>
+        <v>7614.47623111608</v>
       </c>
       <c r="Q14">
-        <v>8126.22051651608</v>
+        <v>8130.97623111608</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1157611602685741</v>
+        <v>0.1157453706235091</v>
       </c>
       <c r="T14">
         <v>1.0177903684141</v>
       </c>
       <c r="U14">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V14">
         <v>0.35</v>
       </c>
       <c r="W14">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>32.7495699085425</v>
+        <v>33.4125407458388</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1071490014700044</v>
+        <v>0.1070168573465505</v>
       </c>
       <c r="C15">
-        <v>34741.98098600451</v>
+        <v>34788.99900425325</v>
       </c>
       <c r="D15">
-        <v>37021.84598600452</v>
+        <v>37068.86400425326</v>
       </c>
       <c r="E15">
         <v>-22255.335</v>
@@ -2523,37 +2523,37 @@
         <v>12076</v>
       </c>
       <c r="M15">
-        <v>399.4658058065336</v>
+        <v>391.5396148065336</v>
       </c>
       <c r="N15">
-        <v>11676.53419419347</v>
+        <v>11684.46038519347</v>
       </c>
       <c r="O15">
-        <v>4086.786967967713</v>
+        <v>4089.561134817713</v>
       </c>
       <c r="P15">
-        <v>7589.747226225752</v>
+        <v>7594.899250375753</v>
       </c>
       <c r="Q15">
-        <v>8106.247226225752</v>
+        <v>8111.399250375753</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1163067743853233</v>
+        <v>0.1162908615997441</v>
       </c>
       <c r="T15">
         <v>1.025727926778859</v>
       </c>
       <c r="U15">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.23037222326999</v>
+        <v>30.8423453038512</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1069246978223345</v>
+        <v>0.1067835044630839</v>
       </c>
       <c r="C16">
-        <v>34393.86118240662</v>
+        <v>34444.64560148409</v>
       </c>
       <c r="D16">
-        <v>37109.23118240663</v>
+        <v>37160.01560148409</v>
       </c>
       <c r="E16">
         <v>-21819.83</v>
@@ -2605,37 +2605,37 @@
         <v>12076</v>
       </c>
       <c r="M16">
-        <v>430.1939447147285</v>
+        <v>421.6580467147285</v>
       </c>
       <c r="N16">
-        <v>11645.80605528527</v>
+        <v>11654.34195328527</v>
       </c>
       <c r="O16">
-        <v>4076.032119349845</v>
+        <v>4079.019683649845</v>
       </c>
       <c r="P16">
-        <v>7569.773935935426</v>
+        <v>7575.322269635426</v>
       </c>
       <c r="Q16">
-        <v>8086.273935935426</v>
+        <v>8091.822269635426</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1168650772024619</v>
+        <v>0.1168490384126357</v>
       </c>
       <c r="T16">
         <v>1.033850079524193</v>
       </c>
       <c r="U16">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.07105992160785</v>
+        <v>28.6393206392904</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1067003941746646</v>
+        <v>0.1065501515796174</v>
       </c>
       <c r="C17">
-        <v>34046.15487733488</v>
+        <v>34100.74158366262</v>
       </c>
       <c r="D17">
-        <v>37197.02987733488</v>
+        <v>37251.61658366262</v>
       </c>
       <c r="E17">
         <v>-21384.325</v>
@@ -2687,37 +2687,37 @@
         <v>12076</v>
       </c>
       <c r="M17">
-        <v>460.9220836229234</v>
+        <v>451.7764786229234</v>
       </c>
       <c r="N17">
-        <v>11615.07791637708</v>
+        <v>11624.22352137708</v>
       </c>
       <c r="O17">
-        <v>4065.277270731976</v>
+        <v>4068.478232481977</v>
       </c>
       <c r="P17">
-        <v>7549.8006456451</v>
+        <v>7555.745288895099</v>
       </c>
       <c r="Q17">
-        <v>8066.3006456451</v>
+        <v>8072.245288895099</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1174365165564744</v>
+        <v>0.1174203487975954</v>
       </c>
       <c r="T17">
         <v>1.042163341745888</v>
       </c>
       <c r="U17">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.199655926834</v>
+        <v>26.73003259667104</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1064760905269946</v>
+        <v>0.1063167986961508</v>
       </c>
       <c r="C18">
-        <v>33698.86501270389</v>
+        <v>33757.29028225873</v>
       </c>
       <c r="D18">
-        <v>37285.24501270389</v>
+        <v>37343.67028225874</v>
       </c>
       <c r="E18">
         <v>-20948.82</v>
@@ -2769,37 +2769,37 @@
         <v>12076</v>
       </c>
       <c r="M18">
-        <v>491.6502225311182</v>
+        <v>481.8949105311183</v>
       </c>
       <c r="N18">
-        <v>11584.34977746888</v>
+        <v>11594.10508946888</v>
       </c>
       <c r="O18">
-        <v>4054.522422114108</v>
+        <v>4057.936781314108</v>
       </c>
       <c r="P18">
-        <v>7529.827355354773</v>
+        <v>7536.168308154773</v>
       </c>
       <c r="Q18">
-        <v>8046.327355354773</v>
+        <v>8052.668308154773</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.118021561609392</v>
+        <v>0.1180052618107683</v>
       </c>
       <c r="T18">
         <v>1.050674538782386</v>
       </c>
       <c r="U18">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V18">
         <v>0.35</v>
       </c>
       <c r="W18">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>24.56217743140688</v>
+        <v>25.0594055593791</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1062517868793247</v>
+        <v>0.1060834458126842</v>
       </c>
       <c r="C19">
-        <v>33351.99455840234</v>
+        <v>33414.29506175394</v>
       </c>
       <c r="D19">
-        <v>37373.87955840235</v>
+        <v>37436.18006175394</v>
       </c>
       <c r="E19">
         <v>-20513.315</v>
@@ -2851,37 +2851,37 @@
         <v>12076</v>
       </c>
       <c r="M19">
-        <v>522.3783614393133</v>
+        <v>512.0133424393132</v>
       </c>
       <c r="N19">
-        <v>11553.62163856069</v>
+        <v>11563.98665756069</v>
       </c>
       <c r="O19">
-        <v>4043.76757349624</v>
+        <v>4047.39533014624</v>
       </c>
       <c r="P19">
-        <v>7509.854065064446</v>
+        <v>7516.591327414446</v>
       </c>
       <c r="Q19">
-        <v>8026.354065064446</v>
+        <v>8033.091327414446</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1186207041334642</v>
+        <v>0.1186042691134154</v>
       </c>
       <c r="T19">
         <v>1.0593908249041</v>
       </c>
       <c r="U19">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.11734346485352</v>
+        <v>23.58532287941562</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1060274832316548</v>
+        <v>0.1058500929292177</v>
       </c>
       <c r="C20">
-        <v>33005.54651262633</v>
+        <v>33071.75932005123</v>
       </c>
       <c r="D20">
-        <v>37462.93651262633</v>
+        <v>37529.14932005124</v>
       </c>
       <c r="E20">
         <v>-20077.81</v>
@@ -2933,37 +2933,37 @@
         <v>12076</v>
       </c>
       <c r="M20">
-        <v>553.106500347508</v>
+        <v>542.1317743475081</v>
       </c>
       <c r="N20">
-        <v>11522.89349965249</v>
+        <v>11533.86822565249</v>
       </c>
       <c r="O20">
-        <v>4033.012724878372</v>
+        <v>4036.853878978372</v>
       </c>
       <c r="P20">
-        <v>7489.880774774119</v>
+        <v>7497.014346674119</v>
       </c>
       <c r="Q20">
-        <v>8006.380774774119</v>
+        <v>8013.514346674119</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1192344598898308</v>
+        <v>0.1192178863502733</v>
       </c>
       <c r="T20">
         <v>1.068319703370246</v>
       </c>
       <c r="U20">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.833046605695</v>
+        <v>22.27502716389253</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1058031795839849</v>
+        <v>0.1056167400457511</v>
       </c>
       <c r="C21">
-        <v>32659.52390221739</v>
+        <v>32729.68648889116</v>
       </c>
       <c r="D21">
-        <v>37552.4189022174</v>
+        <v>37622.58148889116</v>
       </c>
       <c r="E21">
         <v>-19642.305</v>
@@ -3015,37 +3015,37 @@
         <v>12076</v>
       </c>
       <c r="M21">
-        <v>583.8346392557029</v>
+        <v>572.2502062557029</v>
       </c>
       <c r="N21">
-        <v>11492.1653607443</v>
+        <v>11503.7497937443</v>
       </c>
       <c r="O21">
-        <v>4022.257876260504</v>
+        <v>4026.312427810504</v>
       </c>
       <c r="P21">
-        <v>7469.907484483793</v>
+        <v>7477.437365933793</v>
       </c>
       <c r="Q21">
-        <v>7986.407484483793</v>
+        <v>7993.937365933793</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1198633701093176</v>
+        <v>0.1198466546300166</v>
       </c>
       <c r="T21">
         <v>1.077469047971359</v>
       </c>
       <c r="U21">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V21">
         <v>0.35</v>
       </c>
       <c r="W21">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>20.68393888960579</v>
+        <v>21.10265731316135</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.105578875936315</v>
+        <v>0.1053833871622845</v>
       </c>
       <c r="C22">
-        <v>32313.92978300549</v>
+        <v>32388.08003427406</v>
       </c>
       <c r="D22">
-        <v>37642.32978300549</v>
+        <v>37716.48003427406</v>
       </c>
       <c r="E22">
         <v>-19206.8</v>
@@ -3097,37 +3097,37 @@
         <v>12076</v>
       </c>
       <c r="M22">
-        <v>614.5627781638979</v>
+        <v>602.3686381638979</v>
       </c>
       <c r="N22">
-        <v>11461.4372218361</v>
+        <v>11473.6313618361</v>
       </c>
       <c r="O22">
-        <v>4011.503027642636</v>
+        <v>4015.770976642636</v>
       </c>
       <c r="P22">
-        <v>7449.934194193467</v>
+        <v>7457.860385193466</v>
       </c>
       <c r="Q22">
-        <v>7966.434194193467</v>
+        <v>7974.360385193466</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1205080030842916</v>
+        <v>0.1204911421167535</v>
       </c>
       <c r="T22">
         <v>1.0868471261875</v>
       </c>
       <c r="U22">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>19.6497419451255</v>
+        <v>20.04752444750328</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1053545722886451</v>
+        <v>0.1051500342788179</v>
       </c>
       <c r="C23">
-        <v>31968.76724015678</v>
+        <v>32046.94345688865</v>
       </c>
       <c r="D23">
-        <v>37732.67224015678</v>
+        <v>37810.84845688865</v>
       </c>
       <c r="E23">
         <v>-18771.295</v>
@@ -3179,37 +3179,37 @@
         <v>12076</v>
       </c>
       <c r="M23">
-        <v>645.2909170720927</v>
+        <v>632.4870700720927</v>
       </c>
       <c r="N23">
-        <v>11430.70908292791</v>
+        <v>11443.51292992791</v>
       </c>
       <c r="O23">
-        <v>4000.748179024768</v>
+        <v>4005.229525474767</v>
       </c>
       <c r="P23">
-        <v>7429.96090390314</v>
+        <v>7438.283404453139</v>
       </c>
       <c r="Q23">
-        <v>7946.46090390314</v>
+        <v>7954.783404453139</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1211689558814168</v>
+        <v>0.1211519457423951</v>
       </c>
       <c r="T23">
         <v>1.096462624105315</v>
       </c>
       <c r="U23">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.71403994773857</v>
+        <v>19.0928804261936</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1051302686409752</v>
+        <v>0.1049166813953514</v>
       </c>
       <c r="C24">
-        <v>31624.03938852659</v>
+        <v>31706.28029254705</v>
       </c>
       <c r="D24">
-        <v>37823.44938852659</v>
+        <v>37905.69029254705</v>
       </c>
       <c r="E24">
         <v>-18335.79</v>
@@ -3261,37 +3261,37 @@
         <v>12076</v>
       </c>
       <c r="M24">
-        <v>676.0190559802877</v>
+        <v>662.6055019802876</v>
       </c>
       <c r="N24">
-        <v>11399.98094401971</v>
+        <v>11413.39449801971</v>
       </c>
       <c r="O24">
-        <v>3989.9933304069</v>
+        <v>3994.688074306899</v>
       </c>
       <c r="P24">
-        <v>7409.987613612813</v>
+        <v>7418.706423712812</v>
       </c>
       <c r="Q24">
-        <v>7926.487613612813</v>
+        <v>7935.206423712812</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1218468561861606</v>
+        <v>0.1218296930507455</v>
       </c>
       <c r="T24">
         <v>1.106324673251792</v>
       </c>
       <c r="U24">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.86340176829591</v>
+        <v>18.22502222500298</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1049059649933053</v>
+        <v>0.1046833285118848</v>
       </c>
       <c r="C25">
-        <v>31279.74937301733</v>
+        <v>31366.0941126265</v>
       </c>
       <c r="D25">
-        <v>37914.66437301733</v>
+        <v>38001.0091126265</v>
       </c>
       <c r="E25">
         <v>-17900.285</v>
@@ -3343,37 +3343,37 @@
         <v>12076</v>
       </c>
       <c r="M25">
-        <v>706.7471948884825</v>
+        <v>692.7239338884825</v>
       </c>
       <c r="N25">
-        <v>11369.25280511152</v>
+        <v>11383.27606611152</v>
       </c>
       <c r="O25">
-        <v>3979.238481789031</v>
+        <v>3984.146623139031</v>
       </c>
       <c r="P25">
-        <v>7390.014323322486</v>
+        <v>7399.129442972486</v>
       </c>
       <c r="Q25">
-        <v>7906.514323322486</v>
+        <v>7915.629442972486</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1225423642910277</v>
+        <v>0.1225250441852868</v>
       </c>
       <c r="T25">
         <v>1.116442879518956</v>
       </c>
       <c r="U25">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V25">
         <v>0.35</v>
       </c>
       <c r="W25">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.08673212619609</v>
+        <v>17.43262995435068</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1046816613456354</v>
+        <v>0.1044499756284182</v>
       </c>
       <c r="C26">
-        <v>30935.90036894179</v>
+        <v>31026.38852451753</v>
       </c>
       <c r="D26">
-        <v>38006.32036894179</v>
+        <v>38096.80852451753</v>
       </c>
       <c r="E26">
         <v>-17464.78</v>
@@ -3425,37 +3425,37 @@
         <v>12076</v>
       </c>
       <c r="M26">
-        <v>737.4753337966773</v>
+        <v>722.8423657966773</v>
       </c>
       <c r="N26">
-        <v>11338.52466620332</v>
+        <v>11353.15763420332</v>
       </c>
       <c r="O26">
-        <v>3968.483633171163</v>
+        <v>3973.605171971163</v>
       </c>
       <c r="P26">
-        <v>7370.041033032159</v>
+        <v>7379.552462232159</v>
       </c>
       <c r="Q26">
-        <v>7886.541033032159</v>
+        <v>7896.052462232159</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1232561752407596</v>
+        <v>0.123238694033895</v>
       </c>
       <c r="T26">
         <v>1.126827354372099</v>
       </c>
       <c r="U26">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.37478495427125</v>
+        <v>16.7062703729194</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1044573576979655</v>
+        <v>0.1042166227449517</v>
       </c>
       <c r="C27">
-        <v>30592.49558239148</v>
+        <v>30687.16717207912</v>
       </c>
       <c r="D27">
-        <v>38098.42058239148</v>
+        <v>38193.09217207912</v>
       </c>
       <c r="E27">
         <v>-17029.275</v>
@@ -3507,37 +3507,37 @@
         <v>12076</v>
       </c>
       <c r="M27">
-        <v>768.2034727048723</v>
+        <v>752.9607977048723</v>
       </c>
       <c r="N27">
-        <v>11307.79652729513</v>
+        <v>11323.03920229513</v>
       </c>
       <c r="O27">
-        <v>3957.728784553295</v>
+        <v>3963.063720803294</v>
       </c>
       <c r="P27">
-        <v>7350.067742741833</v>
+        <v>7359.975481491832</v>
       </c>
       <c r="Q27">
-        <v>7866.567742741833</v>
+        <v>7876.475481491832</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1239890211491511</v>
+        <v>0.1239713745451327</v>
       </c>
       <c r="T27">
         <v>1.137488748554659</v>
       </c>
       <c r="U27">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V27">
         <v>0.35</v>
       </c>
       <c r="W27">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.7197935561004</v>
+        <v>16.03801955800262</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1042330540502956</v>
+        <v>0.1039832698614851</v>
       </c>
       <c r="C28">
-        <v>30249.53825061051</v>
+        <v>30348.43373610069</v>
       </c>
       <c r="D28">
-        <v>38190.96825061051</v>
+        <v>38289.8637361007</v>
       </c>
       <c r="E28">
         <v>-16593.77</v>
@@ -3589,37 +3589,37 @@
         <v>12076</v>
       </c>
       <c r="M28">
-        <v>798.9316116130673</v>
+        <v>783.0792296130672</v>
       </c>
       <c r="N28">
-        <v>11277.06838838693</v>
+        <v>11292.92077038693</v>
       </c>
       <c r="O28">
-        <v>3946.973935935426</v>
+        <v>3952.522269635426</v>
       </c>
       <c r="P28">
-        <v>7330.094452451507</v>
+        <v>7340.398500751506</v>
       </c>
       <c r="Q28">
-        <v>7846.594452451507</v>
+        <v>7856.898500751506</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1247416737037153</v>
+        <v>0.1247238572323498</v>
       </c>
       <c r="T28">
         <v>1.148438288525937</v>
       </c>
       <c r="U28">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.115186111635</v>
+        <v>15.4211726519256</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1040087504026256</v>
+        <v>0.1037499169780186</v>
       </c>
       <c r="C29">
-        <v>29907.03164237494</v>
+        <v>30010.19193477117</v>
       </c>
       <c r="D29">
-        <v>38283.96664237494</v>
+        <v>38387.12693477118</v>
       </c>
       <c r="E29">
         <v>-16158.265</v>
@@ -3671,37 +3671,37 @@
         <v>12076</v>
       </c>
       <c r="M29">
-        <v>829.6597505212621</v>
+        <v>813.1976615212621</v>
       </c>
       <c r="N29">
-        <v>11246.34024947874</v>
+        <v>11262.80233847874</v>
       </c>
       <c r="O29">
-        <v>3936.219087317558</v>
+        <v>3941.980818467558</v>
       </c>
       <c r="P29">
-        <v>7310.121162161179</v>
+        <v>7320.821520011179</v>
       </c>
       <c r="Q29">
-        <v>7826.621162161179</v>
+        <v>7837.321520011179</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1255149468762128</v>
+        <v>0.1254969558836003</v>
       </c>
       <c r="T29">
         <v>1.159687815893688</v>
       </c>
       <c r="U29">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.55536440379666</v>
+        <v>14.85001810926169</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1037844467549557</v>
+        <v>0.103516564094552</v>
       </c>
       <c r="C30">
-        <v>29564.97905837755</v>
+        <v>29672.44552415517</v>
       </c>
       <c r="D30">
-        <v>38377.41905837756</v>
+        <v>38484.88552415517</v>
       </c>
       <c r="E30">
         <v>-15722.76</v>
@@ -3753,37 +3753,37 @@
         <v>12076</v>
       </c>
       <c r="M30">
-        <v>860.387889429457</v>
+        <v>843.3160934294571</v>
       </c>
       <c r="N30">
-        <v>11215.61211057054</v>
+        <v>11232.68390657054</v>
       </c>
       <c r="O30">
-        <v>3925.46423869969</v>
+        <v>3931.43936729969</v>
       </c>
       <c r="P30">
-        <v>7290.147871870853</v>
+        <v>7301.244539270852</v>
       </c>
       <c r="Q30">
-        <v>7806.647871870853</v>
+        <v>7817.744539270852</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1263096998590574</v>
+        <v>0.1262915294973855</v>
       </c>
       <c r="T30">
         <v>1.171249830132765</v>
       </c>
       <c r="U30">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V30">
         <v>0.35</v>
       </c>
       <c r="W30">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.03552996080393</v>
+        <v>14.3196603196452</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1035601431072858</v>
+        <v>0.1032832112110854</v>
       </c>
       <c r="C31">
-        <v>29223.3838316184</v>
+        <v>29335.19829867653</v>
       </c>
       <c r="D31">
-        <v>38471.3288316184</v>
+        <v>38583.14329867653</v>
       </c>
       <c r="E31">
         <v>-15287.255</v>
@@ -3835,37 +3835,37 @@
         <v>12076</v>
       </c>
       <c r="M31">
-        <v>891.1160283376518</v>
+        <v>873.4345253376517</v>
       </c>
       <c r="N31">
-        <v>11184.88397166235</v>
+        <v>11202.56547466235</v>
       </c>
       <c r="O31">
-        <v>3914.709390081821</v>
+        <v>3920.897916131822</v>
       </c>
       <c r="P31">
-        <v>7270.174581580526</v>
+        <v>7281.667558530526</v>
       </c>
       <c r="Q31">
-        <v>7786.674581580526</v>
+        <v>7798.167558530526</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1271268402498694</v>
+        <v>0.1271084854664886</v>
       </c>
       <c r="T31">
         <v>1.183137534913789</v>
       </c>
       <c r="U31">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V31">
         <v>0.35</v>
       </c>
       <c r="W31">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.55154616905207</v>
+        <v>13.82587892931261</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1033358394596159</v>
+        <v>0.1030498583276188</v>
       </c>
       <c r="C32">
-        <v>28882.24932780105</v>
+        <v>28998.45409160922</v>
       </c>
       <c r="D32">
-        <v>38565.69932780106</v>
+        <v>38681.90409160922</v>
       </c>
       <c r="E32">
         <v>-14851.75</v>
@@ -3917,37 +3917,37 @@
         <v>12076</v>
       </c>
       <c r="M32">
-        <v>921.8441672458467</v>
+        <v>903.5529572458468</v>
       </c>
       <c r="N32">
-        <v>11154.15583275415</v>
+        <v>11172.44704275415</v>
       </c>
       <c r="O32">
-        <v>3903.954541463953</v>
+        <v>3910.356464963953</v>
       </c>
       <c r="P32">
-        <v>7250.2012912902</v>
+        <v>7262.090577790199</v>
       </c>
       <c r="Q32">
-        <v>7766.7012912902</v>
+        <v>7778.590577790199</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1279673275089905</v>
+        <v>0.1279487830347089</v>
       </c>
       <c r="T32">
         <v>1.195364888402841</v>
       </c>
       <c r="U32">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V32">
         <v>0.35</v>
       </c>
       <c r="W32">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.099827963417</v>
+        <v>13.36501629833552</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.103111535811946</v>
+        <v>0.1028165054441522</v>
       </c>
       <c r="C33">
-        <v>28541.57894573467</v>
+        <v>28662.21677557593</v>
       </c>
       <c r="D33">
-        <v>38660.53394573467</v>
+        <v>38781.17177557593</v>
       </c>
       <c r="E33">
         <v>-14416.245</v>
@@ -3999,37 +3999,37 @@
         <v>12076</v>
       </c>
       <c r="M33">
-        <v>952.5723061540417</v>
+        <v>933.6713891540417</v>
       </c>
       <c r="N33">
-        <v>11123.42769384596</v>
+        <v>11142.32861084596</v>
       </c>
       <c r="O33">
-        <v>3893.199692846085</v>
+        <v>3899.815013796085</v>
       </c>
       <c r="P33">
-        <v>7230.228000999874</v>
+        <v>7242.513597049872</v>
       </c>
       <c r="Q33">
-        <v>7746.728000999874</v>
+        <v>7759.013597049872</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1288321767176512</v>
+        <v>0.128813437054182</v>
       </c>
       <c r="T33">
         <v>1.207946657935055</v>
       </c>
       <c r="U33">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.6772528678229</v>
+        <v>12.9338867403247</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1028872321642761</v>
+        <v>0.1025831525606857</v>
       </c>
       <c r="C34">
-        <v>28201.37611774209</v>
+        <v>28326.49026305413</v>
       </c>
       <c r="D34">
-        <v>38755.83611774209</v>
+        <v>38880.95026305413</v>
       </c>
       <c r="E34">
         <v>-13980.74</v>
@@ -4081,37 +4081,37 @@
         <v>12076</v>
       </c>
       <c r="M34">
-        <v>983.3004450622365</v>
+        <v>963.7898210622366</v>
       </c>
       <c r="N34">
-        <v>11092.69955493776</v>
+        <v>11112.21017893776</v>
       </c>
       <c r="O34">
-        <v>3882.444844228217</v>
+        <v>3889.273562628217</v>
       </c>
       <c r="P34">
-        <v>7210.254710709547</v>
+        <v>7222.936616309546</v>
       </c>
       <c r="Q34">
-        <v>7726.754710709547</v>
+        <v>7739.436616309546</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1297224626677431</v>
+        <v>0.1297035220742278</v>
       </c>
       <c r="T34">
         <v>1.220898479512334</v>
       </c>
       <c r="U34">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V34">
         <v>0.35</v>
       </c>
       <c r="W34">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.28108871570344</v>
+        <v>12.52970277968955</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1026629285166062</v>
+        <v>0.1023497996772191</v>
       </c>
       <c r="C35">
-        <v>27861.64431007383</v>
+        <v>27991.27850689022</v>
       </c>
       <c r="D35">
-        <v>38851.60931007384</v>
+        <v>38981.24350689023</v>
       </c>
       <c r="E35">
         <v>-13545.235</v>
@@ -4163,37 +4163,37 @@
         <v>12076</v>
       </c>
       <c r="M35">
-        <v>1014.028583970431</v>
+        <v>993.9082529704315</v>
       </c>
       <c r="N35">
-        <v>11061.97141602957</v>
+        <v>11082.09174702957</v>
       </c>
       <c r="O35">
-        <v>3871.689995610348</v>
+        <v>3878.732111460349</v>
       </c>
       <c r="P35">
-        <v>7190.28142041922</v>
+        <v>7203.359635569219</v>
       </c>
       <c r="Q35">
-        <v>7706.78142041922</v>
+        <v>7719.859635569219</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1306393243178378</v>
+        <v>0.1306201767963646</v>
       </c>
       <c r="T35">
         <v>1.234236922629232</v>
       </c>
       <c r="U35">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V35">
         <v>0.35</v>
       </c>
       <c r="W35">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.90893451219727</v>
+        <v>12.15001481666866</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1024386248689363</v>
+        <v>0.1021164467937525</v>
       </c>
       <c r="C36">
-        <v>27522.38702332849</v>
+        <v>27656.58550082147</v>
       </c>
       <c r="D36">
-        <v>38947.8570233285</v>
+        <v>39082.05550082147</v>
       </c>
       <c r="E36">
         <v>-13109.73</v>
@@ -4245,37 +4245,37 @@
         <v>12076</v>
       </c>
       <c r="M36">
-        <v>1044.756722878627</v>
+        <v>1024.026684878626</v>
       </c>
       <c r="N36">
-        <v>11031.24327712137</v>
+        <v>11051.97331512137</v>
       </c>
       <c r="O36">
-        <v>3860.93514699248</v>
+        <v>3868.190660292481</v>
       </c>
       <c r="P36">
-        <v>7170.308130128893</v>
+        <v>7183.782654828892</v>
       </c>
       <c r="Q36">
-        <v>7686.808130128893</v>
+        <v>7700.282654828892</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.131583969654299</v>
+        <v>0.1315646089343236</v>
       </c>
       <c r="T36">
         <v>1.247979560992098</v>
       </c>
       <c r="U36">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V36">
         <v>0.35</v>
       </c>
       <c r="W36">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.55867173242676</v>
+        <v>11.79266143970781</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1022143212212663</v>
+        <v>0.101883093910286</v>
       </c>
       <c r="C37">
-        <v>27183.60779287912</v>
+        <v>27322.4152800061</v>
       </c>
       <c r="D37">
-        <v>39044.58279287913</v>
+        <v>39183.3902800061</v>
       </c>
       <c r="E37">
         <v>-12674.225</v>
@@ -4327,37 +4327,37 @@
         <v>12076</v>
       </c>
       <c r="M37">
-        <v>1075.484861786821</v>
+        <v>1054.145116786821</v>
       </c>
       <c r="N37">
-        <v>11000.51513821318</v>
+        <v>11021.85488321318</v>
       </c>
       <c r="O37">
-        <v>3850.180298374612</v>
+        <v>3857.649209124612</v>
       </c>
       <c r="P37">
-        <v>7150.334839838566</v>
+        <v>7164.205674088566</v>
       </c>
       <c r="Q37">
-        <v>7666.834839838566</v>
+        <v>7680.705674088566</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1325576810011128</v>
+        <v>0.1325381005226815</v>
       </c>
       <c r="T37">
         <v>1.262145049766129</v>
       </c>
       <c r="U37">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.22842396864314</v>
+        <v>11.45572825571616</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1019900175735964</v>
+        <v>0.1016497410268194</v>
       </c>
       <c r="C38">
-        <v>26845.31018930613</v>
+        <v>26988.77192156178</v>
       </c>
       <c r="D38">
-        <v>39141.79018930614</v>
+        <v>39285.25192156179</v>
       </c>
       <c r="E38">
         <v>-12238.72</v>
@@ -4409,37 +4409,37 @@
         <v>12076</v>
       </c>
       <c r="M38">
-        <v>1106.213000695016</v>
+        <v>1084.263548695016</v>
       </c>
       <c r="N38">
-        <v>10969.78699930498</v>
+        <v>10991.73645130498</v>
       </c>
       <c r="O38">
-        <v>3839.425449756744</v>
+        <v>3847.107757956744</v>
       </c>
       <c r="P38">
-        <v>7130.36154954824</v>
+        <v>7144.628693348239</v>
       </c>
       <c r="Q38">
-        <v>7646.86154954824</v>
+        <v>7661.128693348239</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1335618208275146</v>
+        <v>0.1335420137231755</v>
       </c>
       <c r="T38">
         <v>1.276753210064348</v>
       </c>
       <c r="U38">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V38">
         <v>0.35</v>
       </c>
       <c r="W38">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.9165233028475</v>
+        <v>11.13751358194627</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1017657139259265</v>
+        <v>0.1014163881433528</v>
       </c>
       <c r="C39">
-        <v>26507.49781883673</v>
+        <v>26655.65954511239</v>
       </c>
       <c r="D39">
-        <v>39239.48281883673</v>
+        <v>39387.64454511239</v>
       </c>
       <c r="E39">
         <v>-11803.215</v>
@@ -4491,37 +4491,37 @@
         <v>12076</v>
       </c>
       <c r="M39">
-        <v>1136.941139603211</v>
+        <v>1114.381980603211</v>
       </c>
       <c r="N39">
-        <v>10939.05886039679</v>
+        <v>10961.61801939679</v>
       </c>
       <c r="O39">
-        <v>3828.670601138876</v>
+        <v>3836.566306788876</v>
       </c>
       <c r="P39">
-        <v>7110.388259257912</v>
+        <v>7125.051712607912</v>
       </c>
       <c r="Q39">
-        <v>7626.888259257912</v>
+        <v>7641.551712607912</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1345978381087228</v>
+        <v>0.1345777971840026</v>
       </c>
       <c r="T39">
         <v>1.291825121483145</v>
       </c>
       <c r="U39">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V39">
         <v>0.35</v>
       </c>
       <c r="W39">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.62148213250027</v>
+        <v>10.83649970135312</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1015414102782566</v>
+        <v>0.1011830352598863</v>
       </c>
       <c r="C40">
-        <v>26170.17432379082</v>
+        <v>26323.08231334337</v>
       </c>
       <c r="D40">
-        <v>39337.66432379082</v>
+        <v>39490.57231334337</v>
       </c>
       <c r="E40">
         <v>-11367.71</v>
@@ -4573,37 +4573,37 @@
         <v>12076</v>
       </c>
       <c r="M40">
-        <v>1167.669278511406</v>
+        <v>1144.500412511406</v>
       </c>
       <c r="N40">
-        <v>10908.33072148859</v>
+        <v>10931.49958748859</v>
       </c>
       <c r="O40">
-        <v>3817.915752521008</v>
+        <v>3826.024855621008</v>
       </c>
       <c r="P40">
-        <v>7090.414968967586</v>
+        <v>7105.474731867585</v>
       </c>
       <c r="Q40">
-        <v>7606.914968967586</v>
+        <v>7621.974731867585</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.135667275302228</v>
+        <v>0.1356469930145339</v>
       </c>
       <c r="T40">
         <v>1.307383223592872</v>
       </c>
       <c r="U40">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V40">
         <v>0.35</v>
       </c>
       <c r="W40">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.34196944480289</v>
+        <v>10.55132865658067</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1013171066305867</v>
+        <v>0.1009496823764197</v>
       </c>
       <c r="C41">
-        <v>25833.34338303369</v>
+        <v>25991.04443256588</v>
       </c>
       <c r="D41">
-        <v>39436.33838303369</v>
+        <v>39594.03943256589</v>
       </c>
       <c r="E41">
         <v>-10932.205</v>
@@ -4655,37 +4655,37 @@
         <v>12076</v>
       </c>
       <c r="M41">
-        <v>1198.397417419601</v>
+        <v>1174.618844419601</v>
       </c>
       <c r="N41">
-        <v>10877.6025825804</v>
+        <v>10901.3811555804</v>
       </c>
       <c r="O41">
-        <v>3807.16090390314</v>
+        <v>3815.483404453139</v>
       </c>
       <c r="P41">
-        <v>7070.44167867726</v>
+        <v>7085.897751127259</v>
       </c>
       <c r="Q41">
-        <v>7586.94167867726</v>
+        <v>7602.397751127259</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1367717760102743</v>
+        <v>0.1367512444460661</v>
       </c>
       <c r="T41">
         <v>1.323451427411114</v>
       </c>
       <c r="U41">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V41">
         <v>0.35</v>
       </c>
       <c r="W41">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.07679074109</v>
+        <v>10.2807817679504</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1010928029829168</v>
+        <v>0.1007163294929531</v>
       </c>
       <c r="C42">
-        <v>25497.00871243547</v>
+        <v>25659.55015328985</v>
       </c>
       <c r="D42">
-        <v>39535.50871243548</v>
+        <v>39698.05015328985</v>
       </c>
       <c r="E42">
         <v>-10496.7</v>
@@ -4737,37 +4737,37 @@
         <v>12076</v>
       </c>
       <c r="M42">
-        <v>1229.125556327796</v>
+        <v>1204.737276327796</v>
       </c>
       <c r="N42">
-        <v>10846.8744436722</v>
+        <v>10871.2627236722</v>
       </c>
       <c r="O42">
-        <v>3796.406055285271</v>
+        <v>3804.941953285271</v>
       </c>
       <c r="P42">
-        <v>7050.468388386933</v>
+        <v>7066.320770386932</v>
       </c>
       <c r="Q42">
-        <v>7566.968388386933</v>
+        <v>7582.820770386932</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1379130934085889</v>
+        <v>0.1378923042586495</v>
       </c>
       <c r="T42">
         <v>1.340055238023297</v>
       </c>
       <c r="U42">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>9.824870972562749</v>
+        <v>10.02376222375164</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1008684993352469</v>
+        <v>0.1004829766094866</v>
       </c>
       <c r="C43">
-        <v>25161.17406533769</v>
+        <v>25328.60377080587</v>
       </c>
       <c r="D43">
-        <v>39635.1790653377</v>
+        <v>39802.60877080588</v>
       </c>
       <c r="E43">
         <v>-10061.195</v>
@@ -4819,37 +4819,37 @@
         <v>12076</v>
       </c>
       <c r="M43">
-        <v>1259.853695235991</v>
+        <v>1234.855708235991</v>
       </c>
       <c r="N43">
-        <v>10816.14630476401</v>
+        <v>10841.14429176401</v>
       </c>
       <c r="O43">
-        <v>3785.651206667403</v>
+        <v>3794.400502117403</v>
       </c>
       <c r="P43">
-        <v>7030.495098096607</v>
+        <v>7046.743789646605</v>
       </c>
       <c r="Q43">
-        <v>7546.995098096607</v>
+        <v>7563.243789646605</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1390930995322701</v>
+        <v>0.1390720440648797</v>
       </c>
       <c r="T43">
         <v>1.357221889673182</v>
       </c>
       <c r="U43">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V43">
         <v>0.35</v>
       </c>
       <c r="W43">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.58523997323195</v>
+        <v>9.779280218294282</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.100644195687577</v>
+        <v>0.10024962372602</v>
       </c>
       <c r="C44">
-        <v>24825.84323302672</v>
+        <v>24998.20962577676</v>
       </c>
       <c r="D44">
-        <v>39735.35323302672</v>
+        <v>39907.71962577676</v>
       </c>
       <c r="E44">
         <v>-9625.690000000002</v>
@@ -4901,37 +4901,37 @@
         <v>12076</v>
       </c>
       <c r="M44">
-        <v>1290.581834144185</v>
+        <v>1264.974140144185</v>
       </c>
       <c r="N44">
-        <v>10785.41816585582</v>
+        <v>10811.02585985581</v>
       </c>
       <c r="O44">
-        <v>3774.896358049535</v>
+        <v>3783.859050949535</v>
       </c>
       <c r="P44">
-        <v>7010.521807806281</v>
+        <v>7027.166808906279</v>
       </c>
       <c r="Q44">
-        <v>7527.021807806281</v>
+        <v>7543.666808906279</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1403137955222851</v>
+        <v>0.1402924645540834</v>
       </c>
       <c r="T44">
         <v>1.374980494828235</v>
       </c>
       <c r="U44">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V44">
         <v>0.35</v>
       </c>
       <c r="W44">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.357019973869285</v>
+        <v>9.546440213096801</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1004198920399071</v>
+        <v>0.1000162708425534</v>
       </c>
       <c r="C45">
-        <v>24491.02004521449</v>
+        <v>24668.37210483796</v>
       </c>
       <c r="D45">
-        <v>39836.03504521449</v>
+        <v>40013.38710483796</v>
       </c>
       <c r="E45">
         <v>-9190.185000000001</v>
@@ -4983,37 +4983,37 @@
         <v>12076</v>
       </c>
       <c r="M45">
-        <v>1321.30997305238</v>
+        <v>1295.09257205238</v>
       </c>
       <c r="N45">
-        <v>10754.69002694762</v>
+        <v>10780.90742794762</v>
       </c>
       <c r="O45">
-        <v>3764.141509431666</v>
+        <v>3773.317599781667</v>
       </c>
       <c r="P45">
-        <v>6990.548517515953</v>
+        <v>7007.589828165952</v>
       </c>
       <c r="Q45">
-        <v>7507.048517515953</v>
+        <v>7524.089828165952</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1415773229505463</v>
+        <v>0.1415557068148381</v>
       </c>
       <c r="T45">
         <v>1.393362208936097</v>
       </c>
       <c r="U45">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V45">
         <v>0.35</v>
       </c>
       <c r="W45">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.139414858197906</v>
+        <v>9.324429975582921</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1001955883922372</v>
+        <v>0.09978291795908686</v>
       </c>
       <c r="C46">
-        <v>24156.7083705266</v>
+        <v>24339.09564120796</v>
       </c>
       <c r="D46">
-        <v>39937.22837052661</v>
+        <v>40119.61564120797</v>
       </c>
       <c r="E46">
         <v>-8754.68</v>
@@ -5065,37 +5065,37 @@
         <v>12076</v>
       </c>
       <c r="M46">
-        <v>1352.038111960575</v>
+        <v>1325.211003960575</v>
       </c>
       <c r="N46">
-        <v>10723.96188803942</v>
+        <v>10750.78899603942</v>
       </c>
       <c r="O46">
-        <v>3753.386660813798</v>
+        <v>3762.776148613798</v>
       </c>
       <c r="P46">
-        <v>6970.575227225627</v>
+        <v>6988.012847425625</v>
       </c>
       <c r="Q46">
-        <v>7487.075227225627</v>
+        <v>7504.512847425625</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1428859763583882</v>
+        <v>0.1428640648706197</v>
       </c>
       <c r="T46">
         <v>1.412400412833525</v>
       </c>
       <c r="U46">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V46">
         <v>0.35</v>
       </c>
       <c r="W46">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.931700884147952</v>
+        <v>9.11251111250149</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09997128474456726</v>
+        <v>0.09954956507562029</v>
       </c>
       <c r="C47">
-        <v>23822.91211699781</v>
+        <v>24010.38471530824</v>
       </c>
       <c r="D47">
-        <v>40038.93711699781</v>
+        <v>40226.40971530825</v>
       </c>
       <c r="E47">
         <v>-8319.174999999999</v>
@@ -5147,37 +5147,37 @@
         <v>12076</v>
       </c>
       <c r="M47">
-        <v>1382.76625086877</v>
+        <v>1355.32943586877</v>
       </c>
       <c r="N47">
-        <v>10693.23374913123</v>
+        <v>10720.67056413123</v>
       </c>
       <c r="O47">
-        <v>3742.63181219593</v>
+        <v>3752.23469744593</v>
       </c>
       <c r="P47">
-        <v>6950.6019369353</v>
+        <v>6968.435866685299</v>
       </c>
       <c r="Q47">
-        <v>7467.1019369353</v>
+        <v>7484.935866685299</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1442422171628789</v>
+        <v>0.1442199995829753</v>
       </c>
       <c r="T47">
         <v>1.432130915054496</v>
       </c>
       <c r="U47">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04586236734440863</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.733218642278</v>
+        <v>8.910010865557012</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1000758810968974</v>
+        <v>0.09931621219215372</v>
       </c>
       <c r="C48">
-        <v>23339.91432817212</v>
+        <v>23682.24385539319</v>
       </c>
       <c r="D48">
-        <v>39991.44432817213</v>
+        <v>40333.77385539319</v>
       </c>
       <c r="E48">
         <v>-7883.670000000002</v>
@@ -5229,45 +5229,45 @@
         <v>12076</v>
       </c>
       <c r="M48">
-        <v>1435.530942776965</v>
+        <v>1385.447867776965</v>
       </c>
       <c r="N48">
-        <v>10640.46905722304</v>
+        <v>10690.55213222303</v>
       </c>
       <c r="O48">
-        <v>3724.164170028062</v>
+        <v>3741.693246278062</v>
       </c>
       <c r="P48">
-        <v>6916.304887194974</v>
+        <v>6948.858885944972</v>
       </c>
       <c r="Q48">
-        <v>7432.804887194974</v>
+        <v>7465.358885944972</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1456486891082766</v>
+        <v>0.1456261540994921</v>
       </c>
       <c r="T48">
         <v>1.452592176616985</v>
       </c>
       <c r="U48">
-        <v>0.07165748822216711</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V48">
         <v>0.35</v>
       </c>
       <c r="W48">
-        <v>0.04657736734440862</v>
+        <v>0.04495236734440863</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y48">
-        <v>8.412218531938827</v>
+        <v>8.71631497717534</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09985872744922744</v>
+        <v>0.09954110930868713</v>
       </c>
       <c r="C49">
-        <v>23003.13580264226</v>
+        <v>23143.25517689351</v>
       </c>
       <c r="D49">
-        <v>40090.17080264226</v>
+        <v>40230.29017689351</v>
       </c>
       <c r="E49">
         <v>-7448.165000000001</v>
@@ -5311,37 +5311,37 @@
         <v>12076</v>
       </c>
       <c r="M49">
-        <v>1466.73813718516</v>
+        <v>1446.26940218516</v>
       </c>
       <c r="N49">
-        <v>10609.26186281484</v>
+        <v>10629.73059781484</v>
       </c>
       <c r="O49">
-        <v>3713.241651985194</v>
+        <v>3720.405709235194</v>
       </c>
       <c r="P49">
-        <v>6896.020210829647</v>
+        <v>6909.324888579646</v>
       </c>
       <c r="Q49">
-        <v>7412.520210829647</v>
+        <v>7425.824888579646</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1471082354667083</v>
+        <v>0.1470853710505945</v>
       </c>
       <c r="T49">
         <v>1.473825561257303</v>
       </c>
       <c r="U49">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V49">
         <v>0.35</v>
       </c>
       <c r="W49">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.233235158918852</v>
+        <v>8.349758338076187</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09964157380155753</v>
+        <v>0.09931750642522058</v>
       </c>
       <c r="C50">
-        <v>22666.84593355326</v>
+        <v>22810.63680673393</v>
       </c>
       <c r="D50">
-        <v>40189.38593355326</v>
+        <v>40333.17680673393</v>
       </c>
       <c r="E50">
         <v>-7012.660000000003</v>
@@ -5393,37 +5393,37 @@
         <v>12076</v>
       </c>
       <c r="M50">
-        <v>1497.945331593354</v>
+        <v>1477.041091593354</v>
       </c>
       <c r="N50">
-        <v>10578.05466840664</v>
+        <v>10598.95890840665</v>
       </c>
       <c r="O50">
-        <v>3702.319133942326</v>
+        <v>3709.635617942326</v>
       </c>
       <c r="P50">
-        <v>6875.735534464319</v>
+        <v>6889.323290464321</v>
       </c>
       <c r="Q50">
-        <v>7392.235534464319</v>
+        <v>7405.823290464321</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1486239182235411</v>
+        <v>0.1486007117305854</v>
       </c>
       <c r="T50">
         <v>1.495875614537634</v>
       </c>
       <c r="U50">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V50">
         <v>0.35</v>
       </c>
       <c r="W50">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.061709426441377</v>
+        <v>8.175805039366267</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09942442015388761</v>
+        <v>0.09909390354175399</v>
       </c>
       <c r="C51">
-        <v>22331.04835788592</v>
+        <v>22478.5460390437</v>
       </c>
       <c r="D51">
-        <v>40289.09335788593</v>
+        <v>40436.59103904371</v>
       </c>
       <c r="E51">
         <v>-6577.155000000002</v>
@@ -5475,37 +5475,37 @@
         <v>12076</v>
       </c>
       <c r="M51">
-        <v>1529.152526001549</v>
+        <v>1507.812781001549</v>
       </c>
       <c r="N51">
-        <v>10546.84747399845</v>
+        <v>10568.18721899845</v>
       </c>
       <c r="O51">
-        <v>3691.396615899457</v>
+        <v>3698.865526649457</v>
       </c>
       <c r="P51">
-        <v>6855.450858098993</v>
+        <v>6869.321692348993</v>
       </c>
       <c r="Q51">
-        <v>7371.950858098993</v>
+        <v>7385.821692348993</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1501990395198576</v>
+        <v>0.1501754775352819</v>
       </c>
       <c r="T51">
         <v>1.518790375789742</v>
       </c>
       <c r="U51">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V51">
         <v>0.35</v>
       </c>
       <c r="W51">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.897184744269103</v>
+        <v>8.008951875297567</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0992072665062177</v>
+        <v>0.09887030065828742</v>
       </c>
       <c r="C52">
-        <v>21995.74674880334</v>
+        <v>22146.98694257199</v>
       </c>
       <c r="D52">
-        <v>40389.29674880334</v>
+        <v>40540.53694257199</v>
       </c>
       <c r="E52">
         <v>-6141.650000000001</v>
@@ -5557,37 +5557,37 @@
         <v>12076</v>
       </c>
       <c r="M52">
-        <v>1560.359720409744</v>
+        <v>1538.584470409744</v>
       </c>
       <c r="N52">
-        <v>10515.64027959026</v>
+        <v>10537.41552959026</v>
       </c>
       <c r="O52">
-        <v>3680.474097856589</v>
+        <v>3688.095435356589</v>
       </c>
       <c r="P52">
-        <v>6835.166181733666</v>
+        <v>6849.320094233667</v>
       </c>
       <c r="Q52">
-        <v>7351.666181733666</v>
+        <v>7365.820094233667</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1518371656680268</v>
+        <v>0.1518132339721662</v>
       </c>
       <c r="T52">
         <v>1.542621727491935</v>
       </c>
       <c r="U52">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V52">
         <v>0.35</v>
       </c>
       <c r="W52">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.739241049383722</v>
+        <v>7.848772837791616</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09899011285854778</v>
+        <v>0.09864669777482085</v>
       </c>
       <c r="C53">
-        <v>21660.94481610194</v>
+        <v>21815.96362801212</v>
       </c>
       <c r="D53">
-        <v>40489.99981610195</v>
+        <v>40645.01862801213</v>
       </c>
       <c r="E53">
         <v>-5706.145</v>
@@ -5639,37 +5639,37 @@
         <v>12076</v>
       </c>
       <c r="M53">
-        <v>1591.566914817939</v>
+        <v>1569.356159817939</v>
       </c>
       <c r="N53">
-        <v>10484.43308518206</v>
+        <v>10506.64384018206</v>
       </c>
       <c r="O53">
-        <v>3669.551579813721</v>
+        <v>3677.325344063721</v>
       </c>
       <c r="P53">
-        <v>6814.88150536834</v>
+        <v>6829.31849611834</v>
       </c>
       <c r="Q53">
-        <v>7331.38150536834</v>
+        <v>7345.81849611834</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1535421541079579</v>
+        <v>0.153517837610556</v>
       </c>
       <c r="T53">
         <v>1.56742578742687</v>
       </c>
       <c r="U53">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V53">
         <v>0.35</v>
       </c>
       <c r="W53">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.587491224886001</v>
+        <v>7.694875331168252</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09877295921087788</v>
+        <v>0.0984230948913543</v>
       </c>
       <c r="C54">
-        <v>21326.64630666935</v>
+        <v>21485.48024854348</v>
       </c>
       <c r="D54">
-        <v>40591.20630666935</v>
+        <v>40750.04024854349</v>
       </c>
       <c r="E54">
         <v>-5270.639999999999</v>
@@ -5721,37 +5721,37 @@
         <v>12076</v>
       </c>
       <c r="M54">
-        <v>1622.774109226134</v>
+        <v>1600.127849226134</v>
       </c>
       <c r="N54">
-        <v>10453.22589077387</v>
+        <v>10475.87215077387</v>
       </c>
       <c r="O54">
-        <v>3658.629061770852</v>
+        <v>3666.555252770853</v>
       </c>
       <c r="P54">
-        <v>6794.596829003012</v>
+        <v>6809.316898003013</v>
       </c>
       <c r="Q54">
-        <v>7311.096829003012</v>
+        <v>7325.816898003013</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1553181837328863</v>
+        <v>0.1552934664005454</v>
       </c>
       <c r="T54">
         <v>1.593263349859095</v>
       </c>
       <c r="U54">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V54">
         <v>0.35</v>
       </c>
       <c r="W54">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.441577932099731</v>
+        <v>7.546896959415015</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09855580556320798</v>
+        <v>0.09819949200788772</v>
       </c>
       <c r="C55">
-        <v>20992.85500494907</v>
+        <v>21155.54100038188</v>
       </c>
       <c r="D55">
-        <v>40692.92000494908</v>
+        <v>40855.60600038189</v>
       </c>
       <c r="E55">
         <v>-4835.135000000002</v>
@@ -5803,37 +5803,37 @@
         <v>12076</v>
       </c>
       <c r="M55">
-        <v>1653.981303634329</v>
+        <v>1630.899538634329</v>
       </c>
       <c r="N55">
-        <v>10422.01869636567</v>
+        <v>10445.10046136567</v>
       </c>
       <c r="O55">
-        <v>3647.706543727984</v>
+        <v>3655.785161477985</v>
       </c>
       <c r="P55">
-        <v>6774.312152637686</v>
+        <v>6789.315299887687</v>
       </c>
       <c r="Q55">
-        <v>7290.812152637686</v>
+        <v>7305.815299887687</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1571697890865349</v>
+        <v>0.1571446538624493</v>
       </c>
       <c r="T55">
         <v>1.620200383033116</v>
       </c>
       <c r="U55">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V55">
         <v>0.35</v>
       </c>
       <c r="W55">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.301170801305398</v>
+        <v>7.404502677161902</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09833865191553808</v>
+        <v>0.09797588912442116</v>
       </c>
       <c r="C56">
-        <v>20659.57473341225</v>
+        <v>20826.15012333832</v>
       </c>
       <c r="D56">
-        <v>40795.14473341225</v>
+        <v>40961.72012333832</v>
       </c>
       <c r="E56">
         <v>-4399.630000000001</v>
@@ -5885,37 +5885,37 @@
         <v>12076</v>
       </c>
       <c r="M56">
-        <v>1685.188498042524</v>
+        <v>1661.671228042524</v>
       </c>
       <c r="N56">
-        <v>10390.81150195748</v>
+        <v>10414.32877195748</v>
       </c>
       <c r="O56">
-        <v>3636.784025685116</v>
+        <v>3645.015070185117</v>
       </c>
       <c r="P56">
-        <v>6754.02747627236</v>
+        <v>6769.31370177236</v>
       </c>
       <c r="Q56">
-        <v>7270.52747627236</v>
+        <v>7285.81370177236</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.159101899020777</v>
+        <v>0.1590763277357402</v>
       </c>
       <c r="T56">
         <v>1.648308591562529</v>
       </c>
       <c r="U56">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V56">
         <v>0.35</v>
       </c>
       <c r="W56">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.165963934614557</v>
+        <v>7.26738225721446</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09812149826786816</v>
+        <v>0.09775228624095458</v>
       </c>
       <c r="C57">
-        <v>20326.80935303648</v>
+        <v>20497.31190138675</v>
       </c>
       <c r="D57">
-        <v>40897.88435303648</v>
+        <v>41068.38690138676</v>
       </c>
       <c r="E57">
         <v>-3964.125</v>
@@ -5967,37 +5967,37 @@
         <v>12076</v>
       </c>
       <c r="M57">
-        <v>1716.395692450719</v>
+        <v>1692.442917450719</v>
       </c>
       <c r="N57">
-        <v>10359.60430754928</v>
+        <v>10383.55708254928</v>
       </c>
       <c r="O57">
-        <v>3625.861507642248</v>
+        <v>3634.244978892248</v>
       </c>
       <c r="P57">
-        <v>6733.742799907033</v>
+        <v>6749.312103657034</v>
       </c>
       <c r="Q57">
-        <v>7250.242799907033</v>
+        <v>7265.812103657034</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1611198805076521</v>
+        <v>0.1610938537811774</v>
       </c>
       <c r="T57">
         <v>1.677666053804361</v>
       </c>
       <c r="U57">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V57">
         <v>0.35</v>
       </c>
       <c r="W57">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.035673681257928</v>
+        <v>7.135248034356015</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09790434462019823</v>
+        <v>0.09752868335748802</v>
       </c>
       <c r="C58">
-        <v>19994.56276379193</v>
+        <v>20169.03066324048</v>
       </c>
       <c r="D58">
-        <v>41001.14276379193</v>
+        <v>41175.61066324048</v>
       </c>
       <c r="E58">
         <v>-3528.619999999999</v>
@@ -6049,37 +6049,37 @@
         <v>12076</v>
       </c>
       <c r="M58">
-        <v>1747.602886858914</v>
+        <v>1723.214606858914</v>
       </c>
       <c r="N58">
-        <v>10328.39711314109</v>
+        <v>10352.78539314109</v>
       </c>
       <c r="O58">
-        <v>3614.93898959938</v>
+        <v>3623.47488759938</v>
       </c>
       <c r="P58">
-        <v>6713.458123541706</v>
+        <v>6729.310505541706</v>
       </c>
       <c r="Q58">
-        <v>7229.958123541706</v>
+        <v>7245.810505541706</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1632295884257487</v>
+        <v>0.1632030855559527</v>
       </c>
       <c r="T58">
         <v>1.708357946148093</v>
       </c>
       <c r="U58">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V58">
         <v>0.35</v>
       </c>
       <c r="W58">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.910036651235464</v>
+        <v>7.007832890885371</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09768719097252833</v>
+        <v>0.09730508047402145</v>
       </c>
       <c r="C59">
-        <v>19662.83890513482</v>
+        <v>19841.31078293784</v>
       </c>
       <c r="D59">
-        <v>41104.92390513483</v>
+        <v>41283.39578293784</v>
       </c>
       <c r="E59">
         <v>-3093.114999999998</v>
@@ -6131,37 +6131,37 @@
         <v>12076</v>
       </c>
       <c r="M59">
-        <v>1778.810081267109</v>
+        <v>1753.986296267109</v>
       </c>
       <c r="N59">
-        <v>10297.18991873289</v>
+        <v>10322.01370373289</v>
       </c>
       <c r="O59">
-        <v>3604.016471556512</v>
+        <v>3612.704796306512</v>
       </c>
       <c r="P59">
-        <v>6693.173447176379</v>
+        <v>6709.30890742638</v>
       </c>
       <c r="Q59">
-        <v>7209.673447176379</v>
+        <v>7225.80890742638</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1654374222935242</v>
+        <v>0.1654104211342059</v>
       </c>
       <c r="T59">
         <v>1.740477368368279</v>
       </c>
       <c r="U59">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V59">
         <v>0.35</v>
       </c>
       <c r="W59">
-        <v>0.04657736734440862</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.788807938055895</v>
+        <v>6.884888454203171</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09829943732485844</v>
+        <v>0.09708147759055488</v>
       </c>
       <c r="C60">
-        <v>18936.06971171594</v>
+        <v>19514.15668043688</v>
       </c>
       <c r="D60">
-        <v>40813.65971171594</v>
+        <v>41391.74668043688</v>
       </c>
       <c r="E60">
         <v>-2657.610000000004</v>
@@ -6213,45 +6213,45 @@
         <v>12076</v>
       </c>
       <c r="M60">
-        <v>1865.587713675303</v>
+        <v>1784.757985675303</v>
       </c>
       <c r="N60">
-        <v>10210.4122863247</v>
+        <v>10291.2420143247</v>
       </c>
       <c r="O60">
-        <v>3573.644300213643</v>
+        <v>3601.934705013643</v>
       </c>
       <c r="P60">
-        <v>6636.767986111052</v>
+        <v>6689.307309311052</v>
       </c>
       <c r="Q60">
-        <v>7153.267986111052</v>
+        <v>7205.807309311052</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1677503911073844</v>
+        <v>0.1677228679304711</v>
       </c>
       <c r="T60">
         <v>1.774126286884664</v>
       </c>
       <c r="U60">
-        <v>0.07385748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.04800736734440863</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y60">
-        <v>6.473027192170804</v>
+        <v>6.766183480854842</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.09809658367718851</v>
+        <v>0.0975098247070883</v>
       </c>
       <c r="C61">
-        <v>18596.61003277657</v>
+        <v>18871.58451485472</v>
       </c>
       <c r="D61">
-        <v>40909.70503277658</v>
+        <v>41184.67951485472</v>
       </c>
       <c r="E61">
         <v>-2222.105000000003</v>
@@ -6295,37 +6295,37 @@
         <v>12076</v>
       </c>
       <c r="M61">
-        <v>1897.753019083498</v>
+        <v>1859.210826583498</v>
       </c>
       <c r="N61">
-        <v>10178.2469809165</v>
+        <v>10216.7891734165</v>
       </c>
       <c r="O61">
-        <v>3562.386443320775</v>
+        <v>3575.876210695776</v>
       </c>
       <c r="P61">
-        <v>6615.860537595726</v>
+        <v>6640.912962720727</v>
       </c>
       <c r="Q61">
-        <v>7132.360537595726</v>
+        <v>7157.412962720727</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.170176187668262</v>
+        <v>0.170148117009481</v>
       </c>
       <c r="T61">
         <v>1.809416616060385</v>
       </c>
       <c r="U61">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V61">
         <v>0.35</v>
       </c>
       <c r="W61">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.363314866879773</v>
+        <v>6.495228958079467</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09789373002951861</v>
+        <v>0.09729727182362174</v>
       </c>
       <c r="C62">
-        <v>18257.60346013213</v>
+        <v>18538.57004850842</v>
       </c>
       <c r="D62">
-        <v>41006.20346013213</v>
+        <v>41287.17004850842</v>
       </c>
       <c r="E62">
         <v>-1786.600000000002</v>
@@ -6377,37 +6377,37 @@
         <v>12076</v>
       </c>
       <c r="M62">
-        <v>1929.918324491693</v>
+        <v>1890.722874491693</v>
       </c>
       <c r="N62">
-        <v>10146.08167550831</v>
+        <v>10185.27712550831</v>
       </c>
       <c r="O62">
-        <v>3551.128586427907</v>
+        <v>3564.846993927907</v>
       </c>
       <c r="P62">
-        <v>6594.9530890804</v>
+        <v>6620.430131580399</v>
       </c>
       <c r="Q62">
-        <v>7111.4530890804</v>
+        <v>7136.930131580399</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1727232740571836</v>
+        <v>0.1726946285424414</v>
       </c>
       <c r="T62">
         <v>1.846471461694892</v>
       </c>
       <c r="U62">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V62">
         <v>0.35</v>
       </c>
       <c r="W62">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.257259619098444</v>
+        <v>6.386975142111475</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.0976908763818487</v>
+        <v>0.09708471894015518</v>
       </c>
       <c r="C63">
-        <v>17919.05320774558</v>
+        <v>18206.06696238547</v>
       </c>
       <c r="D63">
-        <v>41103.15820774558</v>
+        <v>41390.17196238547</v>
       </c>
       <c r="E63">
         <v>-1351.095000000001</v>
@@ -6459,37 +6459,37 @@
         <v>12076</v>
       </c>
       <c r="M63">
-        <v>1962.083629899888</v>
+        <v>1922.234922399888</v>
       </c>
       <c r="N63">
-        <v>10113.91637010011</v>
+        <v>10153.76507760011</v>
       </c>
       <c r="O63">
-        <v>3539.870729535039</v>
+        <v>3553.817777160039</v>
       </c>
       <c r="P63">
-        <v>6574.045640565073</v>
+        <v>6599.947300440073</v>
       </c>
       <c r="Q63">
-        <v>7090.545640565073</v>
+        <v>7116.447300440073</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1754009802609216</v>
+        <v>0.1753717304104254</v>
       </c>
       <c r="T63">
         <v>1.885426555823476</v>
       </c>
       <c r="U63">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V63">
         <v>0.35</v>
       </c>
       <c r="W63">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.154681592555846</v>
+        <v>6.282270631585058</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09748802273417879</v>
+        <v>0.09687216605668861</v>
       </c>
       <c r="C64">
-        <v>17580.96252004824</v>
+        <v>17874.07909338323</v>
       </c>
       <c r="D64">
-        <v>41200.57252004824</v>
+        <v>41493.68909338323</v>
       </c>
       <c r="E64">
         <v>-915.5900000000001</v>
@@ -6541,37 +6541,37 @@
         <v>12076</v>
       </c>
       <c r="M64">
-        <v>1994.248935308083</v>
+        <v>1953.746970308083</v>
       </c>
       <c r="N64">
-        <v>10081.75106469192</v>
+        <v>10122.25302969192</v>
       </c>
       <c r="O64">
-        <v>3528.612872642171</v>
+        <v>3542.788560392171</v>
       </c>
       <c r="P64">
-        <v>6553.138192049746</v>
+        <v>6579.464469299746</v>
       </c>
       <c r="Q64">
-        <v>7069.638192049746</v>
+        <v>7095.964469299746</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1782196183701196</v>
+        <v>0.1781897323767244</v>
       </c>
       <c r="T64">
         <v>1.926431918064091</v>
       </c>
       <c r="U64">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V64">
         <v>0.35</v>
       </c>
       <c r="W64">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.055412534611397</v>
+        <v>6.180943685914331</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09728516908650889</v>
+        <v>0.09665961317322204</v>
       </c>
       <c r="C65">
-        <v>17243.33467230159</v>
+        <v>17542.61031687971</v>
       </c>
       <c r="D65">
-        <v>41298.44967230159</v>
+        <v>41597.72531687971</v>
       </c>
       <c r="E65">
         <v>-480.0850000000028</v>
@@ -6623,37 +6623,37 @@
         <v>12076</v>
       </c>
       <c r="M65">
-        <v>2026.414240716278</v>
+        <v>1985.259018216278</v>
       </c>
       <c r="N65">
-        <v>10049.58575928372</v>
+        <v>10090.74098178372</v>
       </c>
       <c r="O65">
-        <v>3517.355015749302</v>
+        <v>3531.759343624302</v>
       </c>
       <c r="P65">
-        <v>6532.230743534419</v>
+        <v>6558.981638159419</v>
       </c>
       <c r="Q65">
-        <v>7048.730743534419</v>
+        <v>7075.481638159419</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1811906152960309</v>
+        <v>0.1811600587736341</v>
       </c>
       <c r="T65">
         <v>1.969653786371766</v>
       </c>
       <c r="U65">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V65">
         <v>0.35</v>
       </c>
       <c r="W65">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.959294875331851</v>
+        <v>6.082833468677595</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09708231543883897</v>
+        <v>0.09644706028975547</v>
       </c>
       <c r="C66">
-        <v>16906.17297096444</v>
+        <v>17211.6645472172</v>
       </c>
       <c r="D66">
-        <v>41396.79297096444</v>
+        <v>41702.2845472172</v>
       </c>
       <c r="E66">
         <v>-44.58000000000175</v>
@@ -6705,37 +6705,37 @@
         <v>12076</v>
       </c>
       <c r="M66">
-        <v>2058.579546124473</v>
+        <v>2016.771066124473</v>
       </c>
       <c r="N66">
-        <v>10017.42045387553</v>
+        <v>10059.22893387553</v>
       </c>
       <c r="O66">
-        <v>3506.097158856434</v>
+        <v>3520.730126856434</v>
       </c>
       <c r="P66">
-        <v>6511.323295019093</v>
+        <v>6538.498807019093</v>
       </c>
       <c r="Q66">
-        <v>7027.823295019093</v>
+        <v>7054.998807019093</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1843266676067151</v>
+        <v>0.1842954033037054</v>
       </c>
       <c r="T66">
         <v>2.015276869585424</v>
       </c>
       <c r="U66">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V66">
         <v>0.35</v>
       </c>
       <c r="W66">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.866180892904791</v>
+        <v>5.987789195729508</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09687946179116906</v>
+        <v>0.0962345074062889</v>
       </c>
       <c r="C67">
-        <v>16569.48075406523</v>
+        <v>16881.24573819328</v>
       </c>
       <c r="D67">
-        <v>41495.60575406523</v>
+        <v>41807.37073819328</v>
       </c>
       <c r="E67">
         <v>390.9249999999993</v>
@@ -6787,37 +6787,37 @@
         <v>12076</v>
       </c>
       <c r="M67">
-        <v>2090.744851532668</v>
+        <v>2048.283114032668</v>
       </c>
       <c r="N67">
-        <v>9985.255148467331</v>
+        <v>10027.71688596733</v>
       </c>
       <c r="O67">
-        <v>3494.839301963566</v>
+        <v>3509.700910088566</v>
       </c>
       <c r="P67">
-        <v>6490.415846503765</v>
+        <v>6518.015975878767</v>
       </c>
       <c r="Q67">
-        <v>7006.915846503765</v>
+        <v>7034.515975878767</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1876419229065813</v>
+        <v>0.1876099103783523</v>
       </c>
       <c r="T67">
         <v>2.063506986125576</v>
       </c>
       <c r="U67">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V67">
         <v>0.35</v>
       </c>
       <c r="W67">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.77593195609087</v>
+        <v>5.895669361949054</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09667660814349915</v>
+        <v>0.09602195452282232</v>
       </c>
       <c r="C68">
-        <v>16233.2613915797</v>
+        <v>16551.3578835591</v>
       </c>
       <c r="D68">
-        <v>41594.8913915797</v>
+        <v>41912.9878835591</v>
       </c>
       <c r="E68">
         <v>826.4300000000003</v>
@@ -6869,37 +6869,37 @@
         <v>12076</v>
       </c>
       <c r="M68">
-        <v>2122.910156940863</v>
+        <v>2079.795161940863</v>
       </c>
       <c r="N68">
-        <v>9953.089843059137</v>
+        <v>9996.204838059137</v>
       </c>
       <c r="O68">
-        <v>3483.581445070698</v>
+        <v>3498.671693320698</v>
       </c>
       <c r="P68">
-        <v>6469.508397988439</v>
+        <v>6497.53314473844</v>
       </c>
       <c r="Q68">
-        <v>6986.008397988439</v>
+        <v>7014.03314473844</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1911521932240866</v>
+        <v>0.1911193884573901</v>
       </c>
       <c r="T68">
         <v>2.11457416834456</v>
       </c>
       <c r="U68">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V68">
         <v>0.35</v>
       </c>
       <c r="W68">
-        <v>0.04800736734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.688417835544039</v>
+        <v>5.806341038283159</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09712700449582924</v>
+        <v>0.09580940163935575</v>
       </c>
       <c r="C69">
-        <v>15577.95254479058</v>
+        <v>16222.00501752534</v>
       </c>
       <c r="D69">
-        <v>41375.08754479059</v>
+        <v>42019.14001752534</v>
       </c>
       <c r="E69">
         <v>1261.935000000001</v>
@@ -6951,45 +6951,45 @@
         <v>12076</v>
       </c>
       <c r="M69">
-        <v>2198.843714849058</v>
+        <v>2111.307209849058</v>
       </c>
       <c r="N69">
-        <v>9877.156285150942</v>
+        <v>9964.692790150943</v>
       </c>
       <c r="O69">
-        <v>3457.00469980283</v>
+        <v>3487.64247655283</v>
       </c>
       <c r="P69">
-        <v>6420.151585348112</v>
+        <v>6477.050313598113</v>
       </c>
       <c r="Q69">
-        <v>6936.651585348112</v>
+        <v>6993.550313598113</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1948752071971984</v>
+        <v>0.1948415621775818</v>
       </c>
       <c r="T69">
         <v>2.168736331304089</v>
       </c>
       <c r="U69">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V69">
         <v>0.35</v>
       </c>
       <c r="W69">
-        <v>0.04898236734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>5.491977405419635</v>
+        <v>5.719679231741619</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09693390084815934</v>
+        <v>0.09559684875588918</v>
       </c>
       <c r="C70">
-        <v>15236.40146464786</v>
+        <v>15893.19121527595</v>
       </c>
       <c r="D70">
-        <v>41469.04146464787</v>
+        <v>42125.83121527595</v>
       </c>
       <c r="E70">
         <v>1697.440000000002</v>
@@ -7033,45 +7033,45 @@
         <v>12076</v>
       </c>
       <c r="M70">
-        <v>2231.662277757253</v>
+        <v>2142.819257757253</v>
       </c>
       <c r="N70">
-        <v>9844.337722242748</v>
+        <v>9933.180742242748</v>
       </c>
       <c r="O70">
-        <v>3445.518202784961</v>
+        <v>3476.613259784962</v>
       </c>
       <c r="P70">
-        <v>6398.819519457787</v>
+        <v>6456.567482457786</v>
       </c>
       <c r="Q70">
-        <v>6915.319519457787</v>
+        <v>6973.067482457786</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1988309095436296</v>
+        <v>0.1987963717552854</v>
       </c>
       <c r="T70">
         <v>2.226283629448588</v>
       </c>
       <c r="U70">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V70">
         <v>0.35</v>
       </c>
       <c r="W70">
-        <v>0.04898236734440863</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>5.411213031810522</v>
+        <v>5.635566301863066</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09674079720048942</v>
+        <v>0.09574309587242263</v>
       </c>
       <c r="C71">
-        <v>14895.2780539164</v>
+        <v>15384.21924002869</v>
       </c>
       <c r="D71">
-        <v>41563.42305391641</v>
+        <v>42052.3642400287</v>
       </c>
       <c r="E71">
         <v>2132.945</v>
@@ -7115,37 +7115,37 @@
         <v>12076</v>
       </c>
       <c r="M71">
-        <v>2264.480840665447</v>
+        <v>2198.371181665447</v>
       </c>
       <c r="N71">
-        <v>9811.519159334552</v>
+        <v>9877.628818334553</v>
       </c>
       <c r="O71">
-        <v>3434.031705767093</v>
+        <v>3457.170086417093</v>
       </c>
       <c r="P71">
-        <v>6377.487453567459</v>
+        <v>6420.45873191746</v>
       </c>
       <c r="Q71">
-        <v>6893.987453567459</v>
+        <v>6936.95873191746</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2030418184930564</v>
+        <v>0.2030063303380022</v>
       </c>
       <c r="T71">
         <v>2.287543656505636</v>
       </c>
       <c r="U71">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V71">
         <v>0.35</v>
       </c>
       <c r="W71">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.332789654537907</v>
+        <v>5.493157889220252</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0965476935528195</v>
+        <v>0.09553574298895605</v>
       </c>
       <c r="C72">
-        <v>14554.58523932372</v>
+        <v>15052.95367728945</v>
       </c>
       <c r="D72">
-        <v>41658.23523932372</v>
+        <v>42156.60367728946</v>
       </c>
       <c r="E72">
         <v>2568.450000000001</v>
@@ -7197,37 +7197,37 @@
         <v>12076</v>
       </c>
       <c r="M72">
-        <v>2297.299403573642</v>
+        <v>2230.231633573642</v>
       </c>
       <c r="N72">
-        <v>9778.700596426357</v>
+        <v>9845.768366426357</v>
       </c>
       <c r="O72">
-        <v>3422.545208749225</v>
+        <v>3446.018928249225</v>
       </c>
       <c r="P72">
-        <v>6356.155387677132</v>
+        <v>6399.749438177132</v>
       </c>
       <c r="Q72">
-        <v>6872.655387677132</v>
+        <v>6916.249438177132</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2075334547057782</v>
+        <v>0.2074969528262334</v>
       </c>
       <c r="T72">
         <v>2.352887685366487</v>
       </c>
       <c r="U72">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V72">
         <v>0.35</v>
       </c>
       <c r="W72">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.256606945187364</v>
+        <v>5.414684205088534</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09635458990514961</v>
+        <v>0.09532839010548949</v>
       </c>
       <c r="C73">
-        <v>14214.32597436355</v>
+        <v>14722.20617633874</v>
       </c>
       <c r="D73">
-        <v>41753.48097436356</v>
+        <v>42261.36117633874</v>
       </c>
       <c r="E73">
         <v>3003.954999999998</v>
@@ -7279,37 +7279,37 @@
         <v>12076</v>
       </c>
       <c r="M73">
-        <v>2330.117966481837</v>
+        <v>2262.092085481837</v>
       </c>
       <c r="N73">
-        <v>9745.882033518163</v>
+        <v>9813.907914518164</v>
       </c>
       <c r="O73">
-        <v>3411.058711731357</v>
+        <v>3434.867770081357</v>
       </c>
       <c r="P73">
-        <v>6334.823321786806</v>
+        <v>6379.040144436807</v>
       </c>
       <c r="Q73">
-        <v>6851.323321786806</v>
+        <v>6895.540144436807</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2123348589331706</v>
+        <v>0.2122972734171012</v>
       </c>
       <c r="T73">
         <v>2.422738198976362</v>
       </c>
       <c r="U73">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V73">
         <v>0.35</v>
       </c>
       <c r="W73">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.182570227649514</v>
+        <v>5.338421047270387</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09616148625747969</v>
+        <v>0.09512103722202291</v>
       </c>
       <c r="C74">
-        <v>13874.50323960257</v>
+        <v>14391.980608887</v>
       </c>
       <c r="D74">
-        <v>41849.16323960257</v>
+        <v>42366.64060888701</v>
       </c>
       <c r="E74">
         <v>3439.459999999999</v>
@@ -7361,37 +7361,37 @@
         <v>12076</v>
       </c>
       <c r="M74">
-        <v>2362.936529390032</v>
+        <v>2293.952537390032</v>
       </c>
       <c r="N74">
-        <v>9713.063470609968</v>
+        <v>9782.047462609968</v>
       </c>
       <c r="O74">
-        <v>3399.572214713489</v>
+        <v>3423.716611913489</v>
       </c>
       <c r="P74">
-        <v>6313.491255896479</v>
+        <v>6358.330850696479</v>
       </c>
       <c r="Q74">
-        <v>6829.991255896479</v>
+        <v>6874.830850696479</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2174792206053767</v>
+        <v>0.2174404740501739</v>
       </c>
       <c r="T74">
         <v>2.497578034986942</v>
       </c>
       <c r="U74">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V74">
         <v>0.35</v>
       </c>
       <c r="W74">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.110590085598827</v>
+        <v>5.264276310502741</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09596838260980978</v>
+        <v>0.09491368433855635</v>
       </c>
       <c r="C75">
-        <v>13535.12004299123</v>
+        <v>14062.28088532109</v>
       </c>
       <c r="D75">
-        <v>41945.28504299123</v>
+        <v>42472.44588532109</v>
       </c>
       <c r="E75">
         <v>3874.964999999997</v>
@@ -7443,37 +7443,37 @@
         <v>12076</v>
       </c>
       <c r="M75">
-        <v>2395.755092298227</v>
+        <v>2325.812989298227</v>
       </c>
       <c r="N75">
-        <v>9680.244907701774</v>
+        <v>9750.187010701773</v>
       </c>
       <c r="O75">
-        <v>3388.085717695621</v>
+        <v>3412.56545374562</v>
       </c>
       <c r="P75">
-        <v>6292.159190006153</v>
+        <v>6337.621556956153</v>
       </c>
       <c r="Q75">
-        <v>6808.659190006153</v>
+        <v>6854.121556956153</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2230046461051536</v>
+        <v>0.2229646525079187</v>
       </c>
       <c r="T75">
         <v>2.577961562553862</v>
       </c>
       <c r="U75">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V75">
         <v>0.35</v>
       </c>
       <c r="W75">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.04058200223446</v>
+        <v>5.192162936386266</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09577527896213986</v>
+        <v>0.09470633145508976</v>
       </c>
       <c r="C76">
-        <v>13196.179420179</v>
+        <v>13733.11095518843</v>
       </c>
       <c r="D76">
-        <v>42041.849420179</v>
+        <v>42578.78095518843</v>
       </c>
       <c r="E76">
         <v>4310.469999999998</v>
@@ -7525,37 +7525,37 @@
         <v>12076</v>
       </c>
       <c r="M76">
-        <v>2428.573655206422</v>
+        <v>2357.673441206422</v>
       </c>
       <c r="N76">
-        <v>9647.426344793577</v>
+        <v>9718.326558793578</v>
       </c>
       <c r="O76">
-        <v>3376.599220677752</v>
+        <v>3401.414295577752</v>
       </c>
       <c r="P76">
-        <v>6270.827124115825</v>
+        <v>6316.912263215826</v>
       </c>
       <c r="Q76">
-        <v>6787.327124115825</v>
+        <v>6833.412263215826</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2289551043356826</v>
+        <v>0.2289137677701053</v>
       </c>
       <c r="T76">
         <v>2.66452843839516</v>
       </c>
       <c r="U76">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V76">
         <v>0.35</v>
       </c>
       <c r="W76">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.972466029231291</v>
+        <v>5.121998572381046</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09558217531446996</v>
+        <v>0.0944989785716232</v>
       </c>
       <c r="C77">
-        <v>12857.68443483399</v>
+        <v>13404.47480768843</v>
       </c>
       <c r="D77">
-        <v>42138.85943483399</v>
+        <v>42685.64980768843</v>
       </c>
       <c r="E77">
         <v>4745.974999999999</v>
@@ -7607,37 +7607,37 @@
         <v>12076</v>
       </c>
       <c r="M77">
-        <v>2461.392218114617</v>
+        <v>2389.533893114617</v>
       </c>
       <c r="N77">
-        <v>9614.607781885383</v>
+        <v>9686.466106885384</v>
       </c>
       <c r="O77">
-        <v>3365.112723659884</v>
+        <v>3390.263137409884</v>
       </c>
       <c r="P77">
-        <v>6249.495058225499</v>
+        <v>6296.2029694755</v>
       </c>
       <c r="Q77">
-        <v>6765.995058225499</v>
+        <v>6812.7029694755</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.235381599224654</v>
+        <v>0.2353388122532669</v>
       </c>
       <c r="T77">
         <v>2.758020664303763</v>
       </c>
       <c r="U77">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.906166482174874</v>
+        <v>5.053705258082632</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.09538907166680005</v>
+        <v>0.09429162568815663</v>
       </c>
       <c r="C78">
-        <v>12519.63817896685</v>
+        <v>13076.37647217143</v>
       </c>
       <c r="D78">
-        <v>42236.31817896685</v>
+        <v>42793.05647217143</v>
       </c>
       <c r="E78">
         <v>5181.479999999996</v>
@@ -7689,37 +7689,37 @@
         <v>12076</v>
       </c>
       <c r="M78">
-        <v>2494.210781022812</v>
+        <v>2421.394345022811</v>
       </c>
       <c r="N78">
-        <v>9581.789218977188</v>
+        <v>9654.605654977189</v>
       </c>
       <c r="O78">
-        <v>3353.626226642016</v>
+        <v>3379.111979242016</v>
       </c>
       <c r="P78">
-        <v>6228.162992335172</v>
+        <v>6275.493675735173</v>
       </c>
       <c r="Q78">
-        <v>6744.662992335172</v>
+        <v>6791.993675735173</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2423436353543729</v>
+        <v>0.2422992771100253</v>
       </c>
       <c r="T78">
         <v>2.859303909038082</v>
       </c>
       <c r="U78">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V78">
         <v>0.35</v>
       </c>
       <c r="W78">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.841611660040995</v>
+        <v>4.987209136265756</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.09519596801913013</v>
+        <v>0.09408427280469006</v>
       </c>
       <c r="C79">
-        <v>12182.04377325942</v>
+        <v>12748.82001864503</v>
       </c>
       <c r="D79">
-        <v>42334.22877325943</v>
+        <v>42901.00501864503</v>
       </c>
       <c r="E79">
         <v>5616.985000000001</v>
@@ -7771,37 +7771,37 @@
         <v>12076</v>
       </c>
       <c r="M79">
-        <v>2527.029343931007</v>
+        <v>2453.254796931007</v>
       </c>
       <c r="N79">
-        <v>9548.970656068994</v>
+        <v>9622.745203068993</v>
       </c>
       <c r="O79">
-        <v>3342.139729624148</v>
+        <v>3367.960821074147</v>
       </c>
       <c r="P79">
-        <v>6206.830926444846</v>
+        <v>6254.784381994846</v>
       </c>
       <c r="Q79">
-        <v>6723.330926444846</v>
+        <v>6771.284381994846</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2499110659301543</v>
+        <v>0.2498649997804149</v>
       </c>
       <c r="T79">
         <v>2.96939439244495</v>
       </c>
       <c r="U79">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V79">
         <v>0.35</v>
       </c>
       <c r="W79">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.778733586533969</v>
+        <v>4.922440186444121</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09500286437146022</v>
+        <v>0.09387691992122348</v>
       </c>
       <c r="C80">
-        <v>11844.9043673977</v>
+        <v>12421.80955828825</v>
       </c>
       <c r="D80">
-        <v>42432.5943673977</v>
+        <v>43009.49955828825</v>
       </c>
       <c r="E80">
         <v>6052.489999999998</v>
@@ -7853,37 +7853,37 @@
         <v>12076</v>
       </c>
       <c r="M80">
-        <v>2559.847906839202</v>
+        <v>2485.115248839201</v>
       </c>
       <c r="N80">
-        <v>9516.152093160799</v>
+        <v>9590.884751160798</v>
       </c>
       <c r="O80">
-        <v>3330.65323260628</v>
+        <v>3356.809662906279</v>
       </c>
       <c r="P80">
-        <v>6185.49886055452</v>
+        <v>6234.075088254519</v>
       </c>
       <c r="Q80">
-        <v>6701.99886055452</v>
+        <v>6750.575088254519</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2581664447400977</v>
+        <v>0.2581185154208398</v>
       </c>
       <c r="T80">
         <v>3.089493101616079</v>
       </c>
       <c r="U80">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V80">
         <v>0.35</v>
       </c>
       <c r="W80">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.717467771321994</v>
+        <v>4.859331978925607</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09480976072379031</v>
+        <v>0.09366956703775692</v>
       </c>
       <c r="C81">
-        <v>11508.22314040966</v>
+        <v>12095.34924397339</v>
       </c>
       <c r="D81">
-        <v>42531.41814040967</v>
+        <v>43118.5442439734</v>
       </c>
       <c r="E81">
         <v>6487.995000000003</v>
@@ -7935,37 +7935,37 @@
         <v>12076</v>
       </c>
       <c r="M81">
-        <v>2592.666469747397</v>
+        <v>2516.975700747396</v>
       </c>
       <c r="N81">
-        <v>9483.333530252603</v>
+        <v>9559.024299252604</v>
       </c>
       <c r="O81">
-        <v>3319.166735588411</v>
+        <v>3345.658504738411</v>
       </c>
       <c r="P81">
-        <v>6164.166794664192</v>
+        <v>6213.365794514193</v>
       </c>
       <c r="Q81">
-        <v>6680.666794664192</v>
+        <v>6729.865794514193</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2672080501033691</v>
+        <v>0.2671580801698767</v>
       </c>
       <c r="T81">
         <v>3.221029783089221</v>
       </c>
       <c r="U81">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V81">
         <v>0.35</v>
       </c>
       <c r="W81">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.657752989406525</v>
+        <v>4.797821447546802</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.09461665707612041</v>
+        <v>0.09346221415429035</v>
       </c>
       <c r="C82">
-        <v>11172.0033010077</v>
+        <v>11769.44327079603</v>
       </c>
       <c r="D82">
-        <v>42630.70330100771</v>
+        <v>43228.14327079603</v>
       </c>
       <c r="E82">
         <v>6923.5</v>
@@ -8017,37 +8017,37 @@
         <v>12076</v>
       </c>
       <c r="M82">
-        <v>2625.485032655592</v>
+        <v>2548.836152655591</v>
       </c>
       <c r="N82">
-        <v>9450.514967344408</v>
+        <v>9527.163847344409</v>
       </c>
       <c r="O82">
-        <v>3307.680238570543</v>
+        <v>3334.507346570543</v>
       </c>
       <c r="P82">
-        <v>6142.834728773865</v>
+        <v>6192.656500773866</v>
       </c>
       <c r="Q82">
-        <v>6659.334728773865</v>
+        <v>6709.156500773866</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2771538160029676</v>
+        <v>0.2771016013938173</v>
       </c>
       <c r="T82">
         <v>3.365720132709677</v>
       </c>
       <c r="U82">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V82">
         <v>0.35</v>
       </c>
       <c r="W82">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.599531077038944</v>
+        <v>4.737848679452467</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09442355342845049</v>
+        <v>0.09325486127082377</v>
       </c>
       <c r="C83">
-        <v>10836.24808793598</v>
+        <v>11444.09587661286</v>
       </c>
       <c r="D83">
-        <v>42730.45308793598</v>
+        <v>43338.30087661286</v>
       </c>
       <c r="E83">
         <v>7359.004999999997</v>
@@ -8099,37 +8099,37 @@
         <v>12076</v>
       </c>
       <c r="M83">
-        <v>2658.303595563786</v>
+        <v>2580.696604563786</v>
       </c>
       <c r="N83">
-        <v>9417.696404436214</v>
+        <v>9495.303395436214</v>
       </c>
       <c r="O83">
-        <v>3296.193741552675</v>
+        <v>3323.356188402675</v>
       </c>
       <c r="P83">
-        <v>6121.502662883539</v>
+        <v>6171.94720703354</v>
       </c>
       <c r="Q83">
-        <v>6638.002662883539</v>
+        <v>6688.44720703354</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2881465046288396</v>
+        <v>0.2880918090623832</v>
       </c>
       <c r="T83">
         <v>3.525641045448076</v>
       </c>
       <c r="U83">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V83">
         <v>0.35</v>
       </c>
       <c r="W83">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.542746742754513</v>
+        <v>4.679356720446881</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09423044978078057</v>
+        <v>0.0930475083873572</v>
       </c>
       <c r="C84">
-        <v>10500.9607703225</v>
+        <v>11119.31134258802</v>
       </c>
       <c r="D84">
-        <v>42830.67077032251</v>
+        <v>43449.02134258803</v>
       </c>
       <c r="E84">
         <v>7794.510000000002</v>
@@ -8181,37 +8181,37 @@
         <v>12076</v>
       </c>
       <c r="M84">
-        <v>2691.122158471981</v>
+        <v>2612.557056471981</v>
       </c>
       <c r="N84">
-        <v>9384.877841528018</v>
+        <v>9463.442943528018</v>
       </c>
       <c r="O84">
-        <v>3284.707244534806</v>
+        <v>3312.205030234806</v>
       </c>
       <c r="P84">
-        <v>6100.170596993212</v>
+        <v>6151.237913293212</v>
       </c>
       <c r="Q84">
-        <v>6616.670596993212</v>
+        <v>6667.737913293212</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3003606031020307</v>
+        <v>0.3003031509163453</v>
       </c>
       <c r="T84">
         <v>3.70333094849074</v>
       </c>
       <c r="U84">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V84">
         <v>0.35</v>
       </c>
       <c r="W84">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.487347392233115</v>
+        <v>4.622291394587773</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09403734613311068</v>
+        <v>0.09284015550389065</v>
       </c>
       <c r="C85">
-        <v>10166.14464803635</v>
+        <v>10795.0939937477</v>
       </c>
       <c r="D85">
-        <v>42931.35964803636</v>
+        <v>43560.30899374771</v>
       </c>
       <c r="E85">
         <v>8230.014999999999</v>
@@ -8263,37 +8263,37 @@
         <v>12076</v>
       </c>
       <c r="M85">
-        <v>2723.940721380176</v>
+        <v>2644.417508380176</v>
       </c>
       <c r="N85">
-        <v>9352.059278619825</v>
+        <v>9431.582491619825</v>
       </c>
       <c r="O85">
-        <v>3273.220747516938</v>
+        <v>3301.053872066939</v>
       </c>
       <c r="P85">
-        <v>6078.838531102887</v>
+        <v>6130.528619552886</v>
       </c>
       <c r="Q85">
-        <v>6595.338531102887</v>
+        <v>6647.028619552886</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3140116543367737</v>
+        <v>0.3139511212237148</v>
       </c>
       <c r="T85">
         <v>3.901925546009014</v>
       </c>
       <c r="U85">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V85">
         <v>0.35</v>
       </c>
       <c r="W85">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.43328296582067</v>
+        <v>4.566601136821657</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.09384424248544077</v>
+        <v>0.09263280262042407</v>
       </c>
       <c r="C86">
-        <v>9831.803052049829</v>
+        <v>10471.4481995433</v>
       </c>
       <c r="D86">
-        <v>43032.52305204983</v>
+        <v>43672.1681995433</v>
       </c>
       <c r="E86">
         <v>8665.519999999997</v>
@@ -8345,37 +8345,37 @@
         <v>12076</v>
       </c>
       <c r="M86">
-        <v>2756.759284288371</v>
+        <v>2676.277960288371</v>
       </c>
       <c r="N86">
-        <v>9319.240715711629</v>
+        <v>9399.722039711629</v>
       </c>
       <c r="O86">
-        <v>3261.73425049907</v>
+        <v>3289.90271389907</v>
       </c>
       <c r="P86">
-        <v>6057.506465212558</v>
+        <v>6109.819325812559</v>
       </c>
       <c r="Q86">
-        <v>6574.006465212558</v>
+        <v>6626.319325812559</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3293690869758595</v>
+        <v>0.3293050878195051</v>
       </c>
       <c r="T86">
         <v>4.125344468217068</v>
       </c>
       <c r="U86">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V86">
         <v>0.35</v>
       </c>
       <c r="W86">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.380505787656138</v>
+        <v>4.512236837573779</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.09365113883777088</v>
+        <v>0.09242544973695752</v>
       </c>
       <c r="C87">
-        <v>9497.939344805782</v>
+        <v>10148.37837442328</v>
       </c>
       <c r="D87">
-        <v>43134.16434480578</v>
+        <v>43784.60337442328</v>
       </c>
       <c r="E87">
         <v>9101.024999999994</v>
@@ -8427,37 +8427,37 @@
         <v>12076</v>
       </c>
       <c r="M87">
-        <v>2789.577847196565</v>
+        <v>2708.138412196565</v>
       </c>
       <c r="N87">
-        <v>9286.422152803434</v>
+        <v>9367.861587803434</v>
       </c>
       <c r="O87">
-        <v>3250.247753481202</v>
+        <v>3278.751555731202</v>
       </c>
       <c r="P87">
-        <v>6036.174399322232</v>
+        <v>6089.110032072233</v>
       </c>
       <c r="Q87">
-        <v>6552.674399322232</v>
+        <v>6605.610032072233</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3467741773001569</v>
+        <v>0.3467062499614011</v>
       </c>
       <c r="T87">
         <v>4.378552580052866</v>
       </c>
       <c r="U87">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V87">
         <v>0.35</v>
       </c>
       <c r="W87">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.328970425448419</v>
+        <v>4.459151698308204</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.09345803519010096</v>
+        <v>0.09221809685349094</v>
       </c>
       <c r="C88">
-        <v>9164.556920590163</v>
+        <v>9825.888978413939</v>
       </c>
       <c r="D88">
-        <v>43236.28692059017</v>
+        <v>43897.61897841394</v>
       </c>
       <c r="E88">
         <v>9536.529999999999</v>
@@ -8509,37 +8509,37 @@
         <v>12076</v>
       </c>
       <c r="M88">
-        <v>2822.39641010476</v>
+        <v>2739.99886410476</v>
       </c>
       <c r="N88">
-        <v>9253.60358989524</v>
+        <v>9336.00113589524</v>
       </c>
       <c r="O88">
-        <v>3238.761256463334</v>
+        <v>3267.600397563334</v>
       </c>
       <c r="P88">
-        <v>6014.842333431906</v>
+        <v>6068.400738331906</v>
       </c>
       <c r="Q88">
-        <v>6531.342333431906</v>
+        <v>6584.900738331906</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3666657090993538</v>
+        <v>0.3665932924092822</v>
       </c>
       <c r="T88">
         <v>4.667933279293777</v>
       </c>
       <c r="U88">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V88">
         <v>0.35</v>
       </c>
       <c r="W88">
-        <v>0.04898236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.278633560036228</v>
+        <v>4.407301097165086</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.09405663154243103</v>
+        <v>0.09201074397002436</v>
       </c>
       <c r="C89">
-        <v>8414.047498620886</v>
+        <v>9503.984517709105</v>
       </c>
       <c r="D89">
-        <v>42921.28249862089</v>
+        <v>44011.21951770911</v>
       </c>
       <c r="E89">
         <v>9972.034999999996</v>
@@ -8591,45 +8591,45 @@
         <v>12076</v>
       </c>
       <c r="M89">
-        <v>2908.259482012955</v>
+        <v>2771.859316012955</v>
       </c>
       <c r="N89">
-        <v>9167.740517987044</v>
+        <v>9304.140683987045</v>
       </c>
       <c r="O89">
-        <v>3208.709181295465</v>
+        <v>3256.449239395466</v>
       </c>
       <c r="P89">
-        <v>5959.031336691579</v>
+        <v>6047.691444591579</v>
       </c>
       <c r="Q89">
-        <v>6475.531336691579</v>
+        <v>6564.191444591579</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3896174765599656</v>
+        <v>0.3895398798491451</v>
       </c>
       <c r="T89">
         <v>5.001834086110213</v>
       </c>
       <c r="U89">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V89">
         <v>0.35</v>
       </c>
       <c r="W89">
-        <v>0.04989236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y89">
-        <v>4.152311743394225</v>
+        <v>4.356642463864338</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.09387262789476114</v>
+        <v>0.0918033910865578</v>
       </c>
       <c r="C90">
-        <v>8074.882585048574</v>
+        <v>9182.669545269076</v>
       </c>
       <c r="D90">
-        <v>43017.62258504858</v>
+        <v>44125.40954526908</v>
       </c>
       <c r="E90">
         <v>10407.54</v>
@@ -8673,45 +8673,45 @@
         <v>12076</v>
       </c>
       <c r="M90">
-        <v>2941.687751921151</v>
+        <v>2803.71976792115</v>
       </c>
       <c r="N90">
-        <v>9134.31224807885</v>
+        <v>9272.280232078851</v>
       </c>
       <c r="O90">
-        <v>3197.009286827597</v>
+        <v>3245.298081227597</v>
       </c>
       <c r="P90">
-        <v>5937.302961251253</v>
+        <v>6026.982150851253</v>
       </c>
       <c r="Q90">
-        <v>6453.802961251253</v>
+        <v>6543.482150851253</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4163945385973462</v>
+        <v>0.4163108985289851</v>
       </c>
       <c r="T90">
         <v>5.391385027396057</v>
       </c>
       <c r="U90">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V90">
         <v>0.35</v>
       </c>
       <c r="W90">
-        <v>0.04989236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y90">
-        <v>4.105126382673836</v>
+        <v>4.307135163138607</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.09368862424709121</v>
+        <v>0.09159603820309123</v>
       </c>
       <c r="C91">
-        <v>7736.151129724232</v>
+        <v>8861.948661428927</v>
       </c>
       <c r="D91">
-        <v>43114.39612972423</v>
+        <v>44240.19366142893</v>
       </c>
       <c r="E91">
         <v>10843.045</v>
@@ -8755,45 +8755,45 @@
         <v>12076</v>
       </c>
       <c r="M91">
-        <v>2975.116021829345</v>
+        <v>2835.580219829345</v>
       </c>
       <c r="N91">
-        <v>9100.883978170656</v>
+        <v>9240.419780170654</v>
       </c>
       <c r="O91">
-        <v>3185.309392359729</v>
+        <v>3234.146923059729</v>
       </c>
       <c r="P91">
-        <v>5915.574585810926</v>
+        <v>6006.272857110926</v>
       </c>
       <c r="Q91">
-        <v>6432.074585810926</v>
+        <v>6522.772857110926</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4480401573687958</v>
+        <v>0.4479493751506141</v>
       </c>
       <c r="T91">
         <v>5.851763412552051</v>
       </c>
       <c r="U91">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V91">
         <v>0.35</v>
       </c>
       <c r="W91">
-        <v>0.04989236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.059001367138174</v>
+        <v>4.258740386024689</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.0935046205994213</v>
+        <v>0.09197368531962466</v>
       </c>
       <c r="C92">
-        <v>7397.856064599895</v>
+        <v>8217.834463682651</v>
       </c>
       <c r="D92">
-        <v>43211.6060645999</v>
+        <v>44031.58446368266</v>
       </c>
       <c r="E92">
         <v>11278.55</v>
@@ -8837,37 +8837,37 @@
         <v>12076</v>
       </c>
       <c r="M92">
-        <v>3008.54429173754</v>
+        <v>2906.63612173754</v>
       </c>
       <c r="N92">
-        <v>9067.45570826246</v>
+        <v>9169.36387826246</v>
       </c>
       <c r="O92">
-        <v>3173.609497891861</v>
+        <v>3209.277357391861</v>
       </c>
       <c r="P92">
-        <v>5893.846210370599</v>
+        <v>5960.0865208706</v>
       </c>
       <c r="Q92">
-        <v>6410.346210370599</v>
+        <v>6476.5865208706</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4860148998945356</v>
+        <v>0.4859155470965691</v>
       </c>
       <c r="T92">
         <v>6.404217474739247</v>
       </c>
       <c r="U92">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V92">
         <v>0.35</v>
       </c>
       <c r="W92">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.01390135194775</v>
+        <v>4.154630815219196</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.0933206169517514</v>
+        <v>0.09177283243615808</v>
       </c>
       <c r="C93">
-        <v>7060.00034813011</v>
+        <v>7893.033428556388</v>
       </c>
       <c r="D93">
-        <v>43309.25534813011</v>
+        <v>44142.28842855639</v>
       </c>
       <c r="E93">
         <v>11714.055</v>
@@ -8919,37 +8919,37 @@
         <v>12076</v>
       </c>
       <c r="M93">
-        <v>3041.972561645735</v>
+        <v>2938.932078645735</v>
       </c>
       <c r="N93">
-        <v>9034.027438354266</v>
+        <v>9137.067921354264</v>
       </c>
       <c r="O93">
-        <v>3161.909603423993</v>
+        <v>3197.973772473993</v>
       </c>
       <c r="P93">
-        <v>5872.117834930273</v>
+        <v>5939.094148880272</v>
       </c>
       <c r="Q93">
-        <v>6388.617834930273</v>
+        <v>6455.594148880272</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5324284740926617</v>
+        <v>0.5323186461416249</v>
       </c>
       <c r="T93">
         <v>7.079439106301374</v>
       </c>
       <c r="U93">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V93">
         <v>0.35</v>
       </c>
       <c r="W93">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.969792545882391</v>
+        <v>4.108975531535469</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.09313661330408149</v>
+        <v>0.09157197955269152</v>
       </c>
       <c r="C94">
-        <v>6722.586965571936</v>
+        <v>7568.790459101809</v>
       </c>
       <c r="D94">
-        <v>43407.34696557194</v>
+        <v>44253.55045910181</v>
       </c>
       <c r="E94">
         <v>12149.56</v>
@@ -9001,37 +9001,37 @@
         <v>12076</v>
       </c>
       <c r="M94">
-        <v>3075.40083155393</v>
+        <v>2971.22803555393</v>
       </c>
       <c r="N94">
-        <v>9000.59916844607</v>
+        <v>9104.77196444607</v>
       </c>
       <c r="O94">
-        <v>3150.209708956124</v>
+        <v>3186.670187556124</v>
       </c>
       <c r="P94">
-        <v>5850.389459489945</v>
+        <v>5918.101776889946</v>
       </c>
       <c r="Q94">
-        <v>6366.889459489945</v>
+        <v>6434.601776889946</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5904454418403197</v>
+        <v>0.590322519947945</v>
       </c>
       <c r="T94">
         <v>7.923466145754035</v>
       </c>
       <c r="U94">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V94">
         <v>0.35</v>
       </c>
       <c r="W94">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.926642626905408</v>
+        <v>4.064312754018779</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.09295260965641157</v>
+        <v>0.09137112666922494</v>
       </c>
       <c r="C95">
-        <v>6385.618929289194</v>
+        <v>7245.109785848515</v>
       </c>
       <c r="D95">
-        <v>43505.8839292892</v>
+        <v>44365.37478584852</v>
       </c>
       <c r="E95">
         <v>12585.065</v>
@@ -9083,37 +9083,37 @@
         <v>12076</v>
       </c>
       <c r="M95">
-        <v>3108.829101462125</v>
+        <v>3003.523992462125</v>
       </c>
       <c r="N95">
-        <v>8967.170898537875</v>
+        <v>9072.476007537874</v>
       </c>
       <c r="O95">
-        <v>3138.509814488256</v>
+        <v>3175.366602638256</v>
       </c>
       <c r="P95">
-        <v>5828.66108404962</v>
+        <v>5897.109404899618</v>
       </c>
       <c r="Q95">
-        <v>6345.16108404962</v>
+        <v>6413.609404899618</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6650386860873082</v>
+        <v>0.6648989291274993</v>
       </c>
       <c r="T95">
         <v>9.008643767907452</v>
       </c>
       <c r="U95">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V95">
         <v>0.35</v>
       </c>
       <c r="W95">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.884420663175242</v>
+        <v>4.020610466341157</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09276860600874168</v>
+        <v>0.09117027378575837</v>
       </c>
       <c r="C96">
-        <v>6049.099279060843</v>
+        <v>6921.995682194924</v>
       </c>
       <c r="D96">
-        <v>43604.86927906085</v>
+        <v>44477.76568219493</v>
       </c>
       <c r="E96">
         <v>13020.57</v>
@@ -9165,37 +9165,37 @@
         <v>12076</v>
       </c>
       <c r="M96">
-        <v>3142.25737137032</v>
+        <v>3035.81994937032</v>
       </c>
       <c r="N96">
-        <v>8933.74262862968</v>
+        <v>9040.18005062968</v>
       </c>
       <c r="O96">
-        <v>3126.809920020388</v>
+        <v>3164.063017720388</v>
       </c>
       <c r="P96">
-        <v>5806.932708609292</v>
+        <v>5876.117032909293</v>
       </c>
       <c r="Q96">
-        <v>6323.432708609292</v>
+        <v>6392.617032909293</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7644963450832933</v>
+        <v>0.7643341413669053</v>
       </c>
       <c r="T96">
         <v>10.45554726411202</v>
       </c>
       <c r="U96">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V96">
         <v>0.35</v>
       </c>
       <c r="W96">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.84309703909891</v>
+        <v>3.977838014571571</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09258460236107177</v>
+        <v>0.09096942090229181</v>
       </c>
       <c r="C97">
-        <v>5713.031082393572</v>
+        <v>6599.45246495265</v>
       </c>
       <c r="D97">
-        <v>43704.30608239358</v>
+        <v>44590.72746495266</v>
       </c>
       <c r="E97">
         <v>13456.075</v>
@@ -9247,37 +9247,37 @@
         <v>12076</v>
       </c>
       <c r="M97">
-        <v>3175.685641278515</v>
+        <v>3068.115906278515</v>
       </c>
       <c r="N97">
-        <v>8900.314358721485</v>
+        <v>9007.884093721485</v>
       </c>
       <c r="O97">
-        <v>3115.11002555252</v>
+        <v>3152.759432802519</v>
       </c>
       <c r="P97">
-        <v>5785.204333168966</v>
+        <v>5855.124660918966</v>
       </c>
       <c r="Q97">
-        <v>6301.704333168966</v>
+        <v>6371.624660918966</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.9037370676776725</v>
+        <v>0.9035434385020735</v>
       </c>
       <c r="T97">
         <v>12.4812121587984</v>
       </c>
       <c r="U97">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V97">
         <v>0.35</v>
       </c>
       <c r="W97">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.802643386055763</v>
+        <v>3.935966035470817</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.09240059871340184</v>
+        <v>0.09076856801882524</v>
       </c>
       <c r="C98">
-        <v>5377.417434838666</v>
+        <v>6277.484494899254</v>
       </c>
       <c r="D98">
-        <v>43804.19743483866</v>
+        <v>44704.26449489925</v>
       </c>
       <c r="E98">
         <v>13891.57999999999</v>
@@ -9329,37 +9329,37 @@
         <v>12076</v>
       </c>
       <c r="M98">
-        <v>3209.113911186709</v>
+        <v>3100.411863186709</v>
       </c>
       <c r="N98">
-        <v>8866.886088813291</v>
+        <v>8975.58813681329</v>
       </c>
       <c r="O98">
-        <v>3103.410131084652</v>
+        <v>3141.455847884652</v>
       </c>
       <c r="P98">
-        <v>5763.47595772864</v>
+        <v>5834.132288928638</v>
       </c>
       <c r="Q98">
-        <v>6279.97595772864</v>
+        <v>6350.632288928638</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.112598151569238</v>
+        <v>1.112357384204823</v>
       </c>
       <c r="T98">
         <v>15.51970950082794</v>
       </c>
       <c r="U98">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V98">
         <v>0.35</v>
       </c>
       <c r="W98">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.763032517451017</v>
+        <v>3.894966389267997</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.09221659506573196</v>
+        <v>0.09056771513535869</v>
       </c>
       <c r="C99">
-        <v>5042.261460313159</v>
+        <v>5956.096177339299</v>
       </c>
       <c r="D99">
-        <v>43904.54646031316</v>
+        <v>44818.3811773393</v>
       </c>
       <c r="E99">
         <v>14327.085</v>
@@ -9411,37 +9411,37 @@
         <v>12076</v>
       </c>
       <c r="M99">
-        <v>3242.542181094904</v>
+        <v>3132.707820094904</v>
       </c>
       <c r="N99">
-        <v>8833.457818905095</v>
+        <v>8943.292179905096</v>
       </c>
       <c r="O99">
-        <v>3091.710236616783</v>
+        <v>3130.152262966783</v>
       </c>
       <c r="P99">
-        <v>5741.747582288312</v>
+        <v>5813.139916938313</v>
       </c>
       <c r="Q99">
-        <v>6258.247582288312</v>
+        <v>6329.639916938313</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.460699958055185</v>
+        <v>1.460380627042743</v>
       </c>
       <c r="T99">
         <v>20.58387173754389</v>
       </c>
       <c r="U99">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V99">
         <v>0.35</v>
       </c>
       <c r="W99">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.724238367786573</v>
+        <v>3.854812096595131</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.09203259141806203</v>
+        <v>0.0903668622518921</v>
       </c>
       <c r="C100">
-        <v>4707.566311425719</v>
+        <v>5635.291962674302</v>
       </c>
       <c r="D100">
-        <v>44005.35631142572</v>
+        <v>44933.0819626743</v>
       </c>
       <c r="E100">
         <v>14762.59</v>
@@ -9493,37 +9493,37 @@
         <v>12076</v>
       </c>
       <c r="M100">
-        <v>3275.970451003099</v>
+        <v>3165.003777003099</v>
       </c>
       <c r="N100">
-        <v>8800.029548996901</v>
+        <v>8910.996222996901</v>
       </c>
       <c r="O100">
-        <v>3080.010342148915</v>
+        <v>3118.848678048915</v>
       </c>
       <c r="P100">
-        <v>5720.019206847986</v>
+        <v>5792.147544947986</v>
       </c>
       <c r="Q100">
-        <v>6236.519206847986</v>
+        <v>6308.647544947986</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.156903571027077</v>
+        <v>2.156427112718581</v>
       </c>
       <c r="T100">
         <v>30.71219621097577</v>
       </c>
       <c r="U100">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V100">
         <v>0.35</v>
       </c>
       <c r="W100">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.68623593546222</v>
+        <v>3.815477279282936</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.09184858777039212</v>
+        <v>0.09016600936842553</v>
       </c>
       <c r="C101">
-        <v>4373.335169806494</v>
+        <v>5315.076346981048</v>
       </c>
       <c r="D101">
-        <v>44106.6301698065</v>
+        <v>45048.37134698105</v>
       </c>
       <c r="E101">
         <v>15198.095</v>
@@ -9575,37 +9575,37 @@
         <v>12076</v>
       </c>
       <c r="M101">
-        <v>3309.398720911294</v>
+        <v>3197.299733911294</v>
       </c>
       <c r="N101">
-        <v>8766.601279088705</v>
+        <v>8878.700266088706</v>
       </c>
       <c r="O101">
-        <v>3068.310447681047</v>
+        <v>3107.545093131047</v>
       </c>
       <c r="P101">
-        <v>5698.290831407659</v>
+        <v>5771.155172957659</v>
       </c>
       <c r="Q101">
-        <v>6214.790831407659</v>
+        <v>6287.655172957659</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.245514409942754</v>
+        <v>4.244566569746096</v>
       </c>
       <c r="T101">
         <v>61.09716963127144</v>
       </c>
       <c r="U101">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V101">
         <v>0.35</v>
       </c>
       <c r="W101">
-        <v>0.04989236734440863</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>3.649001229043409</v>
+        <v>3.776937104744724</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/colombia/colombia_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_oil_gas_integrated.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1100504448316159</v>
+        <v>0.1098170919481493</v>
       </c>
       <c r="C2">
-        <v>39305.02910482491</v>
+        <v>38955.1225512445</v>
       </c>
       <c r="D2">
-        <v>35923.32910482491</v>
+        <v>36008.9275512445</v>
       </c>
       <c r="E2">
-        <v>-27916.9</v>
+        <v>-27481.395</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>435.505</v>
       </c>
       <c r="G2">
         <v>3381.7</v>
@@ -1457,28 +1457,28 @@
         <v>12076</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>30.11843190819489</v>
       </c>
       <c r="N2">
-        <v>12076</v>
+        <v>12045.88156809181</v>
       </c>
       <c r="O2">
-        <v>4226.599999999999</v>
+        <v>4216.058548832131</v>
       </c>
       <c r="P2">
-        <v>7849.400000000001</v>
+        <v>7829.823019259674</v>
       </c>
       <c r="Q2">
-        <v>8365.900000000001</v>
+        <v>8346.323019259675</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1100504448316159</v>
+        <v>0.110472291186571</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860212</v>
+        <v>0.9410606375547679</v>
       </c>
       <c r="U2">
         <v>0.06915748822216712</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>400.9504889500656</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1098170919481493</v>
+        <v>0.1095837390646828</v>
       </c>
       <c r="C3">
-        <v>38955.1225512445</v>
+        <v>38605.62490157037</v>
       </c>
       <c r="D3">
-        <v>36008.9275512445</v>
+        <v>36094.93490157037</v>
       </c>
       <c r="E3">
-        <v>-27481.395</v>
+        <v>-27045.89</v>
       </c>
       <c r="F3">
-        <v>435.505</v>
+        <v>871.01</v>
       </c>
       <c r="G3">
         <v>3381.7</v>
@@ -1539,28 +1539,28 @@
         <v>12076</v>
       </c>
       <c r="M3">
-        <v>30.11843190819489</v>
+        <v>60.23686381638979</v>
       </c>
       <c r="N3">
-        <v>12045.88156809181</v>
+        <v>12015.76313618361</v>
       </c>
       <c r="O3">
-        <v>4216.058548832131</v>
+        <v>4205.517097664263</v>
       </c>
       <c r="P3">
-        <v>7829.823019259674</v>
+        <v>7810.246038519347</v>
       </c>
       <c r="Q3">
-        <v>8346.323019259675</v>
+        <v>8326.746038519348</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.110472291186571</v>
+        <v>0.1109027466508108</v>
       </c>
       <c r="T3">
-        <v>0.9410606375547679</v>
+        <v>0.9473242890534889</v>
       </c>
       <c r="U3">
         <v>0.06915748822216712</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>400.9504889500656</v>
+        <v>200.4752444750328</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1095837390646828</v>
+        <v>0.1093503861812162</v>
       </c>
       <c r="C4">
-        <v>38605.62490157037</v>
+        <v>38256.53909281947</v>
       </c>
       <c r="D4">
-        <v>36094.93490157037</v>
+        <v>36181.35409281947</v>
       </c>
       <c r="E4">
-        <v>-27045.89</v>
+        <v>-26610.385</v>
       </c>
       <c r="F4">
-        <v>871.01</v>
+        <v>1306.515</v>
       </c>
       <c r="G4">
         <v>3381.7</v>
@@ -1621,28 +1621,28 @@
         <v>12076</v>
       </c>
       <c r="M4">
-        <v>60.23686381638979</v>
+        <v>90.35529572458466</v>
       </c>
       <c r="N4">
-        <v>12015.76313618361</v>
+        <v>11985.64470427542</v>
       </c>
       <c r="O4">
-        <v>4205.517097664263</v>
+        <v>4194.975646496395</v>
       </c>
       <c r="P4">
-        <v>7810.246038519347</v>
+        <v>7790.66905777902</v>
       </c>
       <c r="Q4">
-        <v>8326.746038519348</v>
+        <v>8307.169057779021</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1109027466508108</v>
+        <v>0.1113420774854474</v>
       </c>
       <c r="T4">
-        <v>0.9473242890534889</v>
+        <v>0.9537170880057917</v>
       </c>
       <c r="U4">
         <v>0.06915748822216712</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>200.4752444750328</v>
+        <v>133.6501629833552</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1093503861812162</v>
+        <v>0.1091170332977496</v>
       </c>
       <c r="C5">
-        <v>38256.53909281947</v>
+        <v>37907.86809020365</v>
       </c>
       <c r="D5">
-        <v>36181.35409281947</v>
+        <v>36268.18809020365</v>
       </c>
       <c r="E5">
-        <v>-26610.385</v>
+        <v>-26174.88</v>
       </c>
       <c r="F5">
-        <v>1306.515</v>
+        <v>1742.02</v>
       </c>
       <c r="G5">
         <v>3381.7</v>
@@ -1703,28 +1703,28 @@
         <v>12076</v>
       </c>
       <c r="M5">
-        <v>90.35529572458466</v>
+        <v>120.4737276327796</v>
       </c>
       <c r="N5">
-        <v>11985.64470427542</v>
+        <v>11955.52627236722</v>
       </c>
       <c r="O5">
-        <v>4194.975646496395</v>
+        <v>4184.434195328527</v>
       </c>
       <c r="P5">
-        <v>7790.66905777902</v>
+        <v>7771.092077038694</v>
       </c>
       <c r="Q5">
-        <v>8307.169057779021</v>
+        <v>8287.592077038695</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1113420774854474</v>
+        <v>0.1117905610458055</v>
       </c>
       <c r="T5">
-        <v>0.9537170880057917</v>
+        <v>0.960243070269601</v>
       </c>
       <c r="U5">
         <v>0.06915748822216712</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>133.6501629833552</v>
+        <v>100.2376222375164</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1091170332977496</v>
+        <v>0.108883680414283</v>
       </c>
       <c r="C6">
-        <v>37907.86809020365</v>
+        <v>37559.61488746892</v>
       </c>
       <c r="D6">
-        <v>36268.18809020365</v>
+        <v>36355.43988746892</v>
       </c>
       <c r="E6">
-        <v>-26174.88</v>
+        <v>-25739.375</v>
       </c>
       <c r="F6">
-        <v>1742.02</v>
+        <v>2177.525</v>
       </c>
       <c r="G6">
         <v>3381.7</v>
@@ -1785,28 +1785,28 @@
         <v>12076</v>
       </c>
       <c r="M6">
-        <v>120.4737276327796</v>
+        <v>150.5921595409745</v>
       </c>
       <c r="N6">
-        <v>11955.52627236722</v>
+        <v>11925.40784045903</v>
       </c>
       <c r="O6">
-        <v>4184.434195328527</v>
+        <v>4173.892744160658</v>
       </c>
       <c r="P6">
-        <v>7771.092077038694</v>
+        <v>7751.515096298367</v>
       </c>
       <c r="Q6">
-        <v>8287.592077038695</v>
+        <v>8268.015096298368</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1117905610458055</v>
+        <v>0.1122484863653291</v>
       </c>
       <c r="T6">
-        <v>0.960243070269601</v>
+        <v>0.9669064416337009</v>
       </c>
       <c r="U6">
         <v>0.06915748822216712</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>100.2376222375164</v>
+        <v>80.19009779001311</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.108883680414283</v>
+        <v>0.1086503275308165</v>
       </c>
       <c r="C7">
-        <v>37559.61488746892</v>
+        <v>37211.7825072394</v>
       </c>
       <c r="D7">
-        <v>36355.43988746892</v>
+        <v>36443.1125072394</v>
       </c>
       <c r="E7">
-        <v>-25739.375</v>
+        <v>-25303.87</v>
       </c>
       <c r="F7">
-        <v>2177.525</v>
+        <v>2613.03</v>
       </c>
       <c r="G7">
         <v>3381.7</v>
@@ -1867,28 +1867,28 @@
         <v>12076</v>
       </c>
       <c r="M7">
-        <v>150.5921595409745</v>
+        <v>180.7105914491694</v>
       </c>
       <c r="N7">
-        <v>11925.40784045903</v>
+        <v>11895.28940855083</v>
       </c>
       <c r="O7">
-        <v>4173.892744160658</v>
+        <v>4163.35129299279</v>
       </c>
       <c r="P7">
-        <v>7751.515096298367</v>
+        <v>7731.93811555804</v>
       </c>
       <c r="Q7">
-        <v>8268.015096298368</v>
+        <v>8248.438115558041</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1122484863653291</v>
+        <v>0.1127161547767574</v>
       </c>
       <c r="T7">
-        <v>0.9669064416337009</v>
+        <v>0.9737115868566115</v>
       </c>
       <c r="U7">
         <v>0.06915748822216712</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>80.19009779001311</v>
+        <v>66.82508149167761</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1086503275308165</v>
+        <v>0.1084169746473499</v>
       </c>
       <c r="C8">
-        <v>37211.7825072394</v>
+        <v>36864.37400136645</v>
       </c>
       <c r="D8">
-        <v>36443.1125072394</v>
+        <v>36531.20900136645</v>
       </c>
       <c r="E8">
-        <v>-25303.87</v>
+        <v>-24868.365</v>
       </c>
       <c r="F8">
-        <v>2613.03</v>
+        <v>3048.535</v>
       </c>
       <c r="G8">
         <v>3381.7</v>
@@ -1949,28 +1949,28 @@
         <v>12076</v>
       </c>
       <c r="M8">
-        <v>180.7105914491693</v>
+        <v>210.8290233573642</v>
       </c>
       <c r="N8">
-        <v>11895.28940855083</v>
+        <v>11865.17097664264</v>
       </c>
       <c r="O8">
-        <v>4163.35129299279</v>
+        <v>4152.809841824922</v>
       </c>
       <c r="P8">
-        <v>7731.93811555804</v>
+        <v>7712.361134817714</v>
       </c>
       <c r="Q8">
-        <v>8248.438115558041</v>
+        <v>8228.861134817715</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1127161547767574</v>
+        <v>0.1131938805733778</v>
       </c>
       <c r="T8">
-        <v>0.9737115868566115</v>
+        <v>0.9806630792886168</v>
       </c>
       <c r="U8">
         <v>0.06915748822216712</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>66.82508149167761</v>
+        <v>57.27864127858081</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1084169746473499</v>
+        <v>0.1081836217638834</v>
       </c>
       <c r="C9">
-        <v>36864.37400136645</v>
+        <v>36517.39245128275</v>
       </c>
       <c r="D9">
-        <v>36531.20900136646</v>
+        <v>36619.73245128275</v>
       </c>
       <c r="E9">
-        <v>-24868.365</v>
+        <v>-24432.86</v>
       </c>
       <c r="F9">
-        <v>3048.535</v>
+        <v>3484.04</v>
       </c>
       <c r="G9">
         <v>3381.7</v>
@@ -2031,28 +2031,28 @@
         <v>12076</v>
       </c>
       <c r="M9">
-        <v>210.8290233573643</v>
+        <v>240.9474552655591</v>
       </c>
       <c r="N9">
-        <v>11865.17097664264</v>
+        <v>11835.05254473444</v>
       </c>
       <c r="O9">
-        <v>4152.809841824922</v>
+        <v>4142.268390657054</v>
       </c>
       <c r="P9">
-        <v>7712.361134817714</v>
+        <v>7692.784154077387</v>
       </c>
       <c r="Q9">
-        <v>8228.861134817715</v>
+        <v>8209.284154077388</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1131938805733778</v>
+        <v>0.1136819917134029</v>
       </c>
       <c r="T9">
-        <v>0.9806630792886168</v>
+        <v>0.987765691121318</v>
       </c>
       <c r="U9">
         <v>0.06915748822216712</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>57.2786412785808</v>
+        <v>50.1188111187582</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1081836217638834</v>
+        <v>0.1079502688804168</v>
       </c>
       <c r="C10">
-        <v>36517.39245128275</v>
+        <v>36170.84096836159</v>
       </c>
       <c r="D10">
-        <v>36619.73245128275</v>
+        <v>36708.68596836159</v>
       </c>
       <c r="E10">
-        <v>-24432.86</v>
+        <v>-23997.355</v>
       </c>
       <c r="F10">
-        <v>3484.04</v>
+        <v>3919.545</v>
       </c>
       <c r="G10">
         <v>3381.7</v>
@@ -2113,28 +2113,28 @@
         <v>12076</v>
       </c>
       <c r="M10">
-        <v>240.9474552655591</v>
+        <v>271.065887173754</v>
       </c>
       <c r="N10">
-        <v>11835.05254473444</v>
+        <v>11804.93411282625</v>
       </c>
       <c r="O10">
-        <v>4142.268390657054</v>
+        <v>4131.726939489185</v>
       </c>
       <c r="P10">
-        <v>7692.784154077387</v>
+        <v>7673.20717333706</v>
       </c>
       <c r="Q10">
-        <v>8209.284154077388</v>
+        <v>8189.70717333706</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1136819917134029</v>
+        <v>0.1141808305707912</v>
       </c>
       <c r="T10">
-        <v>0.987765691121318</v>
+        <v>0.9950244043129797</v>
       </c>
       <c r="U10">
         <v>0.06915748822216712</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>50.1188111187582</v>
+        <v>44.55005432778506</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1079502688804168</v>
+        <v>0.1077169159969502</v>
       </c>
       <c r="C11">
-        <v>36170.84096836159</v>
+        <v>35824.72269428139</v>
       </c>
       <c r="D11">
-        <v>36708.68596836159</v>
+        <v>36798.07269428139</v>
       </c>
       <c r="E11">
-        <v>-23997.355</v>
+        <v>-23561.85</v>
       </c>
       <c r="F11">
-        <v>3919.545</v>
+        <v>4355.049999999999</v>
       </c>
       <c r="G11">
         <v>3381.7</v>
@@ -2195,28 +2195,28 @@
         <v>12076</v>
       </c>
       <c r="M11">
-        <v>271.065887173754</v>
+        <v>301.1843190819488</v>
       </c>
       <c r="N11">
-        <v>11804.93411282625</v>
+        <v>11774.81568091805</v>
       </c>
       <c r="O11">
-        <v>4131.726939489185</v>
+        <v>4121.185488321317</v>
       </c>
       <c r="P11">
-        <v>7673.20717333706</v>
+        <v>7653.630192596734</v>
       </c>
       <c r="Q11">
-        <v>8189.70717333706</v>
+        <v>8170.130192596734</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1141808305707912</v>
+        <v>0.1146907547361215</v>
       </c>
       <c r="T11">
-        <v>0.9950244043129797</v>
+        <v>1.002444422242234</v>
       </c>
       <c r="U11">
         <v>0.06915748822216712</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>44.55005432778506</v>
+        <v>40.09504889500657</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1077169159969502</v>
+        <v>0.1074835631134836</v>
       </c>
       <c r="C12">
-        <v>35824.72269428138</v>
+        <v>35479.04080139557</v>
       </c>
       <c r="D12">
-        <v>36798.07269428139</v>
+        <v>36887.89580139557</v>
       </c>
       <c r="E12">
-        <v>-23561.85</v>
+        <v>-23126.345</v>
       </c>
       <c r="F12">
-        <v>4355.05</v>
+        <v>4790.555</v>
       </c>
       <c r="G12">
         <v>3381.7</v>
@@ -2277,28 +2277,28 @@
         <v>12076</v>
       </c>
       <c r="M12">
-        <v>301.184319081949</v>
+        <v>331.3027509901438</v>
       </c>
       <c r="N12">
-        <v>11774.81568091805</v>
+        <v>11744.69724900986</v>
       </c>
       <c r="O12">
-        <v>4121.185488321317</v>
+        <v>4110.644037153449</v>
       </c>
       <c r="P12">
-        <v>7653.630192596734</v>
+        <v>7634.053211856407</v>
       </c>
       <c r="Q12">
-        <v>8170.130192596734</v>
+        <v>8150.553211856407</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1146907547361215</v>
+        <v>0.1152121378714592</v>
       </c>
       <c r="T12">
-        <v>1.002444422242234</v>
+        <v>1.010031182147426</v>
       </c>
       <c r="U12">
         <v>0.06915748822216712</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>40.09504889500656</v>
+        <v>36.45004445000597</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1074835631134836</v>
+        <v>0.1072502102300171</v>
       </c>
       <c r="C13">
-        <v>35479.04080139557</v>
+        <v>35133.7984931079</v>
       </c>
       <c r="D13">
-        <v>36887.89580139557</v>
+        <v>36978.15849310791</v>
       </c>
       <c r="E13">
-        <v>-23126.345</v>
+        <v>-22690.84</v>
       </c>
       <c r="F13">
-        <v>4790.555</v>
+        <v>5226.059999999999</v>
       </c>
       <c r="G13">
         <v>3381.7</v>
@@ -2359,28 +2359,28 @@
         <v>12076</v>
       </c>
       <c r="M13">
-        <v>331.3027509901438</v>
+        <v>361.4211828983387</v>
       </c>
       <c r="N13">
-        <v>11744.69724900986</v>
+        <v>11714.57881710166</v>
       </c>
       <c r="O13">
-        <v>4110.644037153449</v>
+        <v>4100.102585985581</v>
       </c>
       <c r="P13">
-        <v>7634.053211856407</v>
+        <v>7614.47623111608</v>
       </c>
       <c r="Q13">
-        <v>8150.553211856407</v>
+        <v>8130.97623111608</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1152121378714592</v>
+        <v>0.1157453706235091</v>
       </c>
       <c r="T13">
-        <v>1.010031182147426</v>
+        <v>1.0177903684141</v>
       </c>
       <c r="U13">
         <v>0.06915748822216712</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.45004445000597</v>
+        <v>33.4125407458388</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1072502102300171</v>
+        <v>0.1070168573465505</v>
       </c>
       <c r="C14">
-        <v>35133.7984931079</v>
+        <v>34788.99900425325</v>
       </c>
       <c r="D14">
-        <v>36978.15849310791</v>
+        <v>37068.86400425326</v>
       </c>
       <c r="E14">
-        <v>-22690.84</v>
+        <v>-22255.335</v>
       </c>
       <c r="F14">
-        <v>5226.059999999999</v>
+        <v>5661.565000000001</v>
       </c>
       <c r="G14">
         <v>3381.7</v>
@@ -2441,28 +2441,28 @@
         <v>12076</v>
       </c>
       <c r="M14">
-        <v>361.4211828983387</v>
+        <v>391.5396148065336</v>
       </c>
       <c r="N14">
-        <v>11714.57881710166</v>
+        <v>11684.46038519347</v>
       </c>
       <c r="O14">
-        <v>4100.102585985581</v>
+        <v>4089.561134817713</v>
       </c>
       <c r="P14">
-        <v>7614.47623111608</v>
+        <v>7594.899250375753</v>
       </c>
       <c r="Q14">
-        <v>8130.97623111608</v>
+        <v>8111.399250375753</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1157453706235091</v>
+        <v>0.1162908615997441</v>
       </c>
       <c r="T14">
-        <v>1.0177903684141</v>
+        <v>1.025727926778859</v>
       </c>
       <c r="U14">
         <v>0.06915748822216712</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.4125407458388</v>
+        <v>30.8423453038512</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1070168573465505</v>
+        <v>0.1067835044630839</v>
       </c>
       <c r="C15">
-        <v>34788.99900425325</v>
+        <v>34444.64560148409</v>
       </c>
       <c r="D15">
-        <v>37068.86400425326</v>
+        <v>37160.01560148409</v>
       </c>
       <c r="E15">
-        <v>-22255.335</v>
+        <v>-21819.83</v>
       </c>
       <c r="F15">
-        <v>5661.565000000001</v>
+        <v>6097.070000000001</v>
       </c>
       <c r="G15">
         <v>3381.7</v>
@@ -2523,28 +2523,28 @@
         <v>12076</v>
       </c>
       <c r="M15">
-        <v>391.5396148065336</v>
+        <v>421.6580467147285</v>
       </c>
       <c r="N15">
-        <v>11684.46038519347</v>
+        <v>11654.34195328527</v>
       </c>
       <c r="O15">
-        <v>4089.561134817713</v>
+        <v>4079.019683649845</v>
       </c>
       <c r="P15">
-        <v>7594.899250375753</v>
+        <v>7575.322269635426</v>
       </c>
       <c r="Q15">
-        <v>8111.399250375753</v>
+        <v>8091.822269635426</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1162908615997441</v>
+        <v>0.1168490384126357</v>
       </c>
       <c r="T15">
-        <v>1.025727926778859</v>
+        <v>1.033850079524193</v>
       </c>
       <c r="U15">
         <v>0.06915748822216712</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>30.8423453038512</v>
+        <v>28.6393206392904</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1067835044630839</v>
+        <v>0.1065501515796174</v>
       </c>
       <c r="C16">
-        <v>34444.64560148409</v>
+        <v>34100.74158366262</v>
       </c>
       <c r="D16">
-        <v>37160.01560148409</v>
+        <v>37251.61658366262</v>
       </c>
       <c r="E16">
-        <v>-21819.83</v>
+        <v>-21384.325</v>
       </c>
       <c r="F16">
-        <v>6097.070000000001</v>
+        <v>6532.575000000001</v>
       </c>
       <c r="G16">
         <v>3381.7</v>
@@ -2605,28 +2605,28 @@
         <v>12076</v>
       </c>
       <c r="M16">
-        <v>421.6580467147285</v>
+        <v>451.7764786229234</v>
       </c>
       <c r="N16">
-        <v>11654.34195328527</v>
+        <v>11624.22352137708</v>
       </c>
       <c r="O16">
-        <v>4079.019683649845</v>
+        <v>4068.478232481977</v>
       </c>
       <c r="P16">
-        <v>7575.322269635426</v>
+        <v>7555.745288895099</v>
       </c>
       <c r="Q16">
-        <v>8091.822269635426</v>
+        <v>8072.245288895099</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1168490384126357</v>
+        <v>0.1174203487975954</v>
       </c>
       <c r="T16">
-        <v>1.033850079524193</v>
+        <v>1.042163341745888</v>
       </c>
       <c r="U16">
         <v>0.06915748822216712</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.6393206392904</v>
+        <v>26.73003259667104</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1065501515796174</v>
+        <v>0.1063167986961508</v>
       </c>
       <c r="C17">
-        <v>34100.74158366262</v>
+        <v>33757.29028225873</v>
       </c>
       <c r="D17">
-        <v>37251.61658366262</v>
+        <v>37343.67028225874</v>
       </c>
       <c r="E17">
-        <v>-21384.325</v>
+        <v>-20948.82</v>
       </c>
       <c r="F17">
-        <v>6532.575</v>
+        <v>6968.08</v>
       </c>
       <c r="G17">
         <v>3381.7</v>
@@ -2687,28 +2687,28 @@
         <v>12076</v>
       </c>
       <c r="M17">
-        <v>451.7764786229234</v>
+        <v>481.8949105311183</v>
       </c>
       <c r="N17">
-        <v>11624.22352137708</v>
+        <v>11594.10508946888</v>
       </c>
       <c r="O17">
-        <v>4068.478232481977</v>
+        <v>4057.936781314108</v>
       </c>
       <c r="P17">
-        <v>7555.745288895099</v>
+        <v>7536.168308154773</v>
       </c>
       <c r="Q17">
-        <v>8072.245288895099</v>
+        <v>8052.668308154773</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1174203487975954</v>
+        <v>0.1180052618107683</v>
       </c>
       <c r="T17">
-        <v>1.042163341745888</v>
+        <v>1.050674538782386</v>
       </c>
       <c r="U17">
         <v>0.06915748822216712</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>26.73003259667104</v>
+        <v>25.0594055593791</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1063167986961508</v>
+        <v>0.1060834458126842</v>
       </c>
       <c r="C18">
-        <v>33757.29028225873</v>
+        <v>33414.29506175394</v>
       </c>
       <c r="D18">
-        <v>37343.67028225874</v>
+        <v>37436.18006175394</v>
       </c>
       <c r="E18">
-        <v>-20948.82</v>
+        <v>-20513.315</v>
       </c>
       <c r="F18">
-        <v>6968.08</v>
+        <v>7403.585000000001</v>
       </c>
       <c r="G18">
         <v>3381.7</v>
@@ -2769,28 +2769,28 @@
         <v>12076</v>
       </c>
       <c r="M18">
-        <v>481.8949105311183</v>
+        <v>512.0133424393132</v>
       </c>
       <c r="N18">
-        <v>11594.10508946888</v>
+        <v>11563.98665756069</v>
       </c>
       <c r="O18">
-        <v>4057.936781314108</v>
+        <v>4047.39533014624</v>
       </c>
       <c r="P18">
-        <v>7536.168308154773</v>
+        <v>7516.591327414446</v>
       </c>
       <c r="Q18">
-        <v>8052.668308154773</v>
+        <v>8033.091327414446</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1180052618107683</v>
+        <v>0.1186042691134154</v>
       </c>
       <c r="T18">
-        <v>1.050674538782386</v>
+        <v>1.0593908249041</v>
       </c>
       <c r="U18">
         <v>0.06915748822216712</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.0594055593791</v>
+        <v>23.58532287941562</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1060834458126842</v>
+        <v>0.1058500929292176</v>
       </c>
       <c r="C19">
-        <v>33414.29506175394</v>
+        <v>33071.75932005123</v>
       </c>
       <c r="D19">
-        <v>37436.18006175394</v>
+        <v>37529.14932005124</v>
       </c>
       <c r="E19">
-        <v>-20513.315</v>
+        <v>-20077.81</v>
       </c>
       <c r="F19">
-        <v>7403.585000000001</v>
+        <v>7839.090000000001</v>
       </c>
       <c r="G19">
         <v>3381.7</v>
@@ -2851,28 +2851,28 @@
         <v>12076</v>
       </c>
       <c r="M19">
-        <v>512.0133424393132</v>
+        <v>542.1317743475081</v>
       </c>
       <c r="N19">
-        <v>11563.98665756069</v>
+        <v>11533.86822565249</v>
       </c>
       <c r="O19">
-        <v>4047.39533014624</v>
+        <v>4036.853878978372</v>
       </c>
       <c r="P19">
-        <v>7516.591327414446</v>
+        <v>7497.014346674119</v>
       </c>
       <c r="Q19">
-        <v>8033.091327414446</v>
+        <v>8013.514346674119</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1186042691134154</v>
+        <v>0.1192178863502733</v>
       </c>
       <c r="T19">
-        <v>1.0593908249041</v>
+        <v>1.068319703370246</v>
       </c>
       <c r="U19">
         <v>0.06915748822216712</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.58532287941562</v>
+        <v>22.27502716389253</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1058500929292177</v>
+        <v>0.1056167400457511</v>
       </c>
       <c r="C20">
-        <v>33071.75932005123</v>
+        <v>32729.68648889116</v>
       </c>
       <c r="D20">
-        <v>37529.14932005124</v>
+        <v>37622.58148889116</v>
       </c>
       <c r="E20">
-        <v>-20077.81</v>
+        <v>-19642.305</v>
       </c>
       <c r="F20">
-        <v>7839.09</v>
+        <v>8274.594999999999</v>
       </c>
       <c r="G20">
         <v>3381.7</v>
@@ -2933,28 +2933,28 @@
         <v>12076</v>
       </c>
       <c r="M20">
-        <v>542.1317743475081</v>
+        <v>572.2502062557029</v>
       </c>
       <c r="N20">
-        <v>11533.86822565249</v>
+        <v>11503.7497937443</v>
       </c>
       <c r="O20">
-        <v>4036.853878978372</v>
+        <v>4026.312427810504</v>
       </c>
       <c r="P20">
-        <v>7497.014346674119</v>
+        <v>7477.437365933793</v>
       </c>
       <c r="Q20">
-        <v>8013.514346674119</v>
+        <v>7993.937365933793</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1192178863502733</v>
+        <v>0.1198466546300166</v>
       </c>
       <c r="T20">
-        <v>1.068319703370246</v>
+        <v>1.077469047971359</v>
       </c>
       <c r="U20">
         <v>0.06915748822216712</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.27502716389253</v>
+        <v>21.10265731316135</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1056167400457511</v>
+        <v>0.1053833871622845</v>
       </c>
       <c r="C21">
-        <v>32729.68648889116</v>
+        <v>32388.08003427406</v>
       </c>
       <c r="D21">
-        <v>37622.58148889116</v>
+        <v>37716.48003427406</v>
       </c>
       <c r="E21">
-        <v>-19642.305</v>
+        <v>-19206.8</v>
       </c>
       <c r="F21">
-        <v>8274.594999999999</v>
+        <v>8710.1</v>
       </c>
       <c r="G21">
         <v>3381.7</v>
@@ -3015,28 +3015,28 @@
         <v>12076</v>
       </c>
       <c r="M21">
-        <v>572.2502062557029</v>
+        <v>602.3686381638979</v>
       </c>
       <c r="N21">
-        <v>11503.7497937443</v>
+        <v>11473.6313618361</v>
       </c>
       <c r="O21">
-        <v>4026.312427810504</v>
+        <v>4015.770976642636</v>
       </c>
       <c r="P21">
-        <v>7477.437365933793</v>
+        <v>7457.860385193466</v>
       </c>
       <c r="Q21">
-        <v>7993.937365933793</v>
+        <v>7974.360385193466</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1198466546300166</v>
+        <v>0.1204911421167535</v>
       </c>
       <c r="T21">
-        <v>1.077469047971359</v>
+        <v>1.0868471261875</v>
       </c>
       <c r="U21">
         <v>0.06915748822216712</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.10265731316135</v>
+        <v>20.04752444750328</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1053833871622845</v>
+        <v>0.1051500342788179</v>
       </c>
       <c r="C22">
-        <v>32388.08003427406</v>
+        <v>32046.94345688864</v>
       </c>
       <c r="D22">
-        <v>37716.48003427406</v>
+        <v>37810.84845688865</v>
       </c>
       <c r="E22">
-        <v>-19206.8</v>
+        <v>-18771.295</v>
       </c>
       <c r="F22">
-        <v>8710.1</v>
+        <v>9145.605000000001</v>
       </c>
       <c r="G22">
         <v>3381.7</v>
@@ -3097,28 +3097,28 @@
         <v>12076</v>
       </c>
       <c r="M22">
-        <v>602.3686381638979</v>
+        <v>632.4870700720928</v>
       </c>
       <c r="N22">
-        <v>11473.6313618361</v>
+        <v>11443.51292992791</v>
       </c>
       <c r="O22">
-        <v>4015.770976642636</v>
+        <v>4005.229525474767</v>
       </c>
       <c r="P22">
-        <v>7457.860385193466</v>
+        <v>7438.283404453139</v>
       </c>
       <c r="Q22">
-        <v>7974.360385193466</v>
+        <v>7954.783404453139</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1204911421167535</v>
+        <v>0.1211519457423951</v>
       </c>
       <c r="T22">
-        <v>1.0868471261875</v>
+        <v>1.096462624105315</v>
       </c>
       <c r="U22">
         <v>0.06915748822216712</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.04752444750328</v>
+        <v>19.0928804261936</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1051500342788179</v>
+        <v>0.1049166813953514</v>
       </c>
       <c r="C23">
-        <v>32046.94345688865</v>
+        <v>31706.28029254705</v>
       </c>
       <c r="D23">
-        <v>37810.84845688865</v>
+        <v>37905.69029254705</v>
       </c>
       <c r="E23">
-        <v>-18771.295</v>
+        <v>-18335.79</v>
       </c>
       <c r="F23">
-        <v>9145.605</v>
+        <v>9581.110000000001</v>
       </c>
       <c r="G23">
         <v>3381.7</v>
@@ -3179,28 +3179,28 @@
         <v>12076</v>
       </c>
       <c r="M23">
-        <v>632.4870700720927</v>
+        <v>662.6055019802876</v>
       </c>
       <c r="N23">
-        <v>11443.51292992791</v>
+        <v>11413.39449801971</v>
       </c>
       <c r="O23">
-        <v>4005.229525474767</v>
+        <v>3994.688074306899</v>
       </c>
       <c r="P23">
-        <v>7438.283404453139</v>
+        <v>7418.706423712812</v>
       </c>
       <c r="Q23">
-        <v>7954.783404453139</v>
+        <v>7935.206423712812</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1211519457423951</v>
+        <v>0.1218296930507455</v>
       </c>
       <c r="T23">
-        <v>1.096462624105315</v>
+        <v>1.106324673251792</v>
       </c>
       <c r="U23">
         <v>0.06915748822216712</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.0928804261936</v>
+        <v>18.22502222500298</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1049166813953514</v>
+        <v>0.1046833285118848</v>
       </c>
       <c r="C24">
-        <v>31706.28029254705</v>
+        <v>31366.0941126265</v>
       </c>
       <c r="D24">
-        <v>37905.69029254705</v>
+        <v>38001.0091126265</v>
       </c>
       <c r="E24">
-        <v>-18335.79</v>
+        <v>-17900.285</v>
       </c>
       <c r="F24">
-        <v>9581.110000000001</v>
+        <v>10016.615</v>
       </c>
       <c r="G24">
         <v>3381.7</v>
@@ -3261,28 +3261,28 @@
         <v>12076</v>
       </c>
       <c r="M24">
-        <v>662.6055019802876</v>
+        <v>692.7239338884825</v>
       </c>
       <c r="N24">
-        <v>11413.39449801971</v>
+        <v>11383.27606611152</v>
       </c>
       <c r="O24">
-        <v>3994.688074306899</v>
+        <v>3984.146623139031</v>
       </c>
       <c r="P24">
-        <v>7418.706423712812</v>
+        <v>7399.129442972486</v>
       </c>
       <c r="Q24">
-        <v>7935.206423712812</v>
+        <v>7915.629442972486</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1218296930507455</v>
+        <v>0.1225250441852868</v>
       </c>
       <c r="T24">
-        <v>1.106324673251792</v>
+        <v>1.116442879518956</v>
       </c>
       <c r="U24">
         <v>0.06915748822216712</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.22502222500298</v>
+        <v>17.43262995435068</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1046833285118848</v>
+        <v>0.1044499756284182</v>
       </c>
       <c r="C25">
-        <v>31366.0941126265</v>
+        <v>31026.38852451753</v>
       </c>
       <c r="D25">
-        <v>38001.0091126265</v>
+        <v>38096.80852451753</v>
       </c>
       <c r="E25">
-        <v>-17900.285</v>
+        <v>-17464.78</v>
       </c>
       <c r="F25">
-        <v>10016.615</v>
+        <v>10452.12</v>
       </c>
       <c r="G25">
         <v>3381.7</v>
@@ -3343,28 +3343,28 @@
         <v>12076</v>
       </c>
       <c r="M25">
-        <v>692.7239338884825</v>
+        <v>722.8423657966774</v>
       </c>
       <c r="N25">
-        <v>11383.27606611152</v>
+        <v>11353.15763420332</v>
       </c>
       <c r="O25">
-        <v>3984.146623139031</v>
+        <v>3973.605171971163</v>
       </c>
       <c r="P25">
-        <v>7399.129442972486</v>
+        <v>7379.552462232159</v>
       </c>
       <c r="Q25">
-        <v>7915.629442972486</v>
+        <v>7896.052462232159</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1225250441852868</v>
+        <v>0.123238694033895</v>
       </c>
       <c r="T25">
-        <v>1.116442879518956</v>
+        <v>1.126827354372099</v>
       </c>
       <c r="U25">
         <v>0.06915748822216712</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.43262995435068</v>
+        <v>16.7062703729194</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1044499756284182</v>
+        <v>0.1042166227449517</v>
       </c>
       <c r="C26">
-        <v>31026.38852451753</v>
+        <v>30687.16717207912</v>
       </c>
       <c r="D26">
-        <v>38096.80852451753</v>
+        <v>38193.09217207912</v>
       </c>
       <c r="E26">
-        <v>-17464.78</v>
+        <v>-17029.275</v>
       </c>
       <c r="F26">
-        <v>10452.12</v>
+        <v>10887.625</v>
       </c>
       <c r="G26">
         <v>3381.7</v>
@@ -3425,28 +3425,28 @@
         <v>12076</v>
       </c>
       <c r="M26">
-        <v>722.8423657966773</v>
+        <v>752.9607977048723</v>
       </c>
       <c r="N26">
-        <v>11353.15763420332</v>
+        <v>11323.03920229513</v>
       </c>
       <c r="O26">
-        <v>3973.605171971163</v>
+        <v>3963.063720803294</v>
       </c>
       <c r="P26">
-        <v>7379.552462232159</v>
+        <v>7359.975481491832</v>
       </c>
       <c r="Q26">
-        <v>7896.052462232159</v>
+        <v>7876.475481491832</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.123238694033895</v>
+        <v>0.1239713745451327</v>
       </c>
       <c r="T26">
-        <v>1.126827354372099</v>
+        <v>1.137488748554659</v>
       </c>
       <c r="U26">
         <v>0.06915748822216712</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.7062703729194</v>
+        <v>16.03801955800262</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1042166227449517</v>
+        <v>0.1039832698614851</v>
       </c>
       <c r="C27">
-        <v>30687.16717207912</v>
+        <v>30348.43373610069</v>
       </c>
       <c r="D27">
-        <v>38193.09217207912</v>
+        <v>38289.8637361007</v>
       </c>
       <c r="E27">
-        <v>-17029.275</v>
+        <v>-16593.77</v>
       </c>
       <c r="F27">
-        <v>10887.625</v>
+        <v>11323.13</v>
       </c>
       <c r="G27">
         <v>3381.7</v>
@@ -3507,28 +3507,28 @@
         <v>12076</v>
       </c>
       <c r="M27">
-        <v>752.9607977048723</v>
+        <v>783.0792296130672</v>
       </c>
       <c r="N27">
-        <v>11323.03920229513</v>
+        <v>11292.92077038693</v>
       </c>
       <c r="O27">
-        <v>3963.063720803294</v>
+        <v>3952.522269635426</v>
       </c>
       <c r="P27">
-        <v>7359.975481491832</v>
+        <v>7340.398500751506</v>
       </c>
       <c r="Q27">
-        <v>7876.475481491832</v>
+        <v>7856.898500751506</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1239713745451327</v>
+        <v>0.1247238572323498</v>
       </c>
       <c r="T27">
-        <v>1.137488748554659</v>
+        <v>1.148438288525937</v>
       </c>
       <c r="U27">
         <v>0.06915748822216712</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.03801955800262</v>
+        <v>15.4211726519256</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1039832698614851</v>
+        <v>0.1037499169780186</v>
       </c>
       <c r="C28">
-        <v>30348.43373610069</v>
+        <v>30010.19193477117</v>
       </c>
       <c r="D28">
-        <v>38289.8637361007</v>
+        <v>38387.12693477118</v>
       </c>
       <c r="E28">
-        <v>-16593.77</v>
+        <v>-16158.265</v>
       </c>
       <c r="F28">
-        <v>11323.13</v>
+        <v>11758.635</v>
       </c>
       <c r="G28">
         <v>3381.7</v>
@@ -3589,28 +3589,28 @@
         <v>12076</v>
       </c>
       <c r="M28">
-        <v>783.0792296130672</v>
+        <v>813.1976615212621</v>
       </c>
       <c r="N28">
-        <v>11292.92077038693</v>
+        <v>11262.80233847874</v>
       </c>
       <c r="O28">
-        <v>3952.522269635426</v>
+        <v>3941.980818467558</v>
       </c>
       <c r="P28">
-        <v>7340.398500751506</v>
+        <v>7320.821520011179</v>
       </c>
       <c r="Q28">
-        <v>7856.898500751506</v>
+        <v>7837.321520011179</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1247238572323498</v>
+        <v>0.1254969558836003</v>
       </c>
       <c r="T28">
-        <v>1.148438288525937</v>
+        <v>1.159687815893688</v>
       </c>
       <c r="U28">
         <v>0.06915748822216712</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.4211726519256</v>
+        <v>14.85001810926169</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1037499169780186</v>
+        <v>0.103516564094552</v>
       </c>
       <c r="C29">
-        <v>30010.19193477117</v>
+        <v>29672.44552415517</v>
       </c>
       <c r="D29">
-        <v>38387.12693477118</v>
+        <v>38484.88552415517</v>
       </c>
       <c r="E29">
-        <v>-16158.265</v>
+        <v>-15722.76</v>
       </c>
       <c r="F29">
-        <v>11758.635</v>
+        <v>12194.14</v>
       </c>
       <c r="G29">
         <v>3381.7</v>
@@ -3671,28 +3671,28 @@
         <v>12076</v>
       </c>
       <c r="M29">
-        <v>813.1976615212621</v>
+        <v>843.3160934294571</v>
       </c>
       <c r="N29">
-        <v>11262.80233847874</v>
+        <v>11232.68390657054</v>
       </c>
       <c r="O29">
-        <v>3941.980818467558</v>
+        <v>3931.43936729969</v>
       </c>
       <c r="P29">
-        <v>7320.821520011179</v>
+        <v>7301.244539270852</v>
       </c>
       <c r="Q29">
-        <v>7837.321520011179</v>
+        <v>7817.744539270852</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1254969558836003</v>
+        <v>0.1262915294973855</v>
       </c>
       <c r="T29">
-        <v>1.159687815893688</v>
+        <v>1.171249830132765</v>
       </c>
       <c r="U29">
         <v>0.06915748822216712</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.85001810926169</v>
+        <v>14.3196603196452</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.103516564094552</v>
+        <v>0.1032832112110854</v>
       </c>
       <c r="C30">
-        <v>29672.44552415517</v>
+        <v>29335.19829867652</v>
       </c>
       <c r="D30">
-        <v>38484.88552415517</v>
+        <v>38583.14329867653</v>
       </c>
       <c r="E30">
-        <v>-15722.76</v>
+        <v>-15287.255</v>
       </c>
       <c r="F30">
-        <v>12194.14</v>
+        <v>12629.645</v>
       </c>
       <c r="G30">
         <v>3381.7</v>
@@ -3753,28 +3753,28 @@
         <v>12076</v>
       </c>
       <c r="M30">
-        <v>843.3160934294571</v>
+        <v>873.4345253376521</v>
       </c>
       <c r="N30">
-        <v>11232.68390657054</v>
+        <v>11202.56547466235</v>
       </c>
       <c r="O30">
-        <v>3931.43936729969</v>
+        <v>3920.897916131822</v>
       </c>
       <c r="P30">
-        <v>7301.244539270852</v>
+        <v>7281.667558530526</v>
       </c>
       <c r="Q30">
-        <v>7817.744539270852</v>
+        <v>7798.167558530526</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1262915294973855</v>
+        <v>0.1271084854664886</v>
       </c>
       <c r="T30">
-        <v>1.171249830132765</v>
+        <v>1.183137534913789</v>
       </c>
       <c r="U30">
         <v>0.06915748822216712</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.3196603196452</v>
+        <v>13.8258789293126</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1032832112110854</v>
+        <v>0.1030498583276188</v>
       </c>
       <c r="C31">
-        <v>29335.19829867653</v>
+        <v>28998.45409160922</v>
       </c>
       <c r="D31">
-        <v>38583.14329867653</v>
+        <v>38681.90409160922</v>
       </c>
       <c r="E31">
-        <v>-15287.255</v>
+        <v>-14851.75</v>
       </c>
       <c r="F31">
-        <v>12629.645</v>
+        <v>13065.15</v>
       </c>
       <c r="G31">
         <v>3381.7</v>
@@ -3835,28 +3835,28 @@
         <v>12076</v>
       </c>
       <c r="M31">
-        <v>873.4345253376517</v>
+        <v>903.5529572458468</v>
       </c>
       <c r="N31">
-        <v>11202.56547466235</v>
+        <v>11172.44704275415</v>
       </c>
       <c r="O31">
-        <v>3920.897916131822</v>
+        <v>3910.356464963953</v>
       </c>
       <c r="P31">
-        <v>7281.667558530526</v>
+        <v>7262.090577790199</v>
       </c>
       <c r="Q31">
-        <v>7798.167558530526</v>
+        <v>7778.590577790199</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1271084854664886</v>
+        <v>0.1279487830347089</v>
       </c>
       <c r="T31">
-        <v>1.183137534913789</v>
+        <v>1.195364888402841</v>
       </c>
       <c r="U31">
         <v>0.06915748822216712</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.82587892931261</v>
+        <v>13.36501629833552</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1030498583276188</v>
+        <v>0.1028165054441522</v>
       </c>
       <c r="C32">
-        <v>28998.45409160922</v>
+        <v>28662.21677557593</v>
       </c>
       <c r="D32">
-        <v>38681.90409160922</v>
+        <v>38781.17177557593</v>
       </c>
       <c r="E32">
-        <v>-14851.75</v>
+        <v>-14416.245</v>
       </c>
       <c r="F32">
-        <v>13065.15</v>
+        <v>13500.655</v>
       </c>
       <c r="G32">
         <v>3381.7</v>
@@ -3917,28 +3917,28 @@
         <v>12076</v>
       </c>
       <c r="M32">
-        <v>903.5529572458468</v>
+        <v>933.6713891540417</v>
       </c>
       <c r="N32">
-        <v>11172.44704275415</v>
+        <v>11142.32861084596</v>
       </c>
       <c r="O32">
-        <v>3910.356464963953</v>
+        <v>3899.815013796085</v>
       </c>
       <c r="P32">
-        <v>7262.090577790199</v>
+        <v>7242.513597049872</v>
       </c>
       <c r="Q32">
-        <v>7778.590577790199</v>
+        <v>7759.013597049872</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1279487830347089</v>
+        <v>0.128813437054182</v>
       </c>
       <c r="T32">
-        <v>1.195364888402841</v>
+        <v>1.207946657935055</v>
       </c>
       <c r="U32">
         <v>0.06915748822216712</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.36501629833552</v>
+        <v>12.9338867403247</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1028165054441522</v>
+        <v>0.1025831525606857</v>
       </c>
       <c r="C33">
-        <v>28662.21677557593</v>
+        <v>28326.49026305413</v>
       </c>
       <c r="D33">
-        <v>38781.17177557593</v>
+        <v>38880.95026305413</v>
       </c>
       <c r="E33">
-        <v>-14416.245</v>
+        <v>-13980.74</v>
       </c>
       <c r="F33">
-        <v>13500.655</v>
+        <v>13936.16</v>
       </c>
       <c r="G33">
         <v>3381.7</v>
@@ -3999,28 +3999,28 @@
         <v>12076</v>
       </c>
       <c r="M33">
-        <v>933.6713891540417</v>
+        <v>963.7898210622366</v>
       </c>
       <c r="N33">
-        <v>11142.32861084596</v>
+        <v>11112.21017893776</v>
       </c>
       <c r="O33">
-        <v>3899.815013796085</v>
+        <v>3889.273562628217</v>
       </c>
       <c r="P33">
-        <v>7242.513597049872</v>
+        <v>7222.936616309546</v>
       </c>
       <c r="Q33">
-        <v>7759.013597049872</v>
+        <v>7739.436616309546</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.128813437054182</v>
+        <v>0.1297035220742278</v>
       </c>
       <c r="T33">
-        <v>1.207946657935055</v>
+        <v>1.220898479512334</v>
       </c>
       <c r="U33">
         <v>0.06915748822216712</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>12.9338867403247</v>
+        <v>12.52970277968955</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1025831525606857</v>
+        <v>0.1023497996772191</v>
       </c>
       <c r="C34">
-        <v>28326.49026305413</v>
+        <v>27991.27850689022</v>
       </c>
       <c r="D34">
-        <v>38880.95026305413</v>
+        <v>38981.24350689023</v>
       </c>
       <c r="E34">
-        <v>-13980.74</v>
+        <v>-13545.235</v>
       </c>
       <c r="F34">
-        <v>13936.16</v>
+        <v>14371.665</v>
       </c>
       <c r="G34">
         <v>3381.7</v>
@@ -4081,28 +4081,28 @@
         <v>12076</v>
       </c>
       <c r="M34">
-        <v>963.7898210622366</v>
+        <v>993.9082529704315</v>
       </c>
       <c r="N34">
-        <v>11112.21017893776</v>
+        <v>11082.09174702957</v>
       </c>
       <c r="O34">
-        <v>3889.273562628217</v>
+        <v>3878.732111460349</v>
       </c>
       <c r="P34">
-        <v>7222.936616309546</v>
+        <v>7203.359635569219</v>
       </c>
       <c r="Q34">
-        <v>7739.436616309546</v>
+        <v>7719.859635569219</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1297035220742278</v>
+        <v>0.1306201767963646</v>
       </c>
       <c r="T34">
-        <v>1.220898479512334</v>
+        <v>1.234236922629232</v>
       </c>
       <c r="U34">
         <v>0.06915748822216712</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.52970277968955</v>
+        <v>12.15001481666866</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1023497996772191</v>
+        <v>0.1021164467937525</v>
       </c>
       <c r="C35">
-        <v>27991.27850689022</v>
+        <v>27656.58550082147</v>
       </c>
       <c r="D35">
-        <v>38981.24350689023</v>
+        <v>39082.05550082147</v>
       </c>
       <c r="E35">
-        <v>-13545.235</v>
+        <v>-13109.73</v>
       </c>
       <c r="F35">
-        <v>14371.665</v>
+        <v>14807.17</v>
       </c>
       <c r="G35">
         <v>3381.7</v>
@@ -4163,28 +4163,28 @@
         <v>12076</v>
       </c>
       <c r="M35">
-        <v>993.9082529704315</v>
+        <v>1024.026684878626</v>
       </c>
       <c r="N35">
-        <v>11082.09174702957</v>
+        <v>11051.97331512137</v>
       </c>
       <c r="O35">
-        <v>3878.732111460349</v>
+        <v>3868.190660292481</v>
       </c>
       <c r="P35">
-        <v>7203.359635569219</v>
+        <v>7183.782654828892</v>
       </c>
       <c r="Q35">
-        <v>7719.859635569219</v>
+        <v>7700.282654828892</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1306201767963646</v>
+        <v>0.1315646089343236</v>
       </c>
       <c r="T35">
-        <v>1.234236922629232</v>
+        <v>1.247979560992098</v>
       </c>
       <c r="U35">
         <v>0.06915748822216712</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.15001481666866</v>
+        <v>11.79266143970781</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1021164467937525</v>
+        <v>0.101883093910286</v>
       </c>
       <c r="C36">
-        <v>27656.58550082147</v>
+        <v>27322.4152800061</v>
       </c>
       <c r="D36">
-        <v>39082.05550082147</v>
+        <v>39183.3902800061</v>
       </c>
       <c r="E36">
-        <v>-13109.73</v>
+        <v>-12674.225</v>
       </c>
       <c r="F36">
-        <v>14807.17</v>
+        <v>15242.675</v>
       </c>
       <c r="G36">
         <v>3381.7</v>
@@ -4245,28 +4245,28 @@
         <v>12076</v>
       </c>
       <c r="M36">
-        <v>1024.026684878626</v>
+        <v>1054.145116786821</v>
       </c>
       <c r="N36">
-        <v>11051.97331512137</v>
+        <v>11021.85488321318</v>
       </c>
       <c r="O36">
-        <v>3868.190660292481</v>
+        <v>3857.649209124612</v>
       </c>
       <c r="P36">
-        <v>7183.782654828892</v>
+        <v>7164.205674088566</v>
       </c>
       <c r="Q36">
-        <v>7700.282654828892</v>
+        <v>7680.705674088566</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1315646089343236</v>
+        <v>0.1325381005226815</v>
       </c>
       <c r="T36">
-        <v>1.247979560992098</v>
+        <v>1.262145049766129</v>
       </c>
       <c r="U36">
         <v>0.06915748822216712</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.79266143970781</v>
+        <v>11.45572825571616</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.101883093910286</v>
+        <v>0.1016497410268194</v>
       </c>
       <c r="C37">
-        <v>27322.4152800061</v>
+        <v>26988.77192156179</v>
       </c>
       <c r="D37">
-        <v>39183.3902800061</v>
+        <v>39285.25192156179</v>
       </c>
       <c r="E37">
-        <v>-12674.225</v>
+        <v>-12238.72</v>
       </c>
       <c r="F37">
-        <v>15242.675</v>
+        <v>15678.18</v>
       </c>
       <c r="G37">
         <v>3381.7</v>
@@ -4327,28 +4327,28 @@
         <v>12076</v>
       </c>
       <c r="M37">
-        <v>1054.145116786821</v>
+        <v>1084.263548695016</v>
       </c>
       <c r="N37">
-        <v>11021.85488321318</v>
+        <v>10991.73645130498</v>
       </c>
       <c r="O37">
-        <v>3857.649209124612</v>
+        <v>3847.107757956744</v>
       </c>
       <c r="P37">
-        <v>7164.205674088566</v>
+        <v>7144.628693348239</v>
       </c>
       <c r="Q37">
-        <v>7680.705674088566</v>
+        <v>7661.128693348239</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1325381005226815</v>
+        <v>0.1335420137231755</v>
       </c>
       <c r="T37">
-        <v>1.262145049766129</v>
+        <v>1.276753210064348</v>
       </c>
       <c r="U37">
         <v>0.06915748822216712</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.45572825571616</v>
+        <v>11.13751358194627</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1016497410268194</v>
+        <v>0.1014163881433528</v>
       </c>
       <c r="C38">
-        <v>26988.77192156178</v>
+        <v>26655.65954511239</v>
       </c>
       <c r="D38">
-        <v>39285.25192156179</v>
+        <v>39387.64454511239</v>
       </c>
       <c r="E38">
-        <v>-12238.72</v>
+        <v>-11803.215</v>
       </c>
       <c r="F38">
-        <v>15678.18</v>
+        <v>16113.685</v>
       </c>
       <c r="G38">
         <v>3381.7</v>
@@ -4409,28 +4409,28 @@
         <v>12076</v>
       </c>
       <c r="M38">
-        <v>1084.263548695016</v>
+        <v>1114.381980603211</v>
       </c>
       <c r="N38">
-        <v>10991.73645130498</v>
+        <v>10961.61801939679</v>
       </c>
       <c r="O38">
-        <v>3847.107757956744</v>
+        <v>3836.566306788876</v>
       </c>
       <c r="P38">
-        <v>7144.628693348239</v>
+        <v>7125.051712607912</v>
       </c>
       <c r="Q38">
-        <v>7661.128693348239</v>
+        <v>7641.551712607912</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1335420137231755</v>
+        <v>0.1345777971840026</v>
       </c>
       <c r="T38">
-        <v>1.276753210064348</v>
+        <v>1.291825121483145</v>
       </c>
       <c r="U38">
         <v>0.06915748822216712</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.13751358194627</v>
+        <v>10.83649970135312</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1014163881433528</v>
+        <v>0.1011830352598863</v>
       </c>
       <c r="C39">
-        <v>26655.65954511239</v>
+        <v>26323.08231334337</v>
       </c>
       <c r="D39">
-        <v>39387.64454511239</v>
+        <v>39490.57231334337</v>
       </c>
       <c r="E39">
-        <v>-11803.215</v>
+        <v>-11367.71</v>
       </c>
       <c r="F39">
-        <v>16113.685</v>
+        <v>16549.19</v>
       </c>
       <c r="G39">
         <v>3381.7</v>
@@ -4491,28 +4491,28 @@
         <v>12076</v>
       </c>
       <c r="M39">
-        <v>1114.381980603211</v>
+        <v>1144.500412511406</v>
       </c>
       <c r="N39">
-        <v>10961.61801939679</v>
+        <v>10931.49958748859</v>
       </c>
       <c r="O39">
-        <v>3836.566306788876</v>
+        <v>3826.024855621008</v>
       </c>
       <c r="P39">
-        <v>7125.051712607912</v>
+        <v>7105.474731867585</v>
       </c>
       <c r="Q39">
-        <v>7641.551712607912</v>
+        <v>7621.974731867585</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1345777971840026</v>
+        <v>0.1356469930145339</v>
       </c>
       <c r="T39">
-        <v>1.291825121483145</v>
+        <v>1.307383223592872</v>
       </c>
       <c r="U39">
         <v>0.06915748822216712</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.83649970135312</v>
+        <v>10.55132865658067</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1011830352598863</v>
+        <v>0.1009496823764197</v>
       </c>
       <c r="C40">
-        <v>26323.08231334337</v>
+        <v>25991.04443256588</v>
       </c>
       <c r="D40">
-        <v>39490.57231334337</v>
+        <v>39594.03943256589</v>
       </c>
       <c r="E40">
-        <v>-11367.71</v>
+        <v>-10932.205</v>
       </c>
       <c r="F40">
-        <v>16549.19</v>
+        <v>16984.695</v>
       </c>
       <c r="G40">
         <v>3381.7</v>
@@ -4573,28 +4573,28 @@
         <v>12076</v>
       </c>
       <c r="M40">
-        <v>1144.500412511406</v>
+        <v>1174.618844419601</v>
       </c>
       <c r="N40">
-        <v>10931.49958748859</v>
+        <v>10901.3811555804</v>
       </c>
       <c r="O40">
-        <v>3826.024855621008</v>
+        <v>3815.483404453139</v>
       </c>
       <c r="P40">
-        <v>7105.474731867585</v>
+        <v>7085.897751127259</v>
       </c>
       <c r="Q40">
-        <v>7621.974731867585</v>
+        <v>7602.397751127259</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1356469930145339</v>
+        <v>0.1367512444460661</v>
       </c>
       <c r="T40">
-        <v>1.307383223592872</v>
+        <v>1.323451427411114</v>
       </c>
       <c r="U40">
         <v>0.06915748822216712</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.55132865658067</v>
+        <v>10.2807817679504</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1009496823764197</v>
+        <v>0.1007163294929531</v>
       </c>
       <c r="C41">
-        <v>25991.04443256588</v>
+        <v>25659.55015328985</v>
       </c>
       <c r="D41">
-        <v>39594.03943256589</v>
+        <v>39698.05015328985</v>
       </c>
       <c r="E41">
-        <v>-10932.205</v>
+        <v>-10496.7</v>
       </c>
       <c r="F41">
-        <v>16984.695</v>
+        <v>17420.2</v>
       </c>
       <c r="G41">
         <v>3381.7</v>
@@ -4655,28 +4655,28 @@
         <v>12076</v>
       </c>
       <c r="M41">
-        <v>1174.618844419601</v>
+        <v>1204.737276327796</v>
       </c>
       <c r="N41">
-        <v>10901.3811555804</v>
+        <v>10871.2627236722</v>
       </c>
       <c r="O41">
-        <v>3815.483404453139</v>
+        <v>3804.941953285271</v>
       </c>
       <c r="P41">
-        <v>7085.897751127259</v>
+        <v>7066.320770386932</v>
       </c>
       <c r="Q41">
-        <v>7602.397751127259</v>
+        <v>7582.820770386932</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1367512444460661</v>
+        <v>0.1378923042586495</v>
       </c>
       <c r="T41">
-        <v>1.323451427411114</v>
+        <v>1.340055238023297</v>
       </c>
       <c r="U41">
         <v>0.06915748822216712</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.2807817679504</v>
+        <v>10.02376222375164</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1007163294929531</v>
+        <v>0.1004829766094866</v>
       </c>
       <c r="C42">
-        <v>25659.55015328985</v>
+        <v>25328.60377080587</v>
       </c>
       <c r="D42">
-        <v>39698.05015328985</v>
+        <v>39802.60877080588</v>
       </c>
       <c r="E42">
-        <v>-10496.7</v>
+        <v>-10061.195</v>
       </c>
       <c r="F42">
-        <v>17420.2</v>
+        <v>17855.705</v>
       </c>
       <c r="G42">
         <v>3381.7</v>
@@ -4737,28 +4737,28 @@
         <v>12076</v>
       </c>
       <c r="M42">
-        <v>1204.737276327796</v>
+        <v>1234.855708235991</v>
       </c>
       <c r="N42">
-        <v>10871.2627236722</v>
+        <v>10841.14429176401</v>
       </c>
       <c r="O42">
-        <v>3804.941953285271</v>
+        <v>3794.400502117403</v>
       </c>
       <c r="P42">
-        <v>7066.320770386932</v>
+        <v>7046.743789646605</v>
       </c>
       <c r="Q42">
-        <v>7582.820770386932</v>
+        <v>7563.243789646605</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1378923042586495</v>
+        <v>0.1390720440648797</v>
       </c>
       <c r="T42">
-        <v>1.340055238023297</v>
+        <v>1.357221889673182</v>
       </c>
       <c r="U42">
         <v>0.06915748822216712</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.02376222375164</v>
+        <v>9.779280218294282</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1004829766094866</v>
+        <v>0.10024962372602</v>
       </c>
       <c r="C43">
-        <v>25328.60377080587</v>
+        <v>24998.20962577677</v>
       </c>
       <c r="D43">
-        <v>39802.60877080588</v>
+        <v>39907.71962577677</v>
       </c>
       <c r="E43">
-        <v>-10061.195</v>
+        <v>-9625.689999999999</v>
       </c>
       <c r="F43">
-        <v>17855.705</v>
+        <v>18291.21</v>
       </c>
       <c r="G43">
         <v>3381.7</v>
@@ -4819,28 +4819,28 @@
         <v>12076</v>
       </c>
       <c r="M43">
-        <v>1234.855708235991</v>
+        <v>1264.974140144186</v>
       </c>
       <c r="N43">
-        <v>10841.14429176401</v>
+        <v>10811.02585985581</v>
       </c>
       <c r="O43">
-        <v>3794.400502117403</v>
+        <v>3783.859050949535</v>
       </c>
       <c r="P43">
-        <v>7046.743789646605</v>
+        <v>7027.166808906279</v>
       </c>
       <c r="Q43">
-        <v>7563.243789646605</v>
+        <v>7543.666808906279</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1390720440648797</v>
+        <v>0.1402924645540834</v>
       </c>
       <c r="T43">
-        <v>1.357221889673182</v>
+        <v>1.374980494828235</v>
       </c>
       <c r="U43">
         <v>0.06915748822216712</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.779280218294282</v>
+        <v>9.546440213096799</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.10024962372602</v>
+        <v>0.1000162708425534</v>
       </c>
       <c r="C44">
-        <v>24998.20962577676</v>
+        <v>24668.37210483796</v>
       </c>
       <c r="D44">
-        <v>39907.71962577676</v>
+        <v>40013.38710483796</v>
       </c>
       <c r="E44">
-        <v>-9625.690000000002</v>
+        <v>-9190.185000000001</v>
       </c>
       <c r="F44">
-        <v>18291.21</v>
+        <v>18726.715</v>
       </c>
       <c r="G44">
         <v>3381.7</v>
@@ -4901,28 +4901,28 @@
         <v>12076</v>
       </c>
       <c r="M44">
-        <v>1264.974140144185</v>
+        <v>1295.09257205238</v>
       </c>
       <c r="N44">
-        <v>10811.02585985581</v>
+        <v>10780.90742794762</v>
       </c>
       <c r="O44">
-        <v>3783.859050949535</v>
+        <v>3773.317599781667</v>
       </c>
       <c r="P44">
-        <v>7027.166808906279</v>
+        <v>7007.589828165952</v>
       </c>
       <c r="Q44">
-        <v>7543.666808906279</v>
+        <v>7524.089828165952</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1402924645540834</v>
+        <v>0.1415557068148381</v>
       </c>
       <c r="T44">
-        <v>1.374980494828235</v>
+        <v>1.393362208936097</v>
       </c>
       <c r="U44">
         <v>0.06915748822216712</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.546440213096801</v>
+        <v>9.324429975582921</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1000162708425534</v>
+        <v>0.09978291795908686</v>
       </c>
       <c r="C45">
-        <v>24668.37210483796</v>
+        <v>24339.09564120796</v>
       </c>
       <c r="D45">
-        <v>40013.38710483796</v>
+        <v>40119.61564120797</v>
       </c>
       <c r="E45">
-        <v>-9190.185000000001</v>
+        <v>-8754.68</v>
       </c>
       <c r="F45">
-        <v>18726.715</v>
+        <v>19162.22</v>
       </c>
       <c r="G45">
         <v>3381.7</v>
@@ -4983,28 +4983,28 @@
         <v>12076</v>
       </c>
       <c r="M45">
-        <v>1295.09257205238</v>
+        <v>1325.211003960575</v>
       </c>
       <c r="N45">
-        <v>10780.90742794762</v>
+        <v>10750.78899603942</v>
       </c>
       <c r="O45">
-        <v>3773.317599781667</v>
+        <v>3762.776148613798</v>
       </c>
       <c r="P45">
-        <v>7007.589828165952</v>
+        <v>6988.012847425625</v>
       </c>
       <c r="Q45">
-        <v>7524.089828165952</v>
+        <v>7504.512847425625</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1415557068148381</v>
+        <v>0.1428640648706197</v>
       </c>
       <c r="T45">
-        <v>1.393362208936097</v>
+        <v>1.412400412833525</v>
       </c>
       <c r="U45">
         <v>0.06915748822216712</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.324429975582921</v>
+        <v>9.11251111250149</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09978291795908686</v>
+        <v>0.09954956507562029</v>
       </c>
       <c r="C46">
-        <v>24339.09564120796</v>
+        <v>24010.38471530824</v>
       </c>
       <c r="D46">
-        <v>40119.61564120797</v>
+        <v>40226.40971530825</v>
       </c>
       <c r="E46">
-        <v>-8754.68</v>
+        <v>-8319.174999999999</v>
       </c>
       <c r="F46">
-        <v>19162.22</v>
+        <v>19597.725</v>
       </c>
       <c r="G46">
         <v>3381.7</v>
@@ -5065,28 +5065,28 @@
         <v>12076</v>
       </c>
       <c r="M46">
-        <v>1325.211003960575</v>
+        <v>1355.32943586877</v>
       </c>
       <c r="N46">
-        <v>10750.78899603942</v>
+        <v>10720.67056413123</v>
       </c>
       <c r="O46">
-        <v>3762.776148613798</v>
+        <v>3752.23469744593</v>
       </c>
       <c r="P46">
-        <v>6988.012847425625</v>
+        <v>6968.435866685299</v>
       </c>
       <c r="Q46">
-        <v>7504.512847425625</v>
+        <v>7484.935866685299</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1428640648706197</v>
+        <v>0.1442199995829753</v>
       </c>
       <c r="T46">
-        <v>1.412400412833525</v>
+        <v>1.432130915054496</v>
       </c>
       <c r="U46">
         <v>0.06915748822216712</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.11251111250149</v>
+        <v>8.910010865557012</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09954956507562029</v>
+        <v>0.09931621219215372</v>
       </c>
       <c r="C47">
-        <v>24010.38471530824</v>
+        <v>23682.24385539319</v>
       </c>
       <c r="D47">
-        <v>40226.40971530825</v>
+        <v>40333.77385539319</v>
       </c>
       <c r="E47">
-        <v>-8319.174999999999</v>
+        <v>-7883.670000000002</v>
       </c>
       <c r="F47">
-        <v>19597.725</v>
+        <v>20033.23</v>
       </c>
       <c r="G47">
         <v>3381.7</v>
@@ -5147,28 +5147,28 @@
         <v>12076</v>
       </c>
       <c r="M47">
-        <v>1355.32943586877</v>
+        <v>1385.447867776965</v>
       </c>
       <c r="N47">
-        <v>10720.67056413123</v>
+        <v>10690.55213222303</v>
       </c>
       <c r="O47">
-        <v>3752.23469744593</v>
+        <v>3741.693246278062</v>
       </c>
       <c r="P47">
-        <v>6968.435866685299</v>
+        <v>6948.858885944972</v>
       </c>
       <c r="Q47">
-        <v>7484.935866685299</v>
+        <v>7465.358885944972</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1442199995829753</v>
+        <v>0.1456261540994921</v>
       </c>
       <c r="T47">
-        <v>1.432130915054496</v>
+        <v>1.452592176616985</v>
       </c>
       <c r="U47">
         <v>0.06915748822216712</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.910010865557012</v>
+        <v>8.71631497717534</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09931621219215372</v>
+        <v>0.09954110930868713</v>
       </c>
       <c r="C48">
-        <v>23682.24385539319</v>
+        <v>23143.25517689351</v>
       </c>
       <c r="D48">
-        <v>40333.77385539319</v>
+        <v>40230.29017689351</v>
       </c>
       <c r="E48">
-        <v>-7883.670000000002</v>
+        <v>-7448.165000000001</v>
       </c>
       <c r="F48">
-        <v>20033.23</v>
+        <v>20468.735</v>
       </c>
       <c r="G48">
         <v>3381.7</v>
@@ -5229,45 +5229,45 @@
         <v>12076</v>
       </c>
       <c r="M48">
-        <v>1385.447867776965</v>
+        <v>1446.26940218516</v>
       </c>
       <c r="N48">
-        <v>10690.55213222303</v>
+        <v>10629.73059781484</v>
       </c>
       <c r="O48">
-        <v>3741.693246278062</v>
+        <v>3720.405709235194</v>
       </c>
       <c r="P48">
-        <v>6948.858885944972</v>
+        <v>6909.324888579646</v>
       </c>
       <c r="Q48">
-        <v>7465.358885944972</v>
+        <v>7425.824888579646</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1456261540994921</v>
+        <v>0.1470853710505945</v>
       </c>
       <c r="T48">
-        <v>1.452592176616985</v>
+        <v>1.473825561257303</v>
       </c>
       <c r="U48">
-        <v>0.06915748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V48">
         <v>0.35</v>
       </c>
       <c r="W48">
-        <v>0.04495236734440863</v>
+        <v>0.04592736734440862</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y48">
-        <v>8.71631497717534</v>
+        <v>8.349758338076187</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09954110930868713</v>
+        <v>0.09931750642522058</v>
       </c>
       <c r="C49">
-        <v>23143.25517689351</v>
+        <v>22810.63680673392</v>
       </c>
       <c r="D49">
-        <v>40230.29017689351</v>
+        <v>40333.17680673393</v>
       </c>
       <c r="E49">
-        <v>-7448.165000000001</v>
+        <v>-7012.66</v>
       </c>
       <c r="F49">
-        <v>20468.735</v>
+        <v>20904.24</v>
       </c>
       <c r="G49">
         <v>3381.7</v>
@@ -5311,28 +5311,28 @@
         <v>12076</v>
       </c>
       <c r="M49">
-        <v>1446.26940218516</v>
+        <v>1477.041091593355</v>
       </c>
       <c r="N49">
-        <v>10629.73059781484</v>
+        <v>10598.95890840664</v>
       </c>
       <c r="O49">
-        <v>3720.405709235194</v>
+        <v>3709.635617942326</v>
       </c>
       <c r="P49">
-        <v>6909.324888579646</v>
+        <v>6889.323290464319</v>
       </c>
       <c r="Q49">
-        <v>7425.824888579646</v>
+        <v>7405.823290464319</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1470853710505945</v>
+        <v>0.1486007117305854</v>
       </c>
       <c r="T49">
-        <v>1.473825561257303</v>
+        <v>1.495875614537634</v>
       </c>
       <c r="U49">
         <v>0.07065748822216711</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.349758338076187</v>
+        <v>8.175805039366267</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09931750642522058</v>
+        <v>0.09909390354175399</v>
       </c>
       <c r="C50">
-        <v>22810.63680673393</v>
+        <v>22478.5460390437</v>
       </c>
       <c r="D50">
-        <v>40333.17680673393</v>
+        <v>40436.59103904371</v>
       </c>
       <c r="E50">
-        <v>-7012.660000000003</v>
+        <v>-6577.155000000002</v>
       </c>
       <c r="F50">
-        <v>20904.24</v>
+        <v>21339.745</v>
       </c>
       <c r="G50">
         <v>3381.7</v>
@@ -5393,28 +5393,28 @@
         <v>12076</v>
       </c>
       <c r="M50">
-        <v>1477.041091593354</v>
+        <v>1507.812781001549</v>
       </c>
       <c r="N50">
-        <v>10598.95890840665</v>
+        <v>10568.18721899845</v>
       </c>
       <c r="O50">
-        <v>3709.635617942326</v>
+        <v>3698.865526649457</v>
       </c>
       <c r="P50">
-        <v>6889.323290464321</v>
+        <v>6869.321692348993</v>
       </c>
       <c r="Q50">
-        <v>7405.823290464321</v>
+        <v>7385.821692348993</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1486007117305854</v>
+        <v>0.1501754775352819</v>
       </c>
       <c r="T50">
-        <v>1.495875614537634</v>
+        <v>1.518790375789742</v>
       </c>
       <c r="U50">
         <v>0.07065748822216711</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.175805039366267</v>
+        <v>8.008951875297567</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09909390354175399</v>
+        <v>0.09887030065828742</v>
       </c>
       <c r="C51">
-        <v>22478.5460390437</v>
+        <v>22146.98694257199</v>
       </c>
       <c r="D51">
-        <v>40436.59103904371</v>
+        <v>40540.53694257199</v>
       </c>
       <c r="E51">
-        <v>-6577.155000000002</v>
+        <v>-6141.650000000001</v>
       </c>
       <c r="F51">
-        <v>21339.745</v>
+        <v>21775.25</v>
       </c>
       <c r="G51">
         <v>3381.7</v>
@@ -5475,28 +5475,28 @@
         <v>12076</v>
       </c>
       <c r="M51">
-        <v>1507.812781001549</v>
+        <v>1538.584470409744</v>
       </c>
       <c r="N51">
-        <v>10568.18721899845</v>
+        <v>10537.41552959026</v>
       </c>
       <c r="O51">
-        <v>3698.865526649457</v>
+        <v>3688.095435356589</v>
       </c>
       <c r="P51">
-        <v>6869.321692348993</v>
+        <v>6849.320094233667</v>
       </c>
       <c r="Q51">
-        <v>7385.821692348993</v>
+        <v>7365.820094233667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1501754775352819</v>
+        <v>0.1518132339721662</v>
       </c>
       <c r="T51">
-        <v>1.518790375789742</v>
+        <v>1.542621727491935</v>
       </c>
       <c r="U51">
         <v>0.07065748822216711</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.008951875297567</v>
+        <v>7.848772837791616</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09887030065828742</v>
+        <v>0.09864669777482085</v>
       </c>
       <c r="C52">
-        <v>22146.98694257199</v>
+        <v>21815.96362801212</v>
       </c>
       <c r="D52">
-        <v>40540.53694257199</v>
+        <v>40645.01862801213</v>
       </c>
       <c r="E52">
-        <v>-6141.650000000001</v>
+        <v>-5706.145</v>
       </c>
       <c r="F52">
-        <v>21775.25</v>
+        <v>22210.755</v>
       </c>
       <c r="G52">
         <v>3381.7</v>
@@ -5557,28 +5557,28 @@
         <v>12076</v>
       </c>
       <c r="M52">
-        <v>1538.584470409744</v>
+        <v>1569.356159817939</v>
       </c>
       <c r="N52">
-        <v>10537.41552959026</v>
+        <v>10506.64384018206</v>
       </c>
       <c r="O52">
-        <v>3688.095435356589</v>
+        <v>3677.325344063721</v>
       </c>
       <c r="P52">
-        <v>6849.320094233667</v>
+        <v>6829.31849611834</v>
       </c>
       <c r="Q52">
-        <v>7365.820094233667</v>
+        <v>7345.81849611834</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1518132339721662</v>
+        <v>0.153517837610556</v>
       </c>
       <c r="T52">
-        <v>1.542621727491935</v>
+        <v>1.56742578742687</v>
       </c>
       <c r="U52">
         <v>0.07065748822216711</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.848772837791616</v>
+        <v>7.694875331168252</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09864669777482085</v>
+        <v>0.0984230948913543</v>
       </c>
       <c r="C53">
-        <v>21815.96362801212</v>
+        <v>21485.48024854348</v>
       </c>
       <c r="D53">
-        <v>40645.01862801213</v>
+        <v>40750.04024854349</v>
       </c>
       <c r="E53">
-        <v>-5706.145</v>
+        <v>-5270.639999999999</v>
       </c>
       <c r="F53">
-        <v>22210.755</v>
+        <v>22646.26</v>
       </c>
       <c r="G53">
         <v>3381.7</v>
@@ -5639,28 +5639,28 @@
         <v>12076</v>
       </c>
       <c r="M53">
-        <v>1569.356159817939</v>
+        <v>1600.127849226134</v>
       </c>
       <c r="N53">
-        <v>10506.64384018206</v>
+        <v>10475.87215077387</v>
       </c>
       <c r="O53">
-        <v>3677.325344063721</v>
+        <v>3666.555252770853</v>
       </c>
       <c r="P53">
-        <v>6829.31849611834</v>
+        <v>6809.316898003013</v>
       </c>
       <c r="Q53">
-        <v>7345.81849611834</v>
+        <v>7325.816898003013</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.153517837610556</v>
+        <v>0.1552934664005454</v>
       </c>
       <c r="T53">
-        <v>1.56742578742687</v>
+        <v>1.593263349859095</v>
       </c>
       <c r="U53">
         <v>0.07065748822216711</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.694875331168252</v>
+        <v>7.546896959415015</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0984230948913543</v>
+        <v>0.09819949200788772</v>
       </c>
       <c r="C54">
-        <v>21485.48024854348</v>
+        <v>21155.54100038188</v>
       </c>
       <c r="D54">
-        <v>40750.04024854349</v>
+        <v>40855.60600038189</v>
       </c>
       <c r="E54">
-        <v>-5270.639999999999</v>
+        <v>-4835.135000000002</v>
       </c>
       <c r="F54">
-        <v>22646.26</v>
+        <v>23081.765</v>
       </c>
       <c r="G54">
         <v>3381.7</v>
@@ -5721,28 +5721,28 @@
         <v>12076</v>
       </c>
       <c r="M54">
-        <v>1600.127849226134</v>
+        <v>1630.899538634329</v>
       </c>
       <c r="N54">
-        <v>10475.87215077387</v>
+        <v>10445.10046136567</v>
       </c>
       <c r="O54">
-        <v>3666.555252770853</v>
+        <v>3655.785161477985</v>
       </c>
       <c r="P54">
-        <v>6809.316898003013</v>
+        <v>6789.315299887687</v>
       </c>
       <c r="Q54">
-        <v>7325.816898003013</v>
+        <v>7305.815299887687</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1552934664005454</v>
+        <v>0.1571446538624493</v>
       </c>
       <c r="T54">
-        <v>1.593263349859095</v>
+        <v>1.620200383033116</v>
       </c>
       <c r="U54">
         <v>0.07065748822216711</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.546896959415015</v>
+        <v>7.404502677161902</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09819949200788772</v>
+        <v>0.09797588912442116</v>
       </c>
       <c r="C55">
-        <v>21155.54100038188</v>
+        <v>20826.15012333832</v>
       </c>
       <c r="D55">
-        <v>40855.60600038189</v>
+        <v>40961.72012333832</v>
       </c>
       <c r="E55">
-        <v>-4835.135000000002</v>
+        <v>-4399.630000000001</v>
       </c>
       <c r="F55">
-        <v>23081.765</v>
+        <v>23517.27</v>
       </c>
       <c r="G55">
         <v>3381.7</v>
@@ -5803,28 +5803,28 @@
         <v>12076</v>
       </c>
       <c r="M55">
-        <v>1630.899538634329</v>
+        <v>1661.671228042524</v>
       </c>
       <c r="N55">
-        <v>10445.10046136567</v>
+        <v>10414.32877195748</v>
       </c>
       <c r="O55">
-        <v>3655.785161477985</v>
+        <v>3645.015070185117</v>
       </c>
       <c r="P55">
-        <v>6789.315299887687</v>
+        <v>6769.31370177236</v>
       </c>
       <c r="Q55">
-        <v>7305.815299887687</v>
+        <v>7285.81370177236</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1571446538624493</v>
+        <v>0.1590763277357402</v>
       </c>
       <c r="T55">
-        <v>1.620200383033116</v>
+        <v>1.648308591562529</v>
       </c>
       <c r="U55">
         <v>0.07065748822216711</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.404502677161902</v>
+        <v>7.26738225721446</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09797588912442116</v>
+        <v>0.09775228624095458</v>
       </c>
       <c r="C56">
-        <v>20826.15012333832</v>
+        <v>20497.31190138675</v>
       </c>
       <c r="D56">
-        <v>40961.72012333832</v>
+        <v>41068.38690138676</v>
       </c>
       <c r="E56">
-        <v>-4399.630000000001</v>
+        <v>-3964.125</v>
       </c>
       <c r="F56">
-        <v>23517.27</v>
+        <v>23952.775</v>
       </c>
       <c r="G56">
         <v>3381.7</v>
@@ -5885,28 +5885,28 @@
         <v>12076</v>
       </c>
       <c r="M56">
-        <v>1661.671228042524</v>
+        <v>1692.442917450719</v>
       </c>
       <c r="N56">
-        <v>10414.32877195748</v>
+        <v>10383.55708254928</v>
       </c>
       <c r="O56">
-        <v>3645.015070185117</v>
+        <v>3634.244978892248</v>
       </c>
       <c r="P56">
-        <v>6769.31370177236</v>
+        <v>6749.312103657034</v>
       </c>
       <c r="Q56">
-        <v>7285.81370177236</v>
+        <v>7265.812103657034</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1590763277357402</v>
+        <v>0.1610938537811774</v>
       </c>
       <c r="T56">
-        <v>1.648308591562529</v>
+        <v>1.677666053804361</v>
       </c>
       <c r="U56">
         <v>0.07065748822216711</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.26738225721446</v>
+        <v>7.135248034356015</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09775228624095458</v>
+        <v>0.09752868335748802</v>
       </c>
       <c r="C57">
-        <v>20497.31190138675</v>
+        <v>20169.03066324048</v>
       </c>
       <c r="D57">
-        <v>41068.38690138676</v>
+        <v>41175.61066324048</v>
       </c>
       <c r="E57">
-        <v>-3964.125</v>
+        <v>-3528.619999999999</v>
       </c>
       <c r="F57">
-        <v>23952.775</v>
+        <v>24388.28</v>
       </c>
       <c r="G57">
         <v>3381.7</v>
@@ -5967,28 +5967,28 @@
         <v>12076</v>
       </c>
       <c r="M57">
-        <v>1692.442917450719</v>
+        <v>1723.214606858914</v>
       </c>
       <c r="N57">
-        <v>10383.55708254928</v>
+        <v>10352.78539314109</v>
       </c>
       <c r="O57">
-        <v>3634.244978892248</v>
+        <v>3623.47488759938</v>
       </c>
       <c r="P57">
-        <v>6749.312103657034</v>
+        <v>6729.310505541706</v>
       </c>
       <c r="Q57">
-        <v>7265.812103657034</v>
+        <v>7245.810505541706</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1610938537811774</v>
+        <v>0.1632030855559527</v>
       </c>
       <c r="T57">
-        <v>1.677666053804361</v>
+        <v>1.708357946148093</v>
       </c>
       <c r="U57">
         <v>0.07065748822216711</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.135248034356015</v>
+        <v>7.007832890885371</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09752868335748802</v>
+        <v>0.09730508047402145</v>
       </c>
       <c r="C58">
-        <v>20169.03066324048</v>
+        <v>19841.31078293784</v>
       </c>
       <c r="D58">
-        <v>41175.61066324048</v>
+        <v>41283.39578293784</v>
       </c>
       <c r="E58">
-        <v>-3528.619999999999</v>
+        <v>-3093.114999999998</v>
       </c>
       <c r="F58">
-        <v>24388.28</v>
+        <v>24823.785</v>
       </c>
       <c r="G58">
         <v>3381.7</v>
@@ -6049,28 +6049,28 @@
         <v>12076</v>
       </c>
       <c r="M58">
-        <v>1723.214606858914</v>
+        <v>1753.986296267109</v>
       </c>
       <c r="N58">
-        <v>10352.78539314109</v>
+        <v>10322.01370373289</v>
       </c>
       <c r="O58">
-        <v>3623.47488759938</v>
+        <v>3612.704796306512</v>
       </c>
       <c r="P58">
-        <v>6729.310505541706</v>
+        <v>6709.30890742638</v>
       </c>
       <c r="Q58">
-        <v>7245.810505541706</v>
+        <v>7225.80890742638</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1632030855559527</v>
+        <v>0.1654104211342059</v>
       </c>
       <c r="T58">
-        <v>1.708357946148093</v>
+        <v>1.740477368368279</v>
       </c>
       <c r="U58">
         <v>0.07065748822216711</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.007832890885371</v>
+        <v>6.884888454203171</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09730508047402145</v>
+        <v>0.09708147759055488</v>
       </c>
       <c r="C59">
-        <v>19841.31078293784</v>
+        <v>19514.15668043687</v>
       </c>
       <c r="D59">
-        <v>41283.39578293784</v>
+        <v>41391.74668043688</v>
       </c>
       <c r="E59">
-        <v>-3093.114999999998</v>
+        <v>-2657.609999999997</v>
       </c>
       <c r="F59">
-        <v>24823.785</v>
+        <v>25259.29</v>
       </c>
       <c r="G59">
         <v>3381.7</v>
@@ -6131,28 +6131,28 @@
         <v>12076</v>
       </c>
       <c r="M59">
-        <v>1753.986296267109</v>
+        <v>1784.757985675304</v>
       </c>
       <c r="N59">
-        <v>10322.01370373289</v>
+        <v>10291.2420143247</v>
       </c>
       <c r="O59">
-        <v>3612.704796306512</v>
+        <v>3601.934705013643</v>
       </c>
       <c r="P59">
-        <v>6709.30890742638</v>
+        <v>6689.307309311052</v>
       </c>
       <c r="Q59">
-        <v>7225.80890742638</v>
+        <v>7205.807309311052</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1654104211342059</v>
+        <v>0.1677228679304711</v>
       </c>
       <c r="T59">
-        <v>1.740477368368279</v>
+        <v>1.774126286884664</v>
       </c>
       <c r="U59">
         <v>0.07065748822216711</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.884888454203171</v>
+        <v>6.766183480854841</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09708147759055488</v>
+        <v>0.0975098247070883</v>
       </c>
       <c r="C60">
-        <v>19514.15668043688</v>
+        <v>18871.58451485472</v>
       </c>
       <c r="D60">
-        <v>41391.74668043688</v>
+        <v>41184.67951485472</v>
       </c>
       <c r="E60">
-        <v>-2657.610000000004</v>
+        <v>-2222.105000000003</v>
       </c>
       <c r="F60">
-        <v>25259.29</v>
+        <v>25694.795</v>
       </c>
       <c r="G60">
         <v>3381.7</v>
@@ -6213,45 +6213,45 @@
         <v>12076</v>
       </c>
       <c r="M60">
-        <v>1784.757985675303</v>
+        <v>1859.210826583498</v>
       </c>
       <c r="N60">
-        <v>10291.2420143247</v>
+        <v>10216.7891734165</v>
       </c>
       <c r="O60">
-        <v>3601.934705013643</v>
+        <v>3575.876210695776</v>
       </c>
       <c r="P60">
-        <v>6689.307309311052</v>
+        <v>6640.912962720727</v>
       </c>
       <c r="Q60">
-        <v>7205.807309311052</v>
+        <v>7157.412962720727</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1677228679304711</v>
+        <v>0.170148117009481</v>
       </c>
       <c r="T60">
-        <v>1.774126286884664</v>
+        <v>1.809416616060385</v>
       </c>
       <c r="U60">
-        <v>0.07065748822216711</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.04592736734440862</v>
+        <v>0.04703236734440863</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>6.766183480854842</v>
+        <v>6.495228958079467</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0975098247070883</v>
+        <v>0.09729727182362174</v>
       </c>
       <c r="C61">
-        <v>18871.58451485472</v>
+        <v>18538.57004850842</v>
       </c>
       <c r="D61">
-        <v>41184.67951485472</v>
+        <v>41287.17004850842</v>
       </c>
       <c r="E61">
-        <v>-2222.105000000003</v>
+        <v>-1786.600000000002</v>
       </c>
       <c r="F61">
-        <v>25694.795</v>
+        <v>26130.3</v>
       </c>
       <c r="G61">
         <v>3381.7</v>
@@ -6295,28 +6295,28 @@
         <v>12076</v>
       </c>
       <c r="M61">
-        <v>1859.210826583498</v>
+        <v>1890.722874491693</v>
       </c>
       <c r="N61">
-        <v>10216.7891734165</v>
+        <v>10185.27712550831</v>
       </c>
       <c r="O61">
-        <v>3575.876210695776</v>
+        <v>3564.846993927907</v>
       </c>
       <c r="P61">
-        <v>6640.912962720727</v>
+        <v>6620.430131580399</v>
       </c>
       <c r="Q61">
-        <v>7157.412962720727</v>
+        <v>7136.930131580399</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.170148117009481</v>
+        <v>0.1726946285424414</v>
       </c>
       <c r="T61">
-        <v>1.809416616060385</v>
+        <v>1.846471461694892</v>
       </c>
       <c r="U61">
         <v>0.07235748822216712</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.495228958079467</v>
+        <v>6.386975142111475</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09729727182362174</v>
+        <v>0.09708471894015518</v>
       </c>
       <c r="C62">
-        <v>18538.57004850842</v>
+        <v>18206.06696238547</v>
       </c>
       <c r="D62">
-        <v>41287.17004850842</v>
+        <v>41390.17196238547</v>
       </c>
       <c r="E62">
-        <v>-1786.600000000002</v>
+        <v>-1351.095000000001</v>
       </c>
       <c r="F62">
-        <v>26130.3</v>
+        <v>26565.805</v>
       </c>
       <c r="G62">
         <v>3381.7</v>
@@ -6377,28 +6377,28 @@
         <v>12076</v>
       </c>
       <c r="M62">
-        <v>1890.722874491693</v>
+        <v>1922.234922399888</v>
       </c>
       <c r="N62">
-        <v>10185.27712550831</v>
+        <v>10153.76507760011</v>
       </c>
       <c r="O62">
-        <v>3564.846993927907</v>
+        <v>3553.817777160039</v>
       </c>
       <c r="P62">
-        <v>6620.430131580399</v>
+        <v>6599.947300440073</v>
       </c>
       <c r="Q62">
-        <v>7136.930131580399</v>
+        <v>7116.447300440073</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1726946285424414</v>
+        <v>0.1753717304104254</v>
       </c>
       <c r="T62">
-        <v>1.846471461694892</v>
+        <v>1.885426555823476</v>
       </c>
       <c r="U62">
         <v>0.07235748822216712</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.386975142111475</v>
+        <v>6.282270631585058</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09708471894015518</v>
+        <v>0.09687216605668861</v>
       </c>
       <c r="C63">
-        <v>18206.06696238547</v>
+        <v>17874.07909338323</v>
       </c>
       <c r="D63">
-        <v>41390.17196238547</v>
+        <v>41493.68909338323</v>
       </c>
       <c r="E63">
-        <v>-1351.095000000001</v>
+        <v>-915.5900000000001</v>
       </c>
       <c r="F63">
-        <v>26565.805</v>
+        <v>27001.31</v>
       </c>
       <c r="G63">
         <v>3381.7</v>
@@ -6459,28 +6459,28 @@
         <v>12076</v>
       </c>
       <c r="M63">
-        <v>1922.234922399888</v>
+        <v>1953.746970308083</v>
       </c>
       <c r="N63">
-        <v>10153.76507760011</v>
+        <v>10122.25302969192</v>
       </c>
       <c r="O63">
-        <v>3553.817777160039</v>
+        <v>3542.788560392171</v>
       </c>
       <c r="P63">
-        <v>6599.947300440073</v>
+        <v>6579.464469299746</v>
       </c>
       <c r="Q63">
-        <v>7116.447300440073</v>
+        <v>7095.964469299746</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1753717304104254</v>
+        <v>0.1781897323767244</v>
       </c>
       <c r="T63">
-        <v>1.885426555823476</v>
+        <v>1.926431918064091</v>
       </c>
       <c r="U63">
         <v>0.07235748822216712</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.282270631585058</v>
+        <v>6.180943685914331</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09687216605668861</v>
+        <v>0.09665961317322204</v>
       </c>
       <c r="C64">
-        <v>17874.07909338323</v>
+        <v>17542.61031687971</v>
       </c>
       <c r="D64">
-        <v>41493.68909338323</v>
+        <v>41597.72531687971</v>
       </c>
       <c r="E64">
-        <v>-915.5900000000001</v>
+        <v>-480.0850000000028</v>
       </c>
       <c r="F64">
-        <v>27001.31</v>
+        <v>27436.815</v>
       </c>
       <c r="G64">
         <v>3381.7</v>
@@ -6541,28 +6541,28 @@
         <v>12076</v>
       </c>
       <c r="M64">
-        <v>1953.746970308083</v>
+        <v>1985.259018216278</v>
       </c>
       <c r="N64">
-        <v>10122.25302969192</v>
+        <v>10090.74098178372</v>
       </c>
       <c r="O64">
-        <v>3542.788560392171</v>
+        <v>3531.759343624302</v>
       </c>
       <c r="P64">
-        <v>6579.464469299746</v>
+        <v>6558.981638159419</v>
       </c>
       <c r="Q64">
-        <v>7095.964469299746</v>
+        <v>7075.481638159419</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1781897323767244</v>
+        <v>0.1811600587736341</v>
       </c>
       <c r="T64">
-        <v>1.926431918064091</v>
+        <v>1.969653786371766</v>
       </c>
       <c r="U64">
         <v>0.07235748822216712</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.180943685914331</v>
+        <v>6.082833468677595</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09665961317322204</v>
+        <v>0.09644706028975547</v>
       </c>
       <c r="C65">
-        <v>17542.61031687971</v>
+        <v>17211.6645472172</v>
       </c>
       <c r="D65">
-        <v>41597.72531687971</v>
+        <v>41702.2845472172</v>
       </c>
       <c r="E65">
-        <v>-480.0850000000028</v>
+        <v>-44.58000000000175</v>
       </c>
       <c r="F65">
-        <v>27436.815</v>
+        <v>27872.32</v>
       </c>
       <c r="G65">
         <v>3381.7</v>
@@ -6623,28 +6623,28 @@
         <v>12076</v>
       </c>
       <c r="M65">
-        <v>1985.259018216278</v>
+        <v>2016.771066124473</v>
       </c>
       <c r="N65">
-        <v>10090.74098178372</v>
+        <v>10059.22893387553</v>
       </c>
       <c r="O65">
-        <v>3531.759343624302</v>
+        <v>3520.730126856434</v>
       </c>
       <c r="P65">
-        <v>6558.981638159419</v>
+        <v>6538.498807019093</v>
       </c>
       <c r="Q65">
-        <v>7075.481638159419</v>
+        <v>7054.998807019093</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1811600587736341</v>
+        <v>0.1842954033037054</v>
       </c>
       <c r="T65">
-        <v>1.969653786371766</v>
+        <v>2.015276869585424</v>
       </c>
       <c r="U65">
         <v>0.07235748822216712</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.082833468677595</v>
+        <v>5.987789195729508</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09644706028975547</v>
+        <v>0.0962345074062889</v>
       </c>
       <c r="C66">
-        <v>17211.6645472172</v>
+        <v>16881.24573819328</v>
       </c>
       <c r="D66">
-        <v>41702.2845472172</v>
+        <v>41807.37073819328</v>
       </c>
       <c r="E66">
-        <v>-44.58000000000175</v>
+        <v>390.9249999999993</v>
       </c>
       <c r="F66">
-        <v>27872.32</v>
+        <v>28307.825</v>
       </c>
       <c r="G66">
         <v>3381.7</v>
@@ -6705,28 +6705,28 @@
         <v>12076</v>
       </c>
       <c r="M66">
-        <v>2016.771066124473</v>
+        <v>2048.283114032668</v>
       </c>
       <c r="N66">
-        <v>10059.22893387553</v>
+        <v>10027.71688596733</v>
       </c>
       <c r="O66">
-        <v>3520.730126856434</v>
+        <v>3509.700910088566</v>
       </c>
       <c r="P66">
-        <v>6538.498807019093</v>
+        <v>6518.015975878767</v>
       </c>
       <c r="Q66">
-        <v>7054.998807019093</v>
+        <v>7034.515975878767</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1842954033037054</v>
+        <v>0.1876099103783523</v>
       </c>
       <c r="T66">
-        <v>2.015276869585424</v>
+        <v>2.063506986125576</v>
       </c>
       <c r="U66">
         <v>0.07235748822216712</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.987789195729508</v>
+        <v>5.895669361949054</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0962345074062889</v>
+        <v>0.09602195452282232</v>
       </c>
       <c r="C67">
-        <v>16881.24573819328</v>
+        <v>16551.3578835591</v>
       </c>
       <c r="D67">
-        <v>41807.37073819328</v>
+        <v>41912.9878835591</v>
       </c>
       <c r="E67">
-        <v>390.9249999999993</v>
+        <v>826.4300000000003</v>
       </c>
       <c r="F67">
-        <v>28307.825</v>
+        <v>28743.33</v>
       </c>
       <c r="G67">
         <v>3381.7</v>
@@ -6787,28 +6787,28 @@
         <v>12076</v>
       </c>
       <c r="M67">
-        <v>2048.283114032668</v>
+        <v>2079.795161940863</v>
       </c>
       <c r="N67">
-        <v>10027.71688596733</v>
+        <v>9996.204838059137</v>
       </c>
       <c r="O67">
-        <v>3509.700910088566</v>
+        <v>3498.671693320698</v>
       </c>
       <c r="P67">
-        <v>6518.015975878767</v>
+        <v>6497.53314473844</v>
       </c>
       <c r="Q67">
-        <v>7034.515975878767</v>
+        <v>7014.03314473844</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1876099103783523</v>
+        <v>0.1911193884573901</v>
       </c>
       <c r="T67">
-        <v>2.063506986125576</v>
+        <v>2.11457416834456</v>
       </c>
       <c r="U67">
         <v>0.07235748822216712</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.895669361949054</v>
+        <v>5.806341038283159</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09602195452282232</v>
+        <v>0.09580940163935575</v>
       </c>
       <c r="C68">
-        <v>16551.3578835591</v>
+        <v>16222.00501752534</v>
       </c>
       <c r="D68">
-        <v>41912.9878835591</v>
+        <v>42019.14001752534</v>
       </c>
       <c r="E68">
-        <v>826.4300000000003</v>
+        <v>1261.935000000001</v>
       </c>
       <c r="F68">
-        <v>28743.33</v>
+        <v>29178.835</v>
       </c>
       <c r="G68">
         <v>3381.7</v>
@@ -6869,28 +6869,28 @@
         <v>12076</v>
       </c>
       <c r="M68">
-        <v>2079.795161940863</v>
+        <v>2111.307209849058</v>
       </c>
       <c r="N68">
-        <v>9996.204838059137</v>
+        <v>9964.692790150943</v>
       </c>
       <c r="O68">
-        <v>3498.671693320698</v>
+        <v>3487.64247655283</v>
       </c>
       <c r="P68">
-        <v>6497.53314473844</v>
+        <v>6477.050313598113</v>
       </c>
       <c r="Q68">
-        <v>7014.03314473844</v>
+        <v>6993.550313598113</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1911193884573901</v>
+        <v>0.1948415621775818</v>
       </c>
       <c r="T68">
-        <v>2.11457416834456</v>
+        <v>2.168736331304089</v>
       </c>
       <c r="U68">
         <v>0.07235748822216712</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.806341038283159</v>
+        <v>5.719679231741619</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09580940163935575</v>
+        <v>0.09559684875588918</v>
       </c>
       <c r="C69">
-        <v>16222.00501752534</v>
+        <v>15893.19121527595</v>
       </c>
       <c r="D69">
-        <v>42019.14001752534</v>
+        <v>42125.83121527595</v>
       </c>
       <c r="E69">
-        <v>1261.935000000001</v>
+        <v>1697.440000000002</v>
       </c>
       <c r="F69">
-        <v>29178.835</v>
+        <v>29614.34</v>
       </c>
       <c r="G69">
         <v>3381.7</v>
@@ -6951,28 +6951,28 @@
         <v>12076</v>
       </c>
       <c r="M69">
-        <v>2111.307209849058</v>
+        <v>2142.819257757253</v>
       </c>
       <c r="N69">
-        <v>9964.692790150943</v>
+        <v>9933.180742242748</v>
       </c>
       <c r="O69">
-        <v>3487.64247655283</v>
+        <v>3476.613259784962</v>
       </c>
       <c r="P69">
-        <v>6477.050313598113</v>
+        <v>6456.567482457786</v>
       </c>
       <c r="Q69">
-        <v>6993.550313598113</v>
+        <v>6973.067482457786</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1948415621775818</v>
+        <v>0.1987963717552854</v>
       </c>
       <c r="T69">
-        <v>2.168736331304089</v>
+        <v>2.226283629448588</v>
       </c>
       <c r="U69">
         <v>0.07235748822216712</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.719679231741619</v>
+        <v>5.635566301863066</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09559684875588918</v>
+        <v>0.09574309587242263</v>
       </c>
       <c r="C70">
-        <v>15893.19121527595</v>
+        <v>15384.21924002869</v>
       </c>
       <c r="D70">
-        <v>42125.83121527595</v>
+        <v>42052.3642400287</v>
       </c>
       <c r="E70">
-        <v>1697.440000000002</v>
+        <v>2132.945</v>
       </c>
       <c r="F70">
-        <v>29614.34</v>
+        <v>30049.845</v>
       </c>
       <c r="G70">
         <v>3381.7</v>
@@ -7033,45 +7033,45 @@
         <v>12076</v>
       </c>
       <c r="M70">
-        <v>2142.819257757253</v>
+        <v>2198.371181665447</v>
       </c>
       <c r="N70">
-        <v>9933.180742242748</v>
+        <v>9877.628818334553</v>
       </c>
       <c r="O70">
-        <v>3476.613259784962</v>
+        <v>3457.170086417093</v>
       </c>
       <c r="P70">
-        <v>6456.567482457786</v>
+        <v>6420.45873191746</v>
       </c>
       <c r="Q70">
-        <v>6973.067482457786</v>
+        <v>6936.95873191746</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1987963717552854</v>
+        <v>0.2030063303380022</v>
       </c>
       <c r="T70">
-        <v>2.226283629448588</v>
+        <v>2.287543656505636</v>
       </c>
       <c r="U70">
-        <v>0.07235748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V70">
         <v>0.35</v>
       </c>
       <c r="W70">
-        <v>0.04703236734440863</v>
+        <v>0.04755236734440862</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y70">
-        <v>5.635566301863066</v>
+        <v>5.493157889220252</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09574309587242263</v>
+        <v>0.09553574298895605</v>
       </c>
       <c r="C71">
-        <v>15384.21924002869</v>
+        <v>15052.95367728945</v>
       </c>
       <c r="D71">
-        <v>42052.3642400287</v>
+        <v>42156.60367728946</v>
       </c>
       <c r="E71">
-        <v>2132.945</v>
+        <v>2568.450000000001</v>
       </c>
       <c r="F71">
-        <v>30049.845</v>
+        <v>30485.35</v>
       </c>
       <c r="G71">
         <v>3381.7</v>
@@ -7115,28 +7115,28 @@
         <v>12076</v>
       </c>
       <c r="M71">
-        <v>2198.371181665447</v>
+        <v>2230.231633573642</v>
       </c>
       <c r="N71">
-        <v>9877.628818334553</v>
+        <v>9845.768366426357</v>
       </c>
       <c r="O71">
-        <v>3457.170086417093</v>
+        <v>3446.018928249225</v>
       </c>
       <c r="P71">
-        <v>6420.45873191746</v>
+        <v>6399.749438177132</v>
       </c>
       <c r="Q71">
-        <v>6936.95873191746</v>
+        <v>6916.249438177132</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2030063303380022</v>
+        <v>0.2074969528262334</v>
       </c>
       <c r="T71">
-        <v>2.287543656505636</v>
+        <v>2.352887685366487</v>
       </c>
       <c r="U71">
         <v>0.07315748822216711</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.493157889220252</v>
+        <v>5.414684205088534</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09553574298895605</v>
+        <v>0.09532839010548949</v>
       </c>
       <c r="C72">
-        <v>15052.95367728945</v>
+        <v>14722.20617633873</v>
       </c>
       <c r="D72">
-        <v>42156.60367728946</v>
+        <v>42261.36117633874</v>
       </c>
       <c r="E72">
-        <v>2568.450000000001</v>
+        <v>3003.955000000002</v>
       </c>
       <c r="F72">
-        <v>30485.35</v>
+        <v>30920.855</v>
       </c>
       <c r="G72">
         <v>3381.7</v>
@@ -7197,28 +7197,28 @@
         <v>12076</v>
       </c>
       <c r="M72">
-        <v>2230.231633573642</v>
+        <v>2262.092085481837</v>
       </c>
       <c r="N72">
-        <v>9845.768366426357</v>
+        <v>9813.907914518162</v>
       </c>
       <c r="O72">
-        <v>3446.018928249225</v>
+        <v>3434.867770081356</v>
       </c>
       <c r="P72">
-        <v>6399.749438177132</v>
+        <v>6379.040144436805</v>
       </c>
       <c r="Q72">
-        <v>6916.249438177132</v>
+        <v>6895.540144436805</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2074969528262334</v>
+        <v>0.2122972734171013</v>
       </c>
       <c r="T72">
-        <v>2.352887685366487</v>
+        <v>2.422738198976363</v>
       </c>
       <c r="U72">
         <v>0.07315748822216711</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.414684205088534</v>
+        <v>5.338421047270385</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09532839010548949</v>
+        <v>0.09512103722202291</v>
       </c>
       <c r="C73">
-        <v>14722.20617633874</v>
+        <v>14391.980608887</v>
       </c>
       <c r="D73">
-        <v>42261.36117633874</v>
+        <v>42366.64060888701</v>
       </c>
       <c r="E73">
-        <v>3003.954999999998</v>
+        <v>3439.459999999999</v>
       </c>
       <c r="F73">
-        <v>30920.855</v>
+        <v>31356.36</v>
       </c>
       <c r="G73">
         <v>3381.7</v>
@@ -7279,28 +7279,28 @@
         <v>12076</v>
       </c>
       <c r="M73">
-        <v>2262.092085481837</v>
+        <v>2293.952537390032</v>
       </c>
       <c r="N73">
-        <v>9813.907914518164</v>
+        <v>9782.047462609968</v>
       </c>
       <c r="O73">
-        <v>3434.867770081357</v>
+        <v>3423.716611913489</v>
       </c>
       <c r="P73">
-        <v>6379.040144436807</v>
+        <v>6358.330850696479</v>
       </c>
       <c r="Q73">
-        <v>6895.540144436807</v>
+        <v>6874.830850696479</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2122972734171012</v>
+        <v>0.2174404740501739</v>
       </c>
       <c r="T73">
-        <v>2.422738198976362</v>
+        <v>2.497578034986942</v>
       </c>
       <c r="U73">
         <v>0.07315748822216711</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.338421047270387</v>
+        <v>5.264276310502741</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09512103722202291</v>
+        <v>0.09491368433855635</v>
       </c>
       <c r="C74">
-        <v>14391.980608887</v>
+        <v>14062.28088532109</v>
       </c>
       <c r="D74">
-        <v>42366.64060888701</v>
+        <v>42472.44588532109</v>
       </c>
       <c r="E74">
-        <v>3439.459999999999</v>
+        <v>3874.964999999997</v>
       </c>
       <c r="F74">
-        <v>31356.36</v>
+        <v>31791.865</v>
       </c>
       <c r="G74">
         <v>3381.7</v>
@@ -7361,28 +7361,28 @@
         <v>12076</v>
       </c>
       <c r="M74">
-        <v>2293.952537390032</v>
+        <v>2325.812989298227</v>
       </c>
       <c r="N74">
-        <v>9782.047462609968</v>
+        <v>9750.187010701773</v>
       </c>
       <c r="O74">
-        <v>3423.716611913489</v>
+        <v>3412.56545374562</v>
       </c>
       <c r="P74">
-        <v>6358.330850696479</v>
+        <v>6337.621556956153</v>
       </c>
       <c r="Q74">
-        <v>6874.830850696479</v>
+        <v>6854.121556956153</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2174404740501739</v>
+        <v>0.2229646525079187</v>
       </c>
       <c r="T74">
-        <v>2.497578034986942</v>
+        <v>2.577961562553862</v>
       </c>
       <c r="U74">
         <v>0.07315748822216711</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.264276310502741</v>
+        <v>5.192162936386266</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09491368433855635</v>
+        <v>0.09470633145508976</v>
       </c>
       <c r="C75">
-        <v>14062.28088532109</v>
+        <v>13733.11095518843</v>
       </c>
       <c r="D75">
-        <v>42472.44588532109</v>
+        <v>42578.78095518843</v>
       </c>
       <c r="E75">
-        <v>3874.964999999997</v>
+        <v>4310.469999999998</v>
       </c>
       <c r="F75">
-        <v>31791.865</v>
+        <v>32227.37</v>
       </c>
       <c r="G75">
         <v>3381.7</v>
@@ -7443,28 +7443,28 @@
         <v>12076</v>
       </c>
       <c r="M75">
-        <v>2325.812989298227</v>
+        <v>2357.673441206422</v>
       </c>
       <c r="N75">
-        <v>9750.187010701773</v>
+        <v>9718.326558793578</v>
       </c>
       <c r="O75">
-        <v>3412.56545374562</v>
+        <v>3401.414295577752</v>
       </c>
       <c r="P75">
-        <v>6337.621556956153</v>
+        <v>6316.912263215826</v>
       </c>
       <c r="Q75">
-        <v>6854.121556956153</v>
+        <v>6833.412263215826</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2229646525079187</v>
+        <v>0.2289137677701053</v>
       </c>
       <c r="T75">
-        <v>2.577961562553862</v>
+        <v>2.66452843839516</v>
       </c>
       <c r="U75">
         <v>0.07315748822216711</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.192162936386266</v>
+        <v>5.121998572381046</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09470633145508976</v>
+        <v>0.0944989785716232</v>
       </c>
       <c r="C76">
-        <v>13733.11095518843</v>
+        <v>13404.47480768843</v>
       </c>
       <c r="D76">
-        <v>42578.78095518843</v>
+        <v>42685.64980768843</v>
       </c>
       <c r="E76">
-        <v>4310.469999999998</v>
+        <v>4745.974999999999</v>
       </c>
       <c r="F76">
-        <v>32227.37</v>
+        <v>32662.875</v>
       </c>
       <c r="G76">
         <v>3381.7</v>
@@ -7525,28 +7525,28 @@
         <v>12076</v>
       </c>
       <c r="M76">
-        <v>2357.673441206422</v>
+        <v>2389.533893114617</v>
       </c>
       <c r="N76">
-        <v>9718.326558793578</v>
+        <v>9686.466106885384</v>
       </c>
       <c r="O76">
-        <v>3401.414295577752</v>
+        <v>3390.263137409884</v>
       </c>
       <c r="P76">
-        <v>6316.912263215826</v>
+        <v>6296.2029694755</v>
       </c>
       <c r="Q76">
-        <v>6833.412263215826</v>
+        <v>6812.7029694755</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2289137677701053</v>
+        <v>0.2353388122532669</v>
       </c>
       <c r="T76">
-        <v>2.66452843839516</v>
+        <v>2.758020664303763</v>
       </c>
       <c r="U76">
         <v>0.07315748822216711</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.121998572381046</v>
+        <v>5.053705258082632</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0944989785716232</v>
+        <v>0.09429162568815663</v>
       </c>
       <c r="C77">
-        <v>13404.47480768843</v>
+        <v>13076.37647217143</v>
       </c>
       <c r="D77">
-        <v>42685.64980768843</v>
+        <v>42793.05647217143</v>
       </c>
       <c r="E77">
-        <v>4745.974999999999</v>
+        <v>5181.479999999996</v>
       </c>
       <c r="F77">
-        <v>32662.875</v>
+        <v>33098.38</v>
       </c>
       <c r="G77">
         <v>3381.7</v>
@@ -7607,28 +7607,28 @@
         <v>12076</v>
       </c>
       <c r="M77">
-        <v>2389.533893114617</v>
+        <v>2421.394345022811</v>
       </c>
       <c r="N77">
-        <v>9686.466106885384</v>
+        <v>9654.605654977189</v>
       </c>
       <c r="O77">
-        <v>3390.263137409884</v>
+        <v>3379.111979242016</v>
       </c>
       <c r="P77">
-        <v>6296.2029694755</v>
+        <v>6275.493675735173</v>
       </c>
       <c r="Q77">
-        <v>6812.7029694755</v>
+        <v>6791.993675735173</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2353388122532669</v>
+        <v>0.2422992771100253</v>
       </c>
       <c r="T77">
-        <v>2.758020664303763</v>
+        <v>2.859303909038082</v>
       </c>
       <c r="U77">
         <v>0.07315748822216711</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.053705258082632</v>
+        <v>4.987209136265756</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09429162568815663</v>
+        <v>0.09408427280469006</v>
       </c>
       <c r="C78">
-        <v>13076.37647217143</v>
+        <v>12748.82001864503</v>
       </c>
       <c r="D78">
-        <v>42793.05647217143</v>
+        <v>42901.00501864503</v>
       </c>
       <c r="E78">
-        <v>5181.479999999996</v>
+        <v>5616.985000000001</v>
       </c>
       <c r="F78">
-        <v>33098.38</v>
+        <v>33533.885</v>
       </c>
       <c r="G78">
         <v>3381.7</v>
@@ -7689,28 +7689,28 @@
         <v>12076</v>
       </c>
       <c r="M78">
-        <v>2421.394345022811</v>
+        <v>2453.254796931007</v>
       </c>
       <c r="N78">
-        <v>9654.605654977189</v>
+        <v>9622.745203068993</v>
       </c>
       <c r="O78">
-        <v>3379.111979242016</v>
+        <v>3367.960821074147</v>
       </c>
       <c r="P78">
-        <v>6275.493675735173</v>
+        <v>6254.784381994846</v>
       </c>
       <c r="Q78">
-        <v>6791.993675735173</v>
+        <v>6771.284381994846</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2422992771100253</v>
+        <v>0.2498649997804149</v>
       </c>
       <c r="T78">
-        <v>2.859303909038082</v>
+        <v>2.96939439244495</v>
       </c>
       <c r="U78">
         <v>0.07315748822216711</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.987209136265756</v>
+        <v>4.922440186444121</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09408427280469006</v>
+        <v>0.09387691992122348</v>
       </c>
       <c r="C79">
-        <v>12748.82001864503</v>
+        <v>12421.80955828825</v>
       </c>
       <c r="D79">
-        <v>42901.00501864503</v>
+        <v>43009.49955828825</v>
       </c>
       <c r="E79">
-        <v>5616.985000000001</v>
+        <v>6052.489999999998</v>
       </c>
       <c r="F79">
-        <v>33533.885</v>
+        <v>33969.39</v>
       </c>
       <c r="G79">
         <v>3381.7</v>
@@ -7771,28 +7771,28 @@
         <v>12076</v>
       </c>
       <c r="M79">
-        <v>2453.254796931007</v>
+        <v>2485.115248839201</v>
       </c>
       <c r="N79">
-        <v>9622.745203068993</v>
+        <v>9590.884751160798</v>
       </c>
       <c r="O79">
-        <v>3367.960821074147</v>
+        <v>3356.809662906279</v>
       </c>
       <c r="P79">
-        <v>6254.784381994846</v>
+        <v>6234.075088254519</v>
       </c>
       <c r="Q79">
-        <v>6771.284381994846</v>
+        <v>6750.575088254519</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2498649997804149</v>
+        <v>0.2581185154208398</v>
       </c>
       <c r="T79">
-        <v>2.96939439244495</v>
+        <v>3.089493101616079</v>
       </c>
       <c r="U79">
         <v>0.07315748822216711</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.922440186444121</v>
+        <v>4.859331978925607</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09387691992122348</v>
+        <v>0.09366956703775692</v>
       </c>
       <c r="C80">
-        <v>12421.80955828825</v>
+        <v>12095.34924397339</v>
       </c>
       <c r="D80">
-        <v>43009.49955828825</v>
+        <v>43118.5442439734</v>
       </c>
       <c r="E80">
-        <v>6052.489999999998</v>
+        <v>6487.995000000003</v>
       </c>
       <c r="F80">
-        <v>33969.39</v>
+        <v>34404.895</v>
       </c>
       <c r="G80">
         <v>3381.7</v>
@@ -7853,28 +7853,28 @@
         <v>12076</v>
       </c>
       <c r="M80">
-        <v>2485.115248839201</v>
+        <v>2516.975700747396</v>
       </c>
       <c r="N80">
-        <v>9590.884751160798</v>
+        <v>9559.024299252604</v>
       </c>
       <c r="O80">
-        <v>3356.809662906279</v>
+        <v>3345.658504738411</v>
       </c>
       <c r="P80">
-        <v>6234.075088254519</v>
+        <v>6213.365794514193</v>
       </c>
       <c r="Q80">
-        <v>6750.575088254519</v>
+        <v>6729.865794514193</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2581185154208398</v>
+        <v>0.2671580801698767</v>
       </c>
       <c r="T80">
-        <v>3.089493101616079</v>
+        <v>3.221029783089221</v>
       </c>
       <c r="U80">
         <v>0.07315748822216711</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.859331978925607</v>
+        <v>4.797821447546802</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09366956703775692</v>
+        <v>0.09346221415429035</v>
       </c>
       <c r="C81">
-        <v>12095.34924397339</v>
+        <v>11769.44327079603</v>
       </c>
       <c r="D81">
-        <v>43118.5442439734</v>
+        <v>43228.14327079603</v>
       </c>
       <c r="E81">
-        <v>6487.995000000003</v>
+        <v>6923.5</v>
       </c>
       <c r="F81">
-        <v>34404.895</v>
+        <v>34840.4</v>
       </c>
       <c r="G81">
         <v>3381.7</v>
@@ -7935,28 +7935,28 @@
         <v>12076</v>
       </c>
       <c r="M81">
-        <v>2516.975700747396</v>
+        <v>2548.836152655591</v>
       </c>
       <c r="N81">
-        <v>9559.024299252604</v>
+        <v>9527.163847344409</v>
       </c>
       <c r="O81">
-        <v>3345.658504738411</v>
+        <v>3334.507346570543</v>
       </c>
       <c r="P81">
-        <v>6213.365794514193</v>
+        <v>6192.656500773866</v>
       </c>
       <c r="Q81">
-        <v>6729.865794514193</v>
+        <v>6709.156500773866</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2671580801698767</v>
+        <v>0.2771016013938173</v>
       </c>
       <c r="T81">
-        <v>3.221029783089221</v>
+        <v>3.365720132709677</v>
       </c>
       <c r="U81">
         <v>0.07315748822216711</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.797821447546802</v>
+        <v>4.737848679452467</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09346221415429035</v>
+        <v>0.09325486127082377</v>
       </c>
       <c r="C82">
-        <v>11769.44327079603</v>
+        <v>11444.09587661286</v>
       </c>
       <c r="D82">
-        <v>43228.14327079603</v>
+        <v>43338.30087661286</v>
       </c>
       <c r="E82">
-        <v>6923.5</v>
+        <v>7359.004999999997</v>
       </c>
       <c r="F82">
-        <v>34840.4</v>
+        <v>35275.905</v>
       </c>
       <c r="G82">
         <v>3381.7</v>
@@ -8017,28 +8017,28 @@
         <v>12076</v>
       </c>
       <c r="M82">
-        <v>2548.836152655591</v>
+        <v>2580.696604563786</v>
       </c>
       <c r="N82">
-        <v>9527.163847344409</v>
+        <v>9495.303395436214</v>
       </c>
       <c r="O82">
-        <v>3334.507346570543</v>
+        <v>3323.356188402675</v>
       </c>
       <c r="P82">
-        <v>6192.656500773866</v>
+        <v>6171.94720703354</v>
       </c>
       <c r="Q82">
-        <v>6709.156500773866</v>
+        <v>6688.44720703354</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2771016013938173</v>
+        <v>0.2880918090623832</v>
       </c>
       <c r="T82">
-        <v>3.365720132709677</v>
+        <v>3.525641045448076</v>
       </c>
       <c r="U82">
         <v>0.07315748822216711</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.737848679452467</v>
+        <v>4.679356720446881</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09325486127082377</v>
+        <v>0.0930475083873572</v>
       </c>
       <c r="C83">
-        <v>11444.09587661286</v>
+        <v>11119.31134258802</v>
       </c>
       <c r="D83">
-        <v>43338.30087661286</v>
+        <v>43449.02134258803</v>
       </c>
       <c r="E83">
-        <v>7359.004999999997</v>
+        <v>7794.510000000002</v>
       </c>
       <c r="F83">
-        <v>35275.905</v>
+        <v>35711.41</v>
       </c>
       <c r="G83">
         <v>3381.7</v>
@@ -8099,28 +8099,28 @@
         <v>12076</v>
       </c>
       <c r="M83">
-        <v>2580.696604563786</v>
+        <v>2612.557056471981</v>
       </c>
       <c r="N83">
-        <v>9495.303395436214</v>
+        <v>9463.442943528018</v>
       </c>
       <c r="O83">
-        <v>3323.356188402675</v>
+        <v>3312.205030234806</v>
       </c>
       <c r="P83">
-        <v>6171.94720703354</v>
+        <v>6151.237913293212</v>
       </c>
       <c r="Q83">
-        <v>6688.44720703354</v>
+        <v>6667.737913293212</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2880918090623832</v>
+        <v>0.3003031509163453</v>
       </c>
       <c r="T83">
-        <v>3.525641045448076</v>
+        <v>3.70333094849074</v>
       </c>
       <c r="U83">
         <v>0.07315748822216711</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.679356720446881</v>
+        <v>4.622291394587773</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0930475083873572</v>
+        <v>0.09284015550389065</v>
       </c>
       <c r="C84">
-        <v>11119.31134258802</v>
+        <v>10795.0939937477</v>
       </c>
       <c r="D84">
-        <v>43449.02134258803</v>
+        <v>43560.30899374771</v>
       </c>
       <c r="E84">
-        <v>7794.510000000002</v>
+        <v>8230.014999999999</v>
       </c>
       <c r="F84">
-        <v>35711.41</v>
+        <v>36146.915</v>
       </c>
       <c r="G84">
         <v>3381.7</v>
@@ -8181,28 +8181,28 @@
         <v>12076</v>
       </c>
       <c r="M84">
-        <v>2612.557056471981</v>
+        <v>2644.417508380176</v>
       </c>
       <c r="N84">
-        <v>9463.442943528018</v>
+        <v>9431.582491619825</v>
       </c>
       <c r="O84">
-        <v>3312.205030234806</v>
+        <v>3301.053872066939</v>
       </c>
       <c r="P84">
-        <v>6151.237913293212</v>
+        <v>6130.528619552886</v>
       </c>
       <c r="Q84">
-        <v>6667.737913293212</v>
+        <v>6647.028619552886</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3003031509163453</v>
+        <v>0.3139511212237148</v>
       </c>
       <c r="T84">
-        <v>3.70333094849074</v>
+        <v>3.901925546009014</v>
       </c>
       <c r="U84">
         <v>0.07315748822216711</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.622291394587773</v>
+        <v>4.566601136821657</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09284015550389065</v>
+        <v>0.09263280262042407</v>
       </c>
       <c r="C85">
-        <v>10795.0939937477</v>
+        <v>10471.44819954329</v>
       </c>
       <c r="D85">
-        <v>43560.30899374771</v>
+        <v>43672.1681995433</v>
       </c>
       <c r="E85">
-        <v>8230.014999999999</v>
+        <v>8665.520000000004</v>
       </c>
       <c r="F85">
-        <v>36146.915</v>
+        <v>36582.42000000001</v>
       </c>
       <c r="G85">
         <v>3381.7</v>
@@ -8263,28 +8263,28 @@
         <v>12076</v>
       </c>
       <c r="M85">
-        <v>2644.417508380176</v>
+        <v>2676.277960288371</v>
       </c>
       <c r="N85">
-        <v>9431.582491619825</v>
+        <v>9399.722039711629</v>
       </c>
       <c r="O85">
-        <v>3301.053872066939</v>
+        <v>3289.90271389907</v>
       </c>
       <c r="P85">
-        <v>6130.528619552886</v>
+        <v>6109.819325812559</v>
       </c>
       <c r="Q85">
-        <v>6647.028619552886</v>
+        <v>6626.319325812559</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3139511212237148</v>
+        <v>0.3293050878195053</v>
       </c>
       <c r="T85">
-        <v>3.901925546009014</v>
+        <v>4.125344468217071</v>
       </c>
       <c r="U85">
         <v>0.07315748822216711</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.566601136821657</v>
+        <v>4.512236837573777</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09263280262042407</v>
+        <v>0.09242544973695752</v>
       </c>
       <c r="C86">
-        <v>10471.4481995433</v>
+        <v>10148.37837442328</v>
       </c>
       <c r="D86">
-        <v>43672.1681995433</v>
+        <v>43784.60337442328</v>
       </c>
       <c r="E86">
-        <v>8665.519999999997</v>
+        <v>9101.024999999994</v>
       </c>
       <c r="F86">
-        <v>36582.42</v>
+        <v>37017.925</v>
       </c>
       <c r="G86">
         <v>3381.7</v>
@@ -8345,28 +8345,28 @@
         <v>12076</v>
       </c>
       <c r="M86">
-        <v>2676.277960288371</v>
+        <v>2708.138412196565</v>
       </c>
       <c r="N86">
-        <v>9399.722039711629</v>
+        <v>9367.861587803434</v>
       </c>
       <c r="O86">
-        <v>3289.90271389907</v>
+        <v>3278.751555731202</v>
       </c>
       <c r="P86">
-        <v>6109.819325812559</v>
+        <v>6089.110032072233</v>
       </c>
       <c r="Q86">
-        <v>6626.319325812559</v>
+        <v>6605.610032072233</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3293050878195051</v>
+        <v>0.3467062499614011</v>
       </c>
       <c r="T86">
-        <v>4.125344468217068</v>
+        <v>4.378552580052866</v>
       </c>
       <c r="U86">
         <v>0.07315748822216711</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.512236837573779</v>
+        <v>4.459151698308204</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09242544973695752</v>
+        <v>0.09221809685349094</v>
       </c>
       <c r="C87">
-        <v>10148.37837442328</v>
+        <v>9825.888978413939</v>
       </c>
       <c r="D87">
-        <v>43784.60337442328</v>
+        <v>43897.61897841394</v>
       </c>
       <c r="E87">
-        <v>9101.024999999994</v>
+        <v>9536.529999999999</v>
       </c>
       <c r="F87">
-        <v>37017.925</v>
+        <v>37453.43</v>
       </c>
       <c r="G87">
         <v>3381.7</v>
@@ -8427,28 +8427,28 @@
         <v>12076</v>
       </c>
       <c r="M87">
-        <v>2708.138412196565</v>
+        <v>2739.99886410476</v>
       </c>
       <c r="N87">
-        <v>9367.861587803434</v>
+        <v>9336.00113589524</v>
       </c>
       <c r="O87">
-        <v>3278.751555731202</v>
+        <v>3267.600397563334</v>
       </c>
       <c r="P87">
-        <v>6089.110032072233</v>
+        <v>6068.400738331906</v>
       </c>
       <c r="Q87">
-        <v>6605.610032072233</v>
+        <v>6584.900738331906</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3467062499614011</v>
+        <v>0.3665932924092822</v>
       </c>
       <c r="T87">
-        <v>4.378552580052866</v>
+        <v>4.667933279293777</v>
       </c>
       <c r="U87">
         <v>0.07315748822216711</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.459151698308204</v>
+        <v>4.407301097165086</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09221809685349094</v>
+        <v>0.09201074397002436</v>
       </c>
       <c r="C88">
-        <v>9825.888978413939</v>
+        <v>9503.984517709105</v>
       </c>
       <c r="D88">
-        <v>43897.61897841394</v>
+        <v>44011.21951770911</v>
       </c>
       <c r="E88">
-        <v>9536.529999999999</v>
+        <v>9972.034999999996</v>
       </c>
       <c r="F88">
-        <v>37453.43</v>
+        <v>37888.935</v>
       </c>
       <c r="G88">
         <v>3381.7</v>
@@ -8509,28 +8509,28 @@
         <v>12076</v>
       </c>
       <c r="M88">
-        <v>2739.99886410476</v>
+        <v>2771.859316012955</v>
       </c>
       <c r="N88">
-        <v>9336.00113589524</v>
+        <v>9304.140683987045</v>
       </c>
       <c r="O88">
-        <v>3267.600397563334</v>
+        <v>3256.449239395466</v>
       </c>
       <c r="P88">
-        <v>6068.400738331906</v>
+        <v>6047.691444591579</v>
       </c>
       <c r="Q88">
-        <v>6584.900738331906</v>
+        <v>6564.191444591579</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3665932924092822</v>
+        <v>0.3895398798491451</v>
       </c>
       <c r="T88">
-        <v>4.667933279293777</v>
+        <v>5.001834086110213</v>
       </c>
       <c r="U88">
         <v>0.07315748822216711</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.407301097165086</v>
+        <v>4.356642463864338</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09201074397002436</v>
+        <v>0.0918033910865578</v>
       </c>
       <c r="C89">
-        <v>9503.984517709105</v>
+        <v>9182.669545269076</v>
       </c>
       <c r="D89">
-        <v>44011.21951770911</v>
+        <v>44125.40954526908</v>
       </c>
       <c r="E89">
-        <v>9972.034999999996</v>
+        <v>10407.54</v>
       </c>
       <c r="F89">
-        <v>37888.935</v>
+        <v>38324.44</v>
       </c>
       <c r="G89">
         <v>3381.7</v>
@@ -8591,28 +8591,28 @@
         <v>12076</v>
       </c>
       <c r="M89">
-        <v>2771.859316012955</v>
+        <v>2803.71976792115</v>
       </c>
       <c r="N89">
-        <v>9304.140683987045</v>
+        <v>9272.280232078851</v>
       </c>
       <c r="O89">
-        <v>3256.449239395466</v>
+        <v>3245.298081227597</v>
       </c>
       <c r="P89">
-        <v>6047.691444591579</v>
+        <v>6026.982150851253</v>
       </c>
       <c r="Q89">
-        <v>6564.191444591579</v>
+        <v>6543.482150851253</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3895398798491451</v>
+        <v>0.4163108985289851</v>
       </c>
       <c r="T89">
-        <v>5.001834086110213</v>
+        <v>5.391385027396057</v>
       </c>
       <c r="U89">
         <v>0.07315748822216711</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.356642463864338</v>
+        <v>4.307135163138607</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0918033910865578</v>
+        <v>0.09159603820309123</v>
       </c>
       <c r="C90">
-        <v>9182.669545269076</v>
+        <v>8861.948661428927</v>
       </c>
       <c r="D90">
-        <v>44125.40954526908</v>
+        <v>44240.19366142893</v>
       </c>
       <c r="E90">
-        <v>10407.54</v>
+        <v>10843.045</v>
       </c>
       <c r="F90">
-        <v>38324.44</v>
+        <v>38759.945</v>
       </c>
       <c r="G90">
         <v>3381.7</v>
@@ -8673,28 +8673,28 @@
         <v>12076</v>
       </c>
       <c r="M90">
-        <v>2803.71976792115</v>
+        <v>2835.580219829345</v>
       </c>
       <c r="N90">
-        <v>9272.280232078851</v>
+        <v>9240.419780170654</v>
       </c>
       <c r="O90">
-        <v>3245.298081227597</v>
+        <v>3234.146923059729</v>
       </c>
       <c r="P90">
-        <v>6026.982150851253</v>
+        <v>6006.272857110926</v>
       </c>
       <c r="Q90">
-        <v>6543.482150851253</v>
+        <v>6522.772857110926</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4163108985289851</v>
+        <v>0.4479493751506141</v>
       </c>
       <c r="T90">
-        <v>5.391385027396057</v>
+        <v>5.851763412552051</v>
       </c>
       <c r="U90">
         <v>0.07315748822216711</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.307135163138607</v>
+        <v>4.258740386024689</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09159603820309123</v>
+        <v>0.09197368531962466</v>
       </c>
       <c r="C91">
-        <v>8861.948661428927</v>
+        <v>8217.834463682651</v>
       </c>
       <c r="D91">
-        <v>44240.19366142893</v>
+        <v>44031.58446368266</v>
       </c>
       <c r="E91">
-        <v>10843.045</v>
+        <v>11278.55</v>
       </c>
       <c r="F91">
-        <v>38759.945</v>
+        <v>39195.45</v>
       </c>
       <c r="G91">
         <v>3381.7</v>
@@ -8755,45 +8755,45 @@
         <v>12076</v>
       </c>
       <c r="M91">
-        <v>2835.580219829345</v>
+        <v>2906.63612173754</v>
       </c>
       <c r="N91">
-        <v>9240.419780170654</v>
+        <v>9169.36387826246</v>
       </c>
       <c r="O91">
-        <v>3234.146923059729</v>
+        <v>3209.277357391861</v>
       </c>
       <c r="P91">
-        <v>6006.272857110926</v>
+        <v>5960.0865208706</v>
       </c>
       <c r="Q91">
-        <v>6522.772857110926</v>
+        <v>6476.5865208706</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4479493751506141</v>
+        <v>0.4859155470965691</v>
       </c>
       <c r="T91">
-        <v>5.851763412552051</v>
+        <v>6.404217474739247</v>
       </c>
       <c r="U91">
-        <v>0.07315748822216711</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V91">
         <v>0.35</v>
       </c>
       <c r="W91">
-        <v>0.04755236734440862</v>
+        <v>0.04820236734440862</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.258740386024689</v>
+        <v>4.154630815219196</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09197368531962466</v>
+        <v>0.09177283243615808</v>
       </c>
       <c r="C92">
-        <v>8217.834463682651</v>
+        <v>7893.033428556388</v>
       </c>
       <c r="D92">
-        <v>44031.58446368266</v>
+        <v>44142.28842855639</v>
       </c>
       <c r="E92">
-        <v>11278.55</v>
+        <v>11714.055</v>
       </c>
       <c r="F92">
-        <v>39195.45</v>
+        <v>39630.955</v>
       </c>
       <c r="G92">
         <v>3381.7</v>
@@ -8837,28 +8837,28 @@
         <v>12076</v>
       </c>
       <c r="M92">
-        <v>2906.63612173754</v>
+        <v>2938.932078645735</v>
       </c>
       <c r="N92">
-        <v>9169.36387826246</v>
+        <v>9137.067921354264</v>
       </c>
       <c r="O92">
-        <v>3209.277357391861</v>
+        <v>3197.973772473993</v>
       </c>
       <c r="P92">
-        <v>5960.0865208706</v>
+        <v>5939.094148880272</v>
       </c>
       <c r="Q92">
-        <v>6476.5865208706</v>
+        <v>6455.594148880272</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4859155470965691</v>
+        <v>0.5323186461416249</v>
       </c>
       <c r="T92">
-        <v>6.404217474739247</v>
+        <v>7.079439106301374</v>
       </c>
       <c r="U92">
         <v>0.07415748822216711</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.154630815219196</v>
+        <v>4.108975531535469</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09177283243615808</v>
+        <v>0.09157197955269152</v>
       </c>
       <c r="C93">
-        <v>7893.033428556388</v>
+        <v>7568.790459101809</v>
       </c>
       <c r="D93">
-        <v>44142.28842855639</v>
+        <v>44253.55045910181</v>
       </c>
       <c r="E93">
-        <v>11714.055</v>
+        <v>12149.56</v>
       </c>
       <c r="F93">
-        <v>39630.955</v>
+        <v>40066.46</v>
       </c>
       <c r="G93">
         <v>3381.7</v>
@@ -8919,28 +8919,28 @@
         <v>12076</v>
       </c>
       <c r="M93">
-        <v>2938.932078645735</v>
+        <v>2971.22803555393</v>
       </c>
       <c r="N93">
-        <v>9137.067921354264</v>
+        <v>9104.77196444607</v>
       </c>
       <c r="O93">
-        <v>3197.973772473993</v>
+        <v>3186.670187556124</v>
       </c>
       <c r="P93">
-        <v>5939.094148880272</v>
+        <v>5918.101776889946</v>
       </c>
       <c r="Q93">
-        <v>6455.594148880272</v>
+        <v>6434.601776889946</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5323186461416249</v>
+        <v>0.590322519947945</v>
       </c>
       <c r="T93">
-        <v>7.079439106301374</v>
+        <v>7.923466145754035</v>
       </c>
       <c r="U93">
         <v>0.07415748822216711</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.108975531535469</v>
+        <v>4.064312754018779</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09157197955269152</v>
+        <v>0.09137112666922494</v>
       </c>
       <c r="C94">
-        <v>7568.790459101809</v>
+        <v>7245.109785848515</v>
       </c>
       <c r="D94">
-        <v>44253.55045910181</v>
+        <v>44365.37478584852</v>
       </c>
       <c r="E94">
-        <v>12149.56</v>
+        <v>12585.065</v>
       </c>
       <c r="F94">
-        <v>40066.46</v>
+        <v>40501.965</v>
       </c>
       <c r="G94">
         <v>3381.7</v>
@@ -9001,28 +9001,28 @@
         <v>12076</v>
       </c>
       <c r="M94">
-        <v>2971.22803555393</v>
+        <v>3003.523992462125</v>
       </c>
       <c r="N94">
-        <v>9104.77196444607</v>
+        <v>9072.476007537874</v>
       </c>
       <c r="O94">
-        <v>3186.670187556124</v>
+        <v>3175.366602638256</v>
       </c>
       <c r="P94">
-        <v>5918.101776889946</v>
+        <v>5897.109404899618</v>
       </c>
       <c r="Q94">
-        <v>6434.601776889946</v>
+        <v>6413.609404899618</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.590322519947945</v>
+        <v>0.6648989291274993</v>
       </c>
       <c r="T94">
-        <v>7.923466145754035</v>
+        <v>9.008643767907452</v>
       </c>
       <c r="U94">
         <v>0.07415748822216711</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.064312754018779</v>
+        <v>4.020610466341157</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09137112666922494</v>
+        <v>0.09117027378575837</v>
       </c>
       <c r="C95">
-        <v>7245.109785848515</v>
+        <v>6921.995682194924</v>
       </c>
       <c r="D95">
-        <v>44365.37478584852</v>
+        <v>44477.76568219493</v>
       </c>
       <c r="E95">
-        <v>12585.065</v>
+        <v>13020.57</v>
       </c>
       <c r="F95">
-        <v>40501.965</v>
+        <v>40937.47</v>
       </c>
       <c r="G95">
         <v>3381.7</v>
@@ -9083,28 +9083,28 @@
         <v>12076</v>
       </c>
       <c r="M95">
-        <v>3003.523992462125</v>
+        <v>3035.81994937032</v>
       </c>
       <c r="N95">
-        <v>9072.476007537874</v>
+        <v>9040.18005062968</v>
       </c>
       <c r="O95">
-        <v>3175.366602638256</v>
+        <v>3164.063017720388</v>
       </c>
       <c r="P95">
-        <v>5897.109404899618</v>
+        <v>5876.117032909293</v>
       </c>
       <c r="Q95">
-        <v>6413.609404899618</v>
+        <v>6392.617032909293</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6648989291274993</v>
+        <v>0.7643341413669053</v>
       </c>
       <c r="T95">
-        <v>9.008643767907452</v>
+        <v>10.45554726411202</v>
       </c>
       <c r="U95">
         <v>0.07415748822216711</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.020610466341157</v>
+        <v>3.977838014571571</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09117027378575837</v>
+        <v>0.09096942090229181</v>
       </c>
       <c r="C96">
-        <v>6921.995682194924</v>
+        <v>6599.45246495265</v>
       </c>
       <c r="D96">
-        <v>44477.76568219493</v>
+        <v>44590.72746495266</v>
       </c>
       <c r="E96">
-        <v>13020.57</v>
+        <v>13456.075</v>
       </c>
       <c r="F96">
-        <v>40937.47</v>
+        <v>41372.97500000001</v>
       </c>
       <c r="G96">
         <v>3381.7</v>
@@ -9165,28 +9165,28 @@
         <v>12076</v>
       </c>
       <c r="M96">
-        <v>3035.81994937032</v>
+        <v>3068.115906278515</v>
       </c>
       <c r="N96">
-        <v>9040.18005062968</v>
+        <v>9007.884093721485</v>
       </c>
       <c r="O96">
-        <v>3164.063017720388</v>
+        <v>3152.759432802519</v>
       </c>
       <c r="P96">
-        <v>5876.117032909293</v>
+        <v>5855.124660918966</v>
       </c>
       <c r="Q96">
-        <v>6392.617032909293</v>
+        <v>6371.624660918966</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7643341413669053</v>
+        <v>0.9035434385020735</v>
       </c>
       <c r="T96">
-        <v>10.45554726411202</v>
+        <v>12.4812121587984</v>
       </c>
       <c r="U96">
         <v>0.07415748822216711</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.977838014571571</v>
+        <v>3.935966035470817</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09096942090229181</v>
+        <v>0.09076856801882524</v>
       </c>
       <c r="C97">
-        <v>6599.45246495265</v>
+        <v>6277.484494899247</v>
       </c>
       <c r="D97">
-        <v>44590.72746495266</v>
+        <v>44704.26449489925</v>
       </c>
       <c r="E97">
-        <v>13456.075</v>
+        <v>13891.58</v>
       </c>
       <c r="F97">
-        <v>41372.97500000001</v>
+        <v>41808.48</v>
       </c>
       <c r="G97">
         <v>3381.7</v>
@@ -9247,28 +9247,28 @@
         <v>12076</v>
       </c>
       <c r="M97">
-        <v>3068.115906278515</v>
+        <v>3100.41186318671</v>
       </c>
       <c r="N97">
-        <v>9007.884093721485</v>
+        <v>8975.58813681329</v>
       </c>
       <c r="O97">
-        <v>3152.759432802519</v>
+        <v>3141.455847884652</v>
       </c>
       <c r="P97">
-        <v>5855.124660918966</v>
+        <v>5834.132288928638</v>
       </c>
       <c r="Q97">
-        <v>6371.624660918966</v>
+        <v>6350.632288928638</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9035434385020735</v>
+        <v>1.112357384204826</v>
       </c>
       <c r="T97">
-        <v>12.4812121587984</v>
+        <v>15.51970950082798</v>
       </c>
       <c r="U97">
         <v>0.07415748822216711</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.935966035470817</v>
+        <v>3.894966389267997</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09076856801882524</v>
+        <v>0.09056771513535869</v>
       </c>
       <c r="C98">
-        <v>6277.484494899254</v>
+        <v>5956.096177339299</v>
       </c>
       <c r="D98">
-        <v>44704.26449489925</v>
+        <v>44818.3811773393</v>
       </c>
       <c r="E98">
-        <v>13891.57999999999</v>
+        <v>14327.085</v>
       </c>
       <c r="F98">
-        <v>41808.48</v>
+        <v>42243.985</v>
       </c>
       <c r="G98">
         <v>3381.7</v>
@@ -9329,28 +9329,28 @@
         <v>12076</v>
       </c>
       <c r="M98">
-        <v>3100.411863186709</v>
+        <v>3132.707820094904</v>
       </c>
       <c r="N98">
-        <v>8975.58813681329</v>
+        <v>8943.292179905096</v>
       </c>
       <c r="O98">
-        <v>3141.455847884652</v>
+        <v>3130.152262966783</v>
       </c>
       <c r="P98">
-        <v>5834.132288928638</v>
+        <v>5813.139916938313</v>
       </c>
       <c r="Q98">
-        <v>6350.632288928638</v>
+        <v>6329.639916938313</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.112357384204823</v>
+        <v>1.460380627042743</v>
       </c>
       <c r="T98">
-        <v>15.51970950082794</v>
+        <v>20.58387173754389</v>
       </c>
       <c r="U98">
         <v>0.07415748822216711</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.894966389267997</v>
+        <v>3.854812096595131</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09056771513535869</v>
+        <v>0.0903668622518921</v>
       </c>
       <c r="C99">
-        <v>5956.096177339299</v>
+        <v>5635.291962674302</v>
       </c>
       <c r="D99">
-        <v>44818.3811773393</v>
+        <v>44933.0819626743</v>
       </c>
       <c r="E99">
-        <v>14327.085</v>
+        <v>14762.59</v>
       </c>
       <c r="F99">
-        <v>42243.985</v>
+        <v>42679.49</v>
       </c>
       <c r="G99">
         <v>3381.7</v>
@@ -9411,28 +9411,28 @@
         <v>12076</v>
       </c>
       <c r="M99">
-        <v>3132.707820094904</v>
+        <v>3165.003777003099</v>
       </c>
       <c r="N99">
-        <v>8943.292179905096</v>
+        <v>8910.996222996901</v>
       </c>
       <c r="O99">
-        <v>3130.152262966783</v>
+        <v>3118.848678048915</v>
       </c>
       <c r="P99">
-        <v>5813.139916938313</v>
+        <v>5792.147544947986</v>
       </c>
       <c r="Q99">
-        <v>6329.639916938313</v>
+        <v>6308.647544947986</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.460380627042743</v>
+        <v>2.156427112718581</v>
       </c>
       <c r="T99">
-        <v>20.58387173754389</v>
+        <v>30.71219621097577</v>
       </c>
       <c r="U99">
         <v>0.07415748822216711</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.854812096595131</v>
+        <v>3.815477279282936</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0903668622518921</v>
+        <v>0.09016600936842553</v>
       </c>
       <c r="C100">
-        <v>5635.291962674302</v>
+        <v>5315.076346981048</v>
       </c>
       <c r="D100">
-        <v>44933.0819626743</v>
+        <v>45048.37134698105</v>
       </c>
       <c r="E100">
-        <v>14762.59</v>
+        <v>15198.095</v>
       </c>
       <c r="F100">
-        <v>42679.49</v>
+        <v>43114.995</v>
       </c>
       <c r="G100">
         <v>3381.7</v>
@@ -9493,28 +9493,28 @@
         <v>12076</v>
       </c>
       <c r="M100">
-        <v>3165.003777003099</v>
+        <v>3197.299733911294</v>
       </c>
       <c r="N100">
-        <v>8910.996222996901</v>
+        <v>8878.700266088706</v>
       </c>
       <c r="O100">
-        <v>3118.848678048915</v>
+        <v>3107.545093131047</v>
       </c>
       <c r="P100">
-        <v>5792.147544947986</v>
+        <v>5771.155172957659</v>
       </c>
       <c r="Q100">
-        <v>6308.647544947986</v>
+        <v>6287.655172957659</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.156427112718581</v>
+        <v>4.244566569746096</v>
       </c>
       <c r="T100">
-        <v>30.71219621097577</v>
+        <v>61.09716963127144</v>
       </c>
       <c r="U100">
         <v>0.07415748822216711</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.815477279282936</v>
+        <v>3.776937104744724</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09016600936842553</v>
-      </c>
-      <c r="C101">
-        <v>5315.076346981048</v>
-      </c>
-      <c r="D101">
-        <v>45048.37134698105</v>
-      </c>
-      <c r="E101">
-        <v>15198.095</v>
-      </c>
-      <c r="F101">
-        <v>43114.995</v>
-      </c>
-      <c r="G101">
-        <v>3381.7</v>
-      </c>
-      <c r="H101">
-        <v>15633.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12592.5</v>
-      </c>
-      <c r="K101">
-        <v>516.5</v>
-      </c>
-      <c r="L101">
-        <v>12076</v>
-      </c>
-      <c r="M101">
-        <v>3197.299733911294</v>
-      </c>
-      <c r="N101">
-        <v>8878.700266088706</v>
-      </c>
-      <c r="O101">
-        <v>3107.545093131047</v>
-      </c>
-      <c r="P101">
-        <v>5771.155172957659</v>
-      </c>
-      <c r="Q101">
-        <v>6287.655172957659</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.244566569746096</v>
-      </c>
-      <c r="T101">
-        <v>61.09716963127144</v>
-      </c>
-      <c r="U101">
-        <v>0.07415748822216711</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.04820236734440862</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.776937104744724</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
